--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1769,10 +1769,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -1809,12 +1809,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>05/22/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1824,24 +1824,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KESHA – The Freedom Tour</t>
+          <t>NIALL HORAN – Dinner Party Live On Tour</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/kesha/</t>
+          <t>https://thekiaforum.com/event/niall-horan/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>05/24/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1851,24 +1851,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RUSH – Fifty Something</t>
+          <t>KESHA – The Freedom Tour</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rush/</t>
+          <t>https://thekiaforum.com/event/kesha/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1878,24 +1878,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+          <t>RUSH – Fifty Something</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
+          <t>https://thekiaforum.com/event/rush/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1905,24 +1905,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MADISON BEER – the locket tour</t>
+          <t>RUSH – Fifty Something</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/madison-beer/</t>
+          <t>https://thekiaforum.com/event/rush-2/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1932,24 +1932,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
+          <t>RUSH – Fifty Something</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
+          <t>https://thekiaforum.com/event/rush-3/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1959,24 +1959,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
+          <t>RUSH – Fifty Something</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/aap-rocky/</t>
+          <t>https://thekiaforum.com/event/rush-4/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/17/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1986,24 +1986,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ROSALÍA – LUX TOUR 2026</t>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rosalia/</t>
+          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2013,24 +2013,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HILARY DUFF – the lucky me tour</t>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/hilary-duff/</t>
+          <t>https://thekiaforum.com/event/ariana-grande/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2040,24 +2040,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
+          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/24/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2067,24 +2067,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>YOUNG THE GIANT – Victory Garden Tour</t>
+          <t>MADISON BEER – the locket tour</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/young-the-giant/</t>
+          <t>https://thekiaforum.com/event/madison-beer/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EVANESCENCE</t>
+          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/evanescence/</t>
+          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
+          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/motionless-in-white/</t>
+          <t>https://thekiaforum.com/event/aap-rocky/</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>06/29/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2148,24 +2148,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
+          <t>ROSALÍA – LUX TOUR 2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ive/</t>
+          <t>https://thekiaforum.com/event/rosalia/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2175,24 +2175,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RÜFÜS DU SOL</t>
+          <t>ROSALÍA – LUX TOUR 2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
+          <t>https://thekiaforum.com/event/rosalia-2/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2202,24 +2202,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
+          <t>HILARY DUFF – the lucky me tour</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
+          <t>https://thekiaforum.com/event/hilary-duff/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2229,24 +2229,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
+          <t>HILARY DUFF – the lucky me tour</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/melanie-martinez/</t>
+          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2256,24 +2256,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
+          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/omar-courtz/</t>
+          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>07/17/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2283,24 +2283,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
+          <t>YOUNG THE GIANT – Victory Garden Tour</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/chicago-styx/</t>
+          <t>https://thekiaforum.com/event/young-the-giant/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2310,24 +2310,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
+          <t>EVANESCENCE</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
+          <t>https://thekiaforum.com/event/evanescence/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>07/31/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2337,24 +2337,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SODA STEREO – ECOS TOUR</t>
+          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/soda-stereo/</t>
+          <t>https://thekiaforum.com/event/motionless-in-white/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2364,24 +2364,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ROBYN – The Sexistential Tour</t>
+          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/robyn/</t>
+          <t>https://thekiaforum.com/event/ive/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2391,24 +2391,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
+          <t>RÜFÜS DU SOL</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lily-allen/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2418,24 +2418,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BILLY STRINGS</t>
+          <t>RÜFÜS DU SOL</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/billy-strings-3/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>08/11/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2445,24 +2445,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
+          <t>RÜFÜS DU SOL</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>08/12/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2472,24 +2472,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+          <t>RÜFÜS DU SOL</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/mumford-sons/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>08/13/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2499,24 +2499,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>08/14/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SOMBR – You Are The Reason Tour</t>
+          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/sombr/</t>
+          <t>https://thekiaforum.com/event/melanie-martinez/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>08/21/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JUANES</t>
+          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/juanes/</t>
+          <t>https://thekiaforum.com/event/omar-courtz/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2580,24 +2580,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
+          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/monsta-x/</t>
+          <t>https://thekiaforum.com/event/chicago-styx/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2607,24 +2607,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DOJA CAT – Tour Ma Vie World Tour</t>
+          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/doja-cat/</t>
+          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>09/12/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2634,24 +2634,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GORILLAZ – The Mountain Tour</t>
+          <t>SODA STEREO – ECOS TOUR</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/gorillaz-2/</t>
+          <t>https://thekiaforum.com/event/soda-stereo/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2661,24 +2661,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DON OMAR – The Last King World Tour</t>
+          <t>ROBYN – The Sexistential Tour</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/don-omar/</t>
+          <t>https://thekiaforum.com/event/robyn/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2688,24 +2688,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MON LAFERTE – Femme Fatale Tour</t>
+          <t>ROBYN – The Sexistential Tour</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/mon-laferte/</t>
+          <t>https://thekiaforum.com/event/robyn-2/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2715,24 +2715,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
+          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
+          <t>https://thekiaforum.com/event/lily-allen/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>09/26/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2742,24 +2742,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+          <t>BILLY STRINGS</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/slayer/</t>
+          <t>https://thekiaforum.com/event/billy-strings-3/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>09/30/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2769,24 +2769,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
+          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rawayana/</t>
+          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2796,24 +2796,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TEDDY SWIMS – The UGLY Tour</t>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/teddy-swims/</t>
+          <t>https://thekiaforum.com/event/mumford-sons/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>06/12/2023</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2823,12 +2823,417 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NIALL HORAN – Dinner Party Live On Tour</t>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/niall-horan/</t>
+          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SOMBR – You Are The Reason Tour</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/sombr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10/16/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>JUANES</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/juanes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10/20/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/monsta-x/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10/22/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DOJA CAT – Tour Ma Vie World Tour</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/doja-cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GORILLAZ – The Mountain Tour</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/gorillaz-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DON OMAR – The Last King World Tour</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/don-omar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MON LAFERTE – Femme Fatale Tour</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mon-laferte/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>11/15/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rawayana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>11/18/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TEDDY SWIMS – The UGLY Tour</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/teddy-swims/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
         </is>
       </c>
     </row>
@@ -2872,6 +3277,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>06/12/2026</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Friday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,12 +504,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>06/15/2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Monday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -531,12 +531,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>06/18/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -558,12 +558,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>06/21/2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sunday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -585,66 +585,66 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>06/25/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Book Your Flight to SoFi Stadium! – Book today with American Airlines</t>
+          <t>Türkiye vs. USA – FIFA World Cup 26™</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/american-airlines</t>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-turkiye-vs-usa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/25/2026</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>06/28/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Türkiye vs. USA – FIFA World Cup 26™</t>
+          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-turkiye-vs-usa</t>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-june28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/28/2026</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -659,19 +659,19 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-june28</t>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-july2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -681,78 +681,78 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
+          <t>Quarterfinals: TBD vs. TBD – FIFA World Cup 26™</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-july2</t>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-quarterfinal-july10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Quarterfinals: TBD vs. TBD – FIFA World Cup 26™</t>
+          <t>Ed Sheeran – With Myles Smith, Sigrid, Aaron Rowe</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-quarterfinal-july10</t>
+          <t>https://www.sofistadium.com/events/detail/ed-sheeran-august-8-2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>08/14/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ed Sheeran – With Myles Smith, Sigrid, Aaron Rowe</t>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/ed-sheeran-august-8-2026</t>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/14/2026</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>08/15/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -766,33 +766,6 @@
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/karol-g-august-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>08/15/2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>https://www.sofistadium.com/events/detail/karol-g-august-15</t>
         </is>
@@ -811,7 +784,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3521,68 +3493,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>No events found</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3616,27 +3533,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/21/2026</t>
+          <t>05/29/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Romeo Santos &amp; Prince Royce – Mejor Tarde Que Nunca Tour 2026</t>
+          <t>PUBLIC TOURS</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/romeosantosprinceroyce052126</t>
+          <t>https://www.rosebowlstadium.com/events/details/614/public-tours</t>
         </is>
       </c>
     </row>
@@ -3648,22 +3565,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/22/2026</t>
+          <t>05/29/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Crypto.com Arena VIP Tours presented by Delta Air Lines – Click ‘Buy Tickets’ to See All Available Tour Times</t>
+          <t>VIP Fan Day MexTour Live</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/cryptocom-arena-vip-tours-presented-by-delta-air-lines-1450890</t>
+          <t>https://www.rosebowlstadium.com/events/details/646/vip-fan-day-mextour-live</t>
         </is>
       </c>
     </row>
@@ -3675,22 +3592,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Crypto.com Arena VIP Tours presented by Delta Air Lines – Click ‘Buy Tickets’ to See All Available Tour Times</t>
+          <t>Mexico vs Australia</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/crypto-com-arena-vip-tours-presented-by-delta-air-lines-1450893</t>
+          <t>https://www.rosebowlstadium.com/events/details/635/mexico-vs-australia</t>
         </is>
       </c>
     </row>
@@ -3702,49 +3619,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/24/2026</t>
+          <t>06/14/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Crypto.com Arena VIP Tours presented by Delta Air Lines – Click ‘Buy Tickets’ to See All Available Tour Times</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/crypto-com-arena-vip-tours-presented-by-delta-air-lines-1450905</t>
+          <t>https://www.rosebowlstadium.com/events/details/601/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Crypto.com Arena VIP Tours presented by Delta Air Lines – Click ‘Buy Tickets’ to See All Available Tour Times</t>
+          <t>PUBLIC TOURS</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/crypto-com-arena-vip-tours-presented-by-delta-air-lines-1450909</t>
+          <t>https://www.rosebowlstadium.com/events/details/615/public-tours</t>
         </is>
       </c>
     </row>
@@ -3756,22 +3673,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/29/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Crypto.com Arena VIP Tours presented by Delta Air Lines – Click ‘Buy Tickets’ to See All Available Tour Times</t>
+          <t>Foodieland</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/crypto-com-arena-vip-tours-presented-by-delta-air-lines-1450912</t>
+          <t>https://www.rosebowlstadium.com/events/details/637/foodieland</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3700,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3793,12 +3710,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Crypto.com Arena VIP Tours presented by Delta Air Lines – Click ‘Buy Tickets’ to See All Available Tour Times</t>
+          <t>Foodieland</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/crypto-com-arena-vip-tours-presented-by-delta-air-lines-1450914</t>
+          <t>https://www.rosebowlstadium.com/events/details/638/foodieland</t>
         </is>
       </c>
     </row>
@@ -3810,49 +3727,805 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/31/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Crypto.com Arena VIP Tours presented by Delta Air Lines – Click ‘Buy Tickets’ to See All Available Tour Times</t>
+          <t>Foodieland</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/crypto-com-arena-vip-tours-presented-by-delta-air-lines-1450915</t>
+          <t>https://www.rosebowlstadium.com/events/details/639/foodieland</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Crypto.com Arena VIP Tours presented by Delta Air Lines – Click ‘Buy Tickets’ to See All Available Tour Times</t>
+          <t>DRUM CORPS AT THE ROSE BOWL</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/crypto-com-arena-vip-tours-presented-by-delta-air-lines-1434456</t>
+          <t>https://www.rosebowlstadium.com/events/details/644/drum-corps-at-the-rose-bowl</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/602/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>07/31/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PUBLIC TOURS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/616/public-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Head in the Clouds</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/642/head-in-the-clouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/603/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NOAH KAHAN - THE GREAT DIVIDE TOUR</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/633/noah-kahan-the-great-divide-tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08/22/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/640/just-like-heaven</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PUBLIC TOURS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/617/public-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GUNS N’ ROSES</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/579/guns-n'-roses</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SAN DIEGO STATE VS UCLA</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/594/san-diego-state-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09/13/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/604/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PURDUE VS UCLA</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/595/purdue-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PUBLIC TOURS</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/618/public-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/605/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>WISCONSIN VS UCLA</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/627/wisconsin-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MICHIGAN STATE VS UCLA</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/628/michigan-state-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10/30/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PUBLIC TOURS</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/620/public-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NEVADA VS UCLA</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/629/nevada-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/606/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ILLINOIS VS UCLA</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/630/illinois-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11/27/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PUBLIC TOURS</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/622/public-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>11/28/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>USC VS UCLA</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/631/usc-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12/13/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/607/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12/26/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/484/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12/27/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/485/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12/28/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/486/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>01/02/2027</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/487/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>01/02/2027</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS (duplicate)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/647/holiday-tours-(duplicate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>01/17/2027</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Rose Bowl Half Marathon &amp; 5K</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/626/rose-bowl-half-marathon-and-5k</t>
         </is>
       </c>
     </row>
@@ -3867,6 +4540,112 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Romeo Santos &amp; Prince Royce – Mejor Tarde Que Nunca Tour 2026</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/romeosantosprinceroyce052126</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -437,14 +437,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,314 +477,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/12/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>USA vs. Paraguay – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-usa-paraguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>06/15/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>IR Iran vs. New Zealand – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-iran-new-zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>06/18/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Switzerland vs. Bosnia and Herzegovina – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-switzerland-vs-bosnia-and-herzegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>06/21/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Belgium vs. IR Iran – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-belgium-iran</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06/25/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Türkiye vs. USA – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-turkiye-vs-usa</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>06/28/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-june28</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>07/02/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-july2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Quarterfinals: TBD vs. TBD – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-quarterfinal-july10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>08/08/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5:30 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Ed Sheeran – With Myles Smith, Sigrid, Aaron Rowe</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/ed-sheeran-august-8-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>08/14/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/karol-g-august-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>08/15/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/karol-g-august-15</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3493,7 +3190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3543,142 +3240,142 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PUBLIC TOURS</t>
+          <t>VIP Fan Day MexTour Live</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/614/public-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/646/vip-fan-day-mextour-live</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/29/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VIP Fan Day MexTour Live</t>
+          <t>Mexico vs Australia</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/646/vip-fan-day-mextour-live</t>
+          <t>https://www.rosebowlstadium.com/events/details/635/mexico-vs-australia</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/14/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mexico vs Australia</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/635/mexico-vs-australia</t>
+          <t>https://www.rosebowlstadium.com/events/details/601/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06/14/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Foodieland</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/601/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/637/foodieland</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PUBLIC TOURS</t>
+          <t>Foodieland</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/615/public-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/638/foodieland</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3688,7 +3385,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/637/foodieland</t>
+          <t>https://www.rosebowlstadium.com/events/details/639/foodieland</t>
         </is>
       </c>
     </row>
@@ -3700,22 +3397,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Foodieland</t>
+          <t>DRUM CORPS AT THE ROSE BOWL</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/638/foodieland</t>
+          <t>https://www.rosebowlstadium.com/events/details/644/drum-corps-at-the-rose-bowl</t>
         </is>
       </c>
     </row>
@@ -3727,22 +3424,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>07/12/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Foodieland</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/639/foodieland</t>
+          <t>https://www.rosebowlstadium.com/events/details/602/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
@@ -3754,22 +3451,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5:15 PM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DRUM CORPS AT THE ROSE BOWL</t>
+          <t>Head in the Clouds</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/644/drum-corps-at-the-rose-bowl</t>
+          <t>https://www.rosebowlstadium.com/events/details/642/head-in-the-clouds</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3478,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3796,34 +3493,34 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/602/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/603/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>08/15/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>6:30 PM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PUBLIC TOURS</t>
+          <t>NOAH KAHAN - THE GREAT DIVIDE TOUR</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/616/public-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/633/noah-kahan-the-great-divide-tour</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3532,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>08/22/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3845,39 +3542,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Head in the Clouds</t>
+          <t>Just Like Heaven</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/642/head-in-the-clouds</t>
+          <t>https://www.rosebowlstadium.com/events/details/640/just-like-heaven</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>GUNS N’ ROSES</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/603/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/579/guns-n'-roses</t>
         </is>
       </c>
     </row>
@@ -3889,61 +3586,61 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>08/15/2026</t>
+          <t>09/12/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6:30 PM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NOAH KAHAN - THE GREAT DIVIDE TOUR</t>
+          <t>SAN DIEGO STATE VS UCLA</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/633/noah-kahan-the-great-divide-tour</t>
+          <t>https://www.rosebowlstadium.com/events/details/594/san-diego-state-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08/22/2026</t>
+          <t>09/13/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Just Like Heaven</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/640/just-like-heaven</t>
+          <t>https://www.rosebowlstadium.com/events/details/604/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>08/28/2026</t>
+          <t>09/19/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3953,39 +3650,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PUBLIC TOURS</t>
+          <t>PURDUE VS UCLA</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/617/public-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/595/purdue-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>10/11/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GUNS N’ ROSES</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/579/guns-n'-roses</t>
+          <t>https://www.rosebowlstadium.com/events/details/605/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3694,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09/12/2026</t>
+          <t>10/17/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4007,39 +3704,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN DIEGO STATE VS UCLA</t>
+          <t>WISCONSIN VS UCLA</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/594/san-diego-state-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/627/wisconsin-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09/13/2026</t>
+          <t>10/24/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>MICHIGAN STATE VS UCLA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/604/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/628/michigan-state-vs-ucla</t>
         </is>
       </c>
     </row>
@@ -4051,7 +3748,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09/19/2026</t>
+          <t>10/31/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4061,66 +3758,66 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PURDUE VS UCLA</t>
+          <t>NEVADA VS UCLA</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/595/purdue-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/629/nevada-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PUBLIC TOURS</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/618/public-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/606/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10/11/2026</t>
+          <t>11/13/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>ILLINOIS VS UCLA</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/605/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/630/illinois-vs-ucla</t>
         </is>
       </c>
     </row>
@@ -4132,7 +3829,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10/17/2026</t>
+          <t>11/28/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4142,51 +3839,51 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>WISCONSIN VS UCLA</t>
+          <t>USC VS UCLA</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/627/wisconsin-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/631/usc-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/24/2026</t>
+          <t>12/13/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MICHIGAN STATE VS UCLA</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/628/michigan-state-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/607/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10/30/2026</t>
+          <t>12/26/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4196,24 +3893,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PUBLIC TOURS</t>
+          <t>HOLIDAY TOURS</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/620/public-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/484/holiday-tours</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10/31/2026</t>
+          <t>12/27/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4223,78 +3920,78 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NEVADA VS UCLA</t>
+          <t>HOLIDAY TOURS</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/629/nevada-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/485/holiday-tours</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/28/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>HOLIDAY TOURS</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/606/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/486/holiday-tours</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11/13/2026</t>
+          <t>01/02/2027</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ILLINOIS VS UCLA</t>
+          <t>HOLIDAY TOURS</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/630/illinois-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/487/holiday-tours</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11/27/2026</t>
+          <t>01/02/2027</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4304,24 +4001,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PUBLIC TOURS</t>
+          <t>HOLIDAY TOURS (duplicate)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/622/public-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/647/holiday-tours-(duplicate)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11/28/2026</t>
+          <t>01/17/2027</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4331,199 +4028,10 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>USC VS UCLA</t>
+          <t>Rose Bowl Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rosebowlstadium.com/events/details/631/usc-vs-ucla</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>12/13/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>5:00 AM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ROSE BOWL FLEA MARKET</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rosebowlstadium.com/events/details/607/rose-bowl-flea-market</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>12/26/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>HOLIDAY TOURS</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rosebowlstadium.com/events/details/484/holiday-tours</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>12/27/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>HOLIDAY TOURS</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rosebowlstadium.com/events/details/485/holiday-tours</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>12/28/2026</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>HOLIDAY TOURS</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rosebowlstadium.com/events/details/486/holiday-tours</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>01/02/2027</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>HOLIDAY TOURS</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rosebowlstadium.com/events/details/487/holiday-tours</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>01/02/2027</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>HOLIDAY TOURS (duplicate)</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rosebowlstadium.com/events/details/647/holiday-tours-(duplicate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>01/17/2027</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Rose Bowl Half Marathon &amp; 5K</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>https://www.rosebowlstadium.com/events/details/626/rose-bowl-half-marathon-and-5k</t>
         </is>
@@ -4561,13 +4069,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -437,14 +437,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,11 +477,314 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/12/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>USA vs. Paraguay – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-usa-paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/15/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IR Iran vs. New Zealand – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-iran-new-zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/18/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Switzerland vs. Bosnia and Herzegovina – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-switzerland-vs-bosnia-and-herzegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/21/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Belgium vs. IR Iran – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-belgium-iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/25/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Türkiye vs. USA – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-turkiye-vs-usa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/28/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-june28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-july2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quarterfinals: TBD vs. TBD – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-quarterfinal-july10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ed Sheeran – With Myles Smith, Sigrid, Aaron Rowe</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/ed-sheeran-august-8-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-15</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1741,7 +1741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1781,12 +1781,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/22/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1796,24 +1796,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NIALL HORAN – Dinner Party Live On Tour</t>
+          <t>RUSH – Fifty Something</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/niall-horan/</t>
+          <t>https://thekiaforum.com/event/rush/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/24/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1823,24 +1823,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KESHA – The Freedom Tour</t>
+          <t>RUSH – Fifty Something</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/kesha/</t>
+          <t>https://thekiaforum.com/event/rush-2/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1855,19 +1855,19 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rush/</t>
+          <t>https://thekiaforum.com/event/rush-3/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1882,19 +1882,19 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rush-2/</t>
+          <t>https://thekiaforum.com/event/rush-4/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>06/17/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1904,24 +1904,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RUSH – Fifty Something</t>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rush-3/</t>
+          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RUSH – Fifty Something</t>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rush-4/</t>
+          <t>https://thekiaforum.com/event/ariana-grande/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06/17/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1963,19 +1963,19 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
+          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/24/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1985,24 +1985,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+          <t>MADISON BEER – the locket tour</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ariana-grande/</t>
+          <t>https://thekiaforum.com/event/madison-beer/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2012,24 +2012,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
+          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>06/24/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2039,24 +2039,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MADISON BEER – the locket tour</t>
+          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/madison-beer/</t>
+          <t>https://thekiaforum.com/event/aap-rocky/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>06/29/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2066,24 +2066,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
+          <t>ROSALÍA – LUX TOUR 2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
+          <t>https://thekiaforum.com/event/rosalia/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2093,24 +2093,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
+          <t>ROSALÍA – LUX TOUR 2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/aap-rocky/</t>
+          <t>https://thekiaforum.com/event/rosalia-2/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>06/29/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2120,24 +2120,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ROSALÍA – LUX TOUR 2026</t>
+          <t>HILARY DUFF – the lucky me tour</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rosalia/</t>
+          <t>https://thekiaforum.com/event/hilary-duff/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2147,24 +2147,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ROSALÍA – LUX TOUR 2026</t>
+          <t>HILARY DUFF – the lucky me tour</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rosalia-2/</t>
+          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2174,24 +2174,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HILARY DUFF – the lucky me tour</t>
+          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/hilary-duff/</t>
+          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>07/17/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HILARY DUFF – the lucky me tour</t>
+          <t>YOUNG THE GIANT – Victory Garden Tour</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
+          <t>https://thekiaforum.com/event/young-the-giant/</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
+          <t>EVANESCENCE</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
+          <t>https://thekiaforum.com/event/evanescence/</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07/17/2026</t>
+          <t>07/31/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>YOUNG THE GIANT – Victory Garden Tour</t>
+          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/young-the-giant/</t>
+          <t>https://thekiaforum.com/event/motionless-in-white/</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>07/18/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2282,24 +2282,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EVANESCENCE</t>
+          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/evanescence/</t>
+          <t>https://thekiaforum.com/event/ive/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2309,24 +2309,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
+          <t>RÜFÜS DU SOL</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/motionless-in-white/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2336,24 +2336,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
+          <t>RÜFÜS DU SOL</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ive/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>08/11/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2368,19 +2368,19 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>08/12/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2395,19 +2395,19 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>08/11/2026</t>
+          <t>08/13/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2417,24 +2417,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RÜFÜS DU SOL</t>
+          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
+          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>08/12/2026</t>
+          <t>08/14/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>RÜFÜS DU SOL</t>
+          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
+          <t>https://thekiaforum.com/event/melanie-martinez/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>08/13/2026</t>
+          <t>08/21/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2471,24 +2471,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
+          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
+          <t>https://thekiaforum.com/event/omar-courtz/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>08/14/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
+          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/melanie-martinez/</t>
+          <t>https://thekiaforum.com/event/chicago-styx/</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>08/21/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2525,24 +2525,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
+          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/omar-courtz/</t>
+          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>09/12/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2552,24 +2552,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
+          <t>SODA STEREO – ECOS TOUR</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/chicago-styx/</t>
+          <t>https://thekiaforum.com/event/soda-stereo/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2579,24 +2579,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
+          <t>ROBYN – The Sexistential Tour</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
+          <t>https://thekiaforum.com/event/robyn/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>09/12/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2606,24 +2606,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SODA STEREO – ECOS TOUR</t>
+          <t>ROBYN – The Sexistential Tour</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/soda-stereo/</t>
+          <t>https://thekiaforum.com/event/robyn-2/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2633,24 +2633,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ROBYN – The Sexistential Tour</t>
+          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/robyn/</t>
+          <t>https://thekiaforum.com/event/lily-allen/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/26/2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2660,24 +2660,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ROBYN – The Sexistential Tour</t>
+          <t>BILLY STRINGS</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/robyn-2/</t>
+          <t>https://thekiaforum.com/event/billy-strings-3/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/30/2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2687,24 +2687,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
+          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lily-allen/</t>
+          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>09/26/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BILLY STRINGS</t>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/billy-strings-3/</t>
+          <t>https://thekiaforum.com/event/mumford-sons/</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>09/30/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2741,24 +2741,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
+          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2768,24 +2768,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/mumford-sons/</t>
+          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+          <t>SOMBR – You Are The Reason Tour</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
+          <t>https://thekiaforum.com/event/sombr/</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>10/16/2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,24 +2822,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+          <t>JUANES</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
+          <t>https://thekiaforum.com/event/juanes/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>10/20/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2849,24 +2849,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SOMBR – You Are The Reason Tour</t>
+          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/sombr/</t>
+          <t>https://thekiaforum.com/event/monsta-x/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/16/2026</t>
+          <t>10/22/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JUANES</t>
+          <t>DOJA CAT – Tour Ma Vie World Tour</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/juanes/</t>
+          <t>https://thekiaforum.com/event/doja-cat/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/20/2026</t>
+          <t>10/24/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2903,24 +2903,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
+          <t>GORILLAZ – The Mountain Tour</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/monsta-x/</t>
+          <t>https://thekiaforum.com/event/gorillaz-2/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/22/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DOJA CAT – Tour Ma Vie World Tour</t>
+          <t>DON OMAR – The Last King World Tour</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/doja-cat/</t>
+          <t>https://thekiaforum.com/event/don-omar/</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/24/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2957,24 +2957,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GORILLAZ – The Mountain Tour</t>
+          <t>MON LAFERTE – Femme Fatale Tour</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/gorillaz-2/</t>
+          <t>https://thekiaforum.com/event/mon-laferte/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>11/12/2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2984,24 +2984,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DON OMAR – The Last King World Tour</t>
+          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/don-omar/</t>
+          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>11/13/2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3011,24 +3011,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MON LAFERTE – Femme Fatale Tour</t>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/mon-laferte/</t>
+          <t>https://thekiaforum.com/event/slayer/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11/12/2026</t>
+          <t>11/14/2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3038,24 +3038,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
+          <t>https://thekiaforum.com/event/slayer-2/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11/13/2026</t>
+          <t>11/15/2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3065,24 +3065,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/slayer/</t>
+          <t>https://thekiaforum.com/event/rawayana/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/14/2026</t>
+          <t>11/18/2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3092,24 +3092,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+          <t>TEDDY SWIMS – The UGLY Tour</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/slayer-2/</t>
+          <t>https://thekiaforum.com/event/teddy-swims/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11/15/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3119,24 +3119,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rawayana/</t>
+          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/18/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3146,24 +3146,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TEDDY SWIMS – The UGLY Tour</t>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/teddy-swims/</t>
+          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>05/22/2027</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3173,39 +3173,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+          <t>NIALL HORAN – Dinner Party Live On Tour</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
+          <t>https://thekiaforum.com/event/niall-horan/</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3236,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3281,7 +3253,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3315,12 +3287,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>07/17/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3330,24 +3302,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Houston Dynamo FC</t>
+          <t>LA Galaxy vs LAFC</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-houston-dynamo-fc</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-lafc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/17/2026</t>
+          <t>07/22/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3357,24 +3329,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA Galaxy vs LAFC</t>
+          <t>LA Galaxy vs St. Louis CITY SC</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-lafc</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-st-louis-city-sc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07/22/2026</t>
+          <t>07/25/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3384,12 +3356,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA Galaxy vs St. Louis CITY SC</t>
+          <t>Campeón de Campeones 2026</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-st-louis-city-sc</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/campeon-de-campeones-2026</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3373,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07/25/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3411,24 +3383,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Campeón de Campeones 2026</t>
+          <t>LA Galaxy vs FC Dallas</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/campeon-de-campeones-2026</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-fc-dallas</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>08/19/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3438,24 +3410,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA Galaxy vs FC Dallas</t>
+          <t>LA Galaxy vs San Jose Earthquakes</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-fc-dallas</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-jose-earthquakes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08/19/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3465,12 +3437,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA Galaxy vs San Jose Earthquakes</t>
+          <t>LA Galaxy vs New England Revolution</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-jose-earthquakes</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-england-revolution</t>
         </is>
       </c>
     </row>
@@ -4383,10 +4355,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -4423,33 +4395,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/21/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Romeo Santos &amp; Prince Royce – Mejor Tarde Que Nunca Tour 2026</t>
+          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/romeosantosprinceroyce052126</t>
+          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Golden State Judo</t>
+          <t>Society of Nuclear Medicine and Molecular Imaging Annual Meeting 2026</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/golden-state-judo</t>
+          <t>https://www.laconventioncenter.com/events/detail/society-of-nuclear-medicine-and-molecular-imaging-annual-meeting-2026</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4845,24 +4845,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Society of Nuclear Medicine and Molecular Imaging Annual Meeting 2026</t>
+          <t>FITTED x COD - LOS ANGELES</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/society-of-nuclear-medicine-and-molecular-imaging-annual-meeting-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/fitted-cod-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4872,24 +4872,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FITTED x COD - LOS ANGELES</t>
+          <t>AWS Summit Los Angeles 2026</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/fitted-cod-los-angeles</t>
+          <t>https://www.laconventioncenter.com/events/detail/aws-summit-los-angeles-2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AWS Summit Los Angeles 2026</t>
+          <t>LA Card Show</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/aws-summit-los-angeles-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/la-card-show</t>
         </is>
       </c>
     </row>
@@ -4926,12 +4926,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA Card Show</t>
+          <t>HorrorCon Los Angeles</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/la-card-show</t>
+          <t>https://www.laconventioncenter.com/events/detail/horrorcon-los-angeles-2026</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HorrorCon Los Angeles</t>
+          <t>CoreTCG x One Piece Regionals</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/horrorcon-los-angeles-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/coretcg-one-piece-regionals</t>
         </is>
       </c>
     </row>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -437,10 +437,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -771,415 +771,57 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>01/13/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>01/16/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>01/17/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>01/20/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>01/21/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>01/24/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>01/25/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>01/28/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01/29/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MORAT</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>08/16/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3671?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260613</t>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>06/14/2026</t>
+          <t>08/20/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+          <t>Chargers vs 49ers – Preseason</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3672?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260614</t>
+          <t>https://www.sofistadium.com/events/detail/chargers-49ers-preseason-2026</t>
         </is>
       </c>
     </row>
@@ -1191,142 +833,142 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>08/22/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12:30 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BIG3</t>
+          <t>Rams vs. Saints – Preseason</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3898?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=big3_260620</t>
+          <t>https://www.sofistadium.com/events/detail/rams-saints-preseason-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>08/27/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JOJI: SOLARIS</t>
+          <t>Chargers vs Rams – Preseason</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3506?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260711</t>
+          <t>https://www.sofistadium.com/events/detail/chargers-rams-preseason-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6:30 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JOJI: SOLARIS</t>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3513?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260712</t>
+          <t>https://www.sofistadium.com/events/detail/bts-september-1-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07/17/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Forrest Frank</t>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
+          <t>https://www.sofistadium.com/events/detail/bts-september-2-2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07/27/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4:30 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WWE Monday Night RAW</t>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3937?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wwe_monday_night_raw_260727</t>
+          <t>https://www.sofistadium.com/events/detail/bts-september-5-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1336,12 +978,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Grupo Frontera</t>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3520?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=grupo_frontera_260807</t>
+          <t>https://www.sofistadium.com/events/detail/bts-september-6-2026</t>
         </is>
       </c>
     </row>
@@ -1353,157 +995,157 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/13/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>1:25 PM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
+          <t>Chargers vs. Cardinals – Week 1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
+          <t>https://www.sofistadium.com/events/detail/chargers-cardinals-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>08/15/2026</t>
+          <t>09/20/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>1:05 PM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Yeat</t>
+          <t>Chargers vs. Raiders – Week 2</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3699?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=yeat_260815</t>
+          <t>https://www.sofistadium.com/events/detail/chargers-raiders-2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>08/21/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ne-Yo &amp; Akon</t>
+          <t>Rams vs. Giants – Week 2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
+          <t>https://www.sofistadium.com/events/detail/rams-giants-2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>J. Cole</t>
+          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3492?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-september-25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>09/26/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>J. Cole</t>
+          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3498?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-september-26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/30/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>World of Warcraft®: 20 Years of Music</t>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3683?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=world_of_warcraft_260910</t>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-september-30</t>
         </is>
       </c>
     </row>
@@ -1515,22 +1157,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Maná</t>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-2</t>
         </is>
       </c>
     </row>
@@ -1542,130 +1184,130 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09/19/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>8:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Maná</t>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>aespa LIVE TOUR – SYNK : COMPLæXITY – in Los Angeles</t>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3850?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=aespa_live_tour_261003</t>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TLC and Salt-N-Pepa</t>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3613?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=tlc_salt-n-pepa_261010</t>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/17/2026</t>
+          <t>10/11/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>1:05 PM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Young Miko</t>
+          <t>Chargers vs. Broncos – Week 5</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3707?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=young_miko_261017</t>
+          <t>https://www.sofistadium.com/events/detail/chargers-broncos-2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10/24/2026</t>
+          <t>10/12/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pokémon Night Out</t>
+          <t>Rams vs. Bills – Week 5</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3674?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=pokemon_night_out_261024</t>
+          <t>https://www.sofistadium.com/events/detail/rams-bills-2026</t>
         </is>
       </c>
     </row>
@@ -1677,22 +1319,346 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>10/18/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Rams vs. Cardinals – Week 6</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-cardinals-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11/01/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Rams vs. Chargers – Week 8</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-chargers-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Chargers vs. Texans – Week 9</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-texans-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>11/15/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-november-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>11/22/2026</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Three Days Grace</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Chargers vs. Jets – Week 11</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-jets-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11/25/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Rams vs. Packers – Week 12</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-packers-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>11/29/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5:20 PM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chargers vs. Patriots – Week 12</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-patriots-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Rams vs. Chiefs – Week 13</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-chiefs-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12/17/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chargers vs. 49ers – Week 15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-49ers-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>12/20/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1:25 PM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Rams vs. Cowboys – Week 15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-cowboys-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chargers vs. Chiefs – Week 17</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-chiefs-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Rams vs. Seahawks – Week 18</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-seahawks-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Super Bowl LXI</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/super-bowl-lxi</t>
         </is>
       </c>
     </row>
@@ -1730,6 +1696,992 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01/17/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01/20/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01/24/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01/25/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MORAT</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3671?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260613</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>06/14/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3672?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260614</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BIG3</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3898?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=big3_260620</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3506?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260711</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3513?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260712</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Forrest Frank</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/27/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WWE Monday Night RAW</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3937?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wwe_monday_night_raw_260727</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Grupo Frontera</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3520?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=grupo_frontera_260807</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Yeat</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3699?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=yeat_260815</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ne-Yo &amp; Akon</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3492?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3498?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>World of Warcraft®: 20 Years of Music</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3683?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=world_of_warcraft_260910</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>09/18/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kehlani</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/4033?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kehlani_260924</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>aespa LIVE TOUR – SYNK : COMPLæXITY – in Los Angeles</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3850?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=aespa_live_tour_261003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TLC and Salt-N-Pepa</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3613?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=tlc_salt-n-pepa_261010</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Young Miko</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3707?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=young_miko_261017</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pokémon Night Out</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3674?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=pokemon_night_out_261024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11/22/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Three Days Grace</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1741,7 +2693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2699,12 +3651,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2714,24 +3666,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+          <t>KLANGKUENSTLER – OUTWORLD – Klangkuenstler All Night Long</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/mumford-sons/</t>
+          <t>https://thekiaforum.com/event/klangkuenstler/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2746,19 +3698,19 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
+          <t>https://thekiaforum.com/event/mumford-sons/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2768,24 +3720,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
+          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2795,24 +3747,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SOMBR – You Are The Reason Tour</t>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/sombr/</t>
+          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/16/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,24 +3774,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JUANES</t>
+          <t>SOMBR – You Are The Reason Tour</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/juanes/</t>
+          <t>https://thekiaforum.com/event/sombr/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/20/2026</t>
+          <t>10/16/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2849,24 +3801,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
+          <t>JUANES</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/monsta-x/</t>
+          <t>https://thekiaforum.com/event/juanes/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/22/2026</t>
+          <t>10/20/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2876,24 +3828,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DOJA CAT – Tour Ma Vie World Tour</t>
+          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/doja-cat/</t>
+          <t>https://thekiaforum.com/event/monsta-x/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/24/2026</t>
+          <t>10/22/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2903,24 +3855,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GORILLAZ – The Mountain Tour</t>
+          <t>DOJA CAT – Tour Ma Vie World Tour</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/gorillaz-2/</t>
+          <t>https://thekiaforum.com/event/doja-cat/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>10/24/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2930,24 +3882,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DON OMAR – The Last King World Tour</t>
+          <t>GORILLAZ – The Mountain Tour</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/don-omar/</t>
+          <t>https://thekiaforum.com/event/gorillaz-2/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2957,24 +3909,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MON LAFERTE – Femme Fatale Tour</t>
+          <t>DON OMAR – The Last King World Tour</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/mon-laferte/</t>
+          <t>https://thekiaforum.com/event/don-omar/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/12/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2984,24 +3936,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
+          <t>MON LAFERTE – Femme Fatale Tour</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
+          <t>https://thekiaforum.com/event/mon-laferte/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11/13/2026</t>
+          <t>11/12/2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3011,24 +3963,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/slayer/</t>
+          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11/14/2026</t>
+          <t>11/13/2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3043,19 +3995,19 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/slayer-2/</t>
+          <t>https://thekiaforum.com/event/slayer/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11/15/2026</t>
+          <t>11/14/2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3065,24 +4017,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/rawayana/</t>
+          <t>https://thekiaforum.com/event/slayer-2/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/18/2026</t>
+          <t>11/15/2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3092,24 +4044,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TEDDY SWIMS – The UGLY Tour</t>
+          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/teddy-swims/</t>
+          <t>https://thekiaforum.com/event/rawayana/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/18/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3119,24 +4071,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+          <t>TEDDY SWIMS – The UGLY Tour</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
+          <t>https://thekiaforum.com/event/teddy-swims/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3151,7 +4103,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
+          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
         </is>
       </c>
     </row>
@@ -3163,20 +4115,47 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>05/22/2027</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>NIALL HORAN – Dinner Party Live On Tour</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>https://thekiaforum.com/event/niall-horan/</t>
         </is>
@@ -3236,6 +4215,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1092,573 +1092,6 @@
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>https://www.sofistadium.com/events/detail/chris-brown-usher-september-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>09/26/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-september-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>09/30/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/bruno-mars-september-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>10/02/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>10/11/2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1:05 PM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Chargers vs. Broncos – Week 5</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-broncos-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>10/12/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>5:15 PM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Rams vs. Bills – Week 5</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/rams-bills-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>10/18/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1:05 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Rams vs. Cardinals – Week 6</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/rams-cardinals-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>11/01/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1:05 PM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Rams vs. Chargers – Week 8</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/rams-chargers-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1:05 PM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Chargers vs. Texans – Week 9</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-texans-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>11/15/2026</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-november-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>11/22/2026</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1:05 PM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Chargers vs. Jets – Week 11</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-jets-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>11/25/2026</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Rams vs. Packers – Week 12</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/rams-packers-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>11/29/2026</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>5:20 PM</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Chargers vs. Patriots – Week 12</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-patriots-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>5:15 PM</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Rams vs. Chiefs – Week 13</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/rams-chiefs-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>12/17/2026</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>5:15 PM</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Chargers vs. 49ers – Week 15</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-49ers-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>12/20/2026</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1:25 PM</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Rams vs. Cowboys – Week 15</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/rams-cowboys-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Chargers vs. Chiefs – Week 17</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-chiefs-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Rams vs. Seahawks – Week 18</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/rams-seahawks-2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Super Bowl LXI</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/super-bowl-lxi</t>
         </is>
       </c>
     </row>
@@ -1687,27 +1120,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4277,7 +3689,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4304,7 +3716,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4331,7 +3743,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4358,7 +3770,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4385,7 +3797,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4412,7 +3824,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5143,7 +4555,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5170,7 +4582,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5197,7 +4609,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5224,7 +4636,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5251,7 +4663,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5491,7 +4903,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5518,7 +4930,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5545,7 +4957,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5572,7 +4984,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5599,7 +5011,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5626,7 +5038,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5653,7 +5065,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5680,7 +5092,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5707,7 +5119,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5793,7 +5205,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5820,7 +5232,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5847,7 +5259,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5874,7 +5286,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5901,7 +5313,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5928,7 +5340,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Past Events" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Past Events" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,14 +438,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,11 +478,986 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/12/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>USA vs. Paraguay – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-usa-paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/15/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IR Iran vs. New Zealand – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-iran-new-zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/18/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Switzerland vs. Bosnia and Herzegovina – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-switzerland-vs-bosnia-and-herzegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/21/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Belgium vs. IR Iran – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-belgium-iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/25/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Türkiye vs. USA – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-turkiye-vs-usa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/28/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-june28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-july2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quarterfinals: TBD vs. TBD – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-quarterfinal-july10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ed Sheeran – With Myles Smith, Sigrid, Aaron Rowe</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/ed-sheeran-august-8-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08/16/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>08/20/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Chargers vs 49ers – Preseason</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-49ers-preseason-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>08/22/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rams vs. Saints – Preseason</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-saints-preseason-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08/27/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Chargers vs Rams – Preseason</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-rams-preseason-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bts-september-1-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bts-september-2-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bts-september-5-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bts-september-6-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>09/13/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1:25 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Chargers vs. Cardinals – Week 1</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-cardinals-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>09/20/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Chargers vs. Raiders – Week 2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-raiders-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Rams vs. Giants – Week 2</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-giants-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-september-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-september-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-september-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Chargers vs. Broncos – Week 5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-broncos-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Rams vs. Bills – Week 5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-bills-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10/18/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Rams vs. Cardinals – Week 6</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-cardinals-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11/01/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Rams vs. Chargers – Week 8</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-chargers-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Chargers vs. Texans – Week 9</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-texans-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>11/15/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-november-15</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -493,14 +1468,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,11 +1508,930 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01/17/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01/20/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01/24/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01/25/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MORAT</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3671?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260613</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>06/14/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3672?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260614</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BIG3</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3898?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=big3_260620</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3506?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260711</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3513?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260712</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Forrest Frank</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/27/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WWE Monday Night RAW</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3937?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wwe_monday_night_raw_260727</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Grupo Frontera</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3520?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=grupo_frontera_260807</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Yeat</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3699?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=yeat_260815</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ne-Yo &amp; Akon</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3492?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3498?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>World of Warcraft®: 20 Years of Music</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3683?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=world_of_warcraft_260910</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>09/18/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kehlani</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/4033?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kehlani_260924</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>aespa LIVE TOUR – SYNK : COMPLæXITY – in Los Angeles</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3850?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=aespa_live_tour_261003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TLC and Salt-N-Pepa</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3613?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=tlc_salt-n-pepa_261010</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Young Miko</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3707?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=young_miko_261017</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pokémon Night Out</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3674?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=pokemon_night_out_261024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11/22/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Three Days Grace</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -548,14 +2442,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,11 +2482,1490 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/17/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/19/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06/24/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MADISON BEER – the locket tour</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/madison-beer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06/26/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06/27/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/aap-rocky/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>06/29/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ROSALÍA – LUX TOUR 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rosalia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ROSALÍA – LUX TOUR 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rosalia-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HILARY DUFF – the lucky me tour</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/hilary-duff/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HILARY DUFF – the lucky me tour</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>YOUNG THE GIANT – Victory Garden Tour</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/young-the-giant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/18/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EVANESCENCE</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/evanescence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/31/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/motionless-in-white/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ive/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08/13/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/melanie-martinez/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/omar-courtz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/chicago-styx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09/11/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SODA STEREO – ECOS TOUR</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/soda-stereo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>09/23/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ROBYN – The Sexistential Tour</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/robyn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ROBYN – The Sexistential Tour</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/robyn-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/lily-allen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BILLY STRINGS</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/billy-strings-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>KLANGKUENSTLER – OUTWORLD – Klangkuenstler All Night Long</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/klangkuenstler/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mumford-sons/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SOMBR – You Are The Reason Tour</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/sombr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10/16/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JUANES</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/juanes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10/20/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/monsta-x/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10/22/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DOJA CAT – Tour Ma Vie World Tour</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/doja-cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GORILLAZ – The Mountain Tour</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/gorillaz-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DON OMAR – The Last King World Tour</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/don-omar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MON LAFERTE – Femme Fatale Tour</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mon-laferte/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>11/15/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rawayana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>11/18/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TEDDY SWIMS – The UGLY Tour</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/teddy-swims/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>05/22/2027</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NIALL HORAN – Dinner Party Live On Tour</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/niall-horan/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -603,14 +3976,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -643,11 +4016,174 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs LAFC</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-lafc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07/22/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-st-louis-city-sc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07/25/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Campeón de Campeones 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/campeon-de-campeones-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs FC Dallas</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-fc-dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08/19/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-jose-earthquakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs New England Revolution</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-england-revolution</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -658,14 +4194,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,11 +4234,846 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>05/29/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VIP Fan Day MexTour Live</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/646/vip-fan-day-mextour-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>05/30/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mexico vs Australia</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/635/mexico-vs-australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/14/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/601/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Foodieland</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/637/foodieland</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Foodieland</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/638/foodieland</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Foodieland</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/639/foodieland</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DRUM CORPS AT THE ROSE BOWL</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/644/drum-corps-at-the-rose-bowl</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/602/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Head in the Clouds</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/642/head-in-the-clouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/603/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NOAH KAHAN - THE GREAT DIVIDE TOUR</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/633/noah-kahan-the-great-divide-tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08/22/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/640/just-like-heaven</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GUNS N’ ROSES</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/579/guns-n'-roses</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SAN DIEGO STATE VS UCLA</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/594/san-diego-state-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>09/13/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/604/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PURDUE VS UCLA</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/595/purdue-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/605/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WISCONSIN VS UCLA</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/627/wisconsin-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MICHIGAN STATE VS UCLA</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/628/michigan-state-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NEVADA VS UCLA</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/629/nevada-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/606/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ILLINOIS VS UCLA</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/630/illinois-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11/28/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>USC VS UCLA</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/631/usc-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12/13/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/607/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12/26/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/484/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12/27/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/485/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12/28/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/486/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>01/02/2027</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/487/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>01/02/2027</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS (duplicate)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/647/holiday-tours-(duplicate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>01/17/2027</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rose Bowl Half Marathon &amp; 5K</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/626/rose-bowl-half-marathon-and-5k</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -713,14 +5084,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,11 +5124,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -768,14 +5190,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -808,11 +5230,258 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FIFA Fan Festival™ Los Angeles</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/fifa-fan-festival-los-angeles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>America250 July 4 Concert</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/america250-july-4-concert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08/29/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Jose State vs USC</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/sanjosestate-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fresno State vs USC</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/fresno-state-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Louisiana vs USC</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/louisiana-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oregon vs USC</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/oregon-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Washington vs USC</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/washington-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ohio State vs USC</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/ohio-state-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11/21/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Maryland vs USC</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/maryland-vs-usc-2026/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -823,14 +5492,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,11 +5532,174 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>05/30/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Society of Nuclear Medicine and Molecular Imaging Annual Meeting 2026</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/society-of-nuclear-medicine-and-molecular-imaging-annual-meeting-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FITTED x COD - LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/fitted-cod-los-angeles</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AWS Summit Los Angeles 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/aws-summit-los-angeles-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LA Card Show</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/la-card-show</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HorrorCon Los Angeles</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/horrorcon-los-angeles-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CoreTCG x One Piece Regionals</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/coretcg-one-piece-regionals</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -878,13 +878,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F208"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -971,7 +971,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1023,7 +1023,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>05/18/2026</t>
@@ -1031,7 +1035,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1095,7 +1099,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1127,7 +1131,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1159,7 +1163,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1223,7 +1227,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1403,7 +1407,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>05/08/2026</t>
@@ -1411,7 +1419,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1495,7 +1503,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>05/03/2026</t>
@@ -1503,7 +1515,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1523,7 +1535,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>05/03/2026</t>
@@ -1531,7 +1547,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1563,7 +1579,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1583,7 +1599,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>04/27/2026</t>
@@ -1591,7 +1611,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1655,7 +1675,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1675,7 +1695,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>04/22/2026</t>
@@ -1683,7 +1707,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1715,7 +1739,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1767,7 +1791,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>04/16/2026</t>
@@ -1775,7 +1803,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1807,7 +1835,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1987,7 +2015,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>04/11/2026</t>
@@ -1995,7 +2027,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2027,7 +2059,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2143,7 +2175,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>04/08/2026</t>
@@ -2151,7 +2187,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2439,7 +2475,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2503,7 +2539,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2567,7 +2603,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2715,7 +2751,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
           <t>03/28/2026</t>
@@ -2723,7 +2763,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2775,7 +2815,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
           <t>03/27/2026</t>
@@ -2783,7 +2827,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2815,7 +2859,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2879,7 +2923,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2943,7 +2987,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3103,7 +3147,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3359,7 +3403,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3583,7 +3627,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3647,7 +3691,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3711,7 +3755,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3743,7 +3787,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3795,7 +3839,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
           <t>03/06/2026</t>
@@ -3803,7 +3851,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3887,7 +3935,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
           <t>03/04/2026</t>
@@ -3895,7 +3947,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3947,7 +3999,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
           <t>03/03/2026</t>
@@ -3955,7 +4011,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4199,7 +4255,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
           <t>02/28/2026</t>
@@ -4207,7 +4267,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4227,7 +4287,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>02/28/2026</t>
@@ -4235,7 +4299,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4267,7 +4331,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4299,7 +4363,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4523,7 +4587,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4587,7 +4651,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4735,7 +4799,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
           <t>02/22/2026</t>
@@ -4743,7 +4811,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4967,7 +5035,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5127,7 +5195,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5159,7 +5227,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5191,7 +5259,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5255,7 +5323,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5319,7 +5387,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5383,7 +5451,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5415,7 +5483,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5435,7 +5503,11 @@
           <t>Crypto.com Arena</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr">
         <is>
           <t>02/13/2026</t>
@@ -5443,7 +5515,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5475,7 +5547,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5527,7 +5599,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
       <c r="C148" t="inlineStr">
         <is>
           <t>02/12/2026</t>
@@ -5535,7 +5611,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5823,7 +5899,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5855,7 +5931,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5887,7 +5963,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5907,7 +5983,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
       <c r="C160" t="inlineStr">
         <is>
           <t>01/31/2026</t>
@@ -5915,7 +5995,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5947,7 +6027,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5967,7 +6047,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
       <c r="C162" t="inlineStr">
         <is>
           <t>01/07/2026</t>
@@ -5975,7 +6059,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5995,7 +6079,11 @@
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
       <c r="C163" t="inlineStr">
         <is>
           <t>01/06/2026</t>
@@ -6003,7 +6091,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Time TBA</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6014,1386 +6102,6 @@
       <c r="F163" s="2" t="inlineStr">
         <is>
           <t>https://www.laconventioncenter.com/events/detail/la-art-show-2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>11/22/2025</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Three Days Grace</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>L.A. Memorial Coliseum</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>11/02/2025</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Maryland vs USC</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/maryland-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>10/22/2025</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>DOJA CAT</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/doja-cat/</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>10/17/2025</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>American Academy of Otolaryngology: 2026 AAO OTO EXPO</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/american-academy-of-otolaryngology-2026-aao-oto-expo</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>10/09/2025</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>10/09/2025</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>SCG CON Los Angeles 2026</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/scg-con-los-angeles-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>L.A. Memorial Coliseum</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>10/03/2025</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Washington vs USC</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/washington-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>L.A. Memorial Coliseum</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>10/03/2025</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Ohio State vs USC</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/ohio-state-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>09/23/2025</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>National Black MBA Annual Conference &amp; Exposition</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/national-black-mba-association-conference-exposition</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>09/19/2025</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>8:30 PM</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Maná</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>09/18/2025</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>8:30 PM</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Maná</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>09/16/2025</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>ASLA 2026 Conference on Landscape Architecture</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/asla-2026-conference-on-landscape-architecture</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>09/06/2025</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>CHICAGO &amp; STYX</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/chicago-styx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>L.A. Memorial Coliseum</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>09/05/2025</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Fresno State vs USC</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/fresno-state-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>L.A. Memorial Coliseum</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>09/02/2025</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Oregon vs USC</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/oregon-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>L.A. Memorial Coliseum</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>09/01/2025</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Louisiana vs USC</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/louisiana-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>08/21/2025</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Ne-Yo &amp; Akon</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>08/15/2025</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>MEGHAN TRAINOR</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/meghan-trainor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>08/15/2025</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>APWU Biennial Convention 2026</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/apwu-biennial-convention-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>08/09/2025</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>El Sembrador Ministries - Metanoia Los Angeles</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/el-sembrador-ministries-metanoia-los-angeles</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>08/07/2025</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Megan Moroney</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/megan-moroney-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>08/03/2025</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>NALC 74th Biennial Convention</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/nalc-74th-biennial-convention</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>L.A. Memorial Coliseum</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>08/02/2025</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>TBD vs USC</t>
-        </is>
-      </c>
-      <c r="F187" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/tbd-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>08/01/2025</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Collect-A-Con Los Angeles</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/collect-a-con-los-angeles-august-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>07/18/2025</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>EVANESCENCE</t>
-        </is>
-      </c>
-      <c r="F189" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/evanescence/</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>07/17/2025</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Forrest Frank</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>07/14/2025</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Olivia Dean</t>
-        </is>
-      </c>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/oliviadean26</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>07/11/2025</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>5 SECONDS OF SUMMER</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>07/02/2025</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Anime Expo 2026</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/anime-expo-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>07/01/2025</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>ROSALÍA</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rosalia-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>06/29/2025</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>ROSALÍA</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rosalia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>06/27/2025</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>A$AP ROCKY</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/aap-rocky/</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>06/24/2025</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>MADISON BEER</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/madison-beer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>06/20/2025</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>06/19/2025</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE</t>
-        </is>
-      </c>
-      <c r="F199" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande/</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>06/19/2025</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>SoCal Cup: The Showcase</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/socal-cup-the-showcase-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>06/17/2025</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>06/13/2025</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>RUSH</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>06/13/2025</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Ariana Grande</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/arianagrande26</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>06/13/2025</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Security and Safety Expo</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/security-and-safety-expo</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>LA Convention Center</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>06/13/2025</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>HorrorCon Los Angeles</t>
-        </is>
-      </c>
-      <c r="F205" s="2" t="inlineStr">
-        <is>
-          <t>https://www.laconventioncenter.com/events/detail/horrorcon-los-angeles-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>06/11/2025</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>RUSH</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>06/09/2025</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>RUSH</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Kia Forum</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>06/07/2025</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Time TBA</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>RUSH</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush/</t>
         </is>
       </c>
     </row>
@@ -7561,51 +6269,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId207"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Past Events" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Past Events" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,14 +438,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,11 +478,650 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/12/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>USA vs. Paraguay – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-usa-paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/15/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IR Iran vs. New Zealand – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-iran-new-zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/18/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Switzerland vs. Bosnia and Herzegovina – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-switzerland-vs-bosnia-and-herzegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/21/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Belgium vs. IR Iran – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-belgium-iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/25/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Türkiye vs. USA – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-turkiye-vs-usa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/28/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-june28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-july2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quarterfinals: TBD vs. TBD – FIFA World Cup 26™</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-quarterfinal-july10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ed Sheeran – With Myles Smith, Sigrid, Aaron Rowe</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/ed-sheeran-august-8-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08/16/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/karol-g-august-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>08/20/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Chargers vs 49ers – Preseason</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-49ers-preseason-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>08/22/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rams vs. Saints – Preseason</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-saints-preseason-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08/27/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Chargers vs Rams – Preseason</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-rams-preseason-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bts-september-1-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bts-september-2-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bts-september-5-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bts-september-6-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>09/13/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1:25 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Chargers vs. Cardinals – Week 1</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-cardinals-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>09/20/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Chargers vs. Raiders – Week 2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-raiders-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Rams vs. Giants – Week 2</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-giants-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-september-25</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -493,14 +1132,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,11 +1172,930 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01/17/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01/20/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01/24/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01/25/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MORAT</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3671?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260613</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>06/14/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3672?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260614</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BIG3</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3898?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=big3_260620</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3506?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260711</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3513?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260712</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Forrest Frank</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/27/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WWE Monday Night RAW</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3937?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wwe_monday_night_raw_260727</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Grupo Frontera</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3520?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=grupo_frontera_260807</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Yeat</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3699?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=yeat_260815</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ne-Yo &amp; Akon</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3492?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3498?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>World of Warcraft®: 20 Years of Music</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3683?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=world_of_warcraft_260910</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>09/18/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kehlani</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/4033?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kehlani_260924</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>aespa LIVE TOUR – SYNK : COMPLæXITY – in Los Angeles</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3850?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=aespa_live_tour_261003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TLC and Salt-N-Pepa</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3613?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=tlc_salt-n-pepa_261010</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Young Miko</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3707?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=young_miko_261017</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pokémon Night Out</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3674?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=pokemon_night_out_261024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11/22/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Three Days Grace</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -548,14 +2106,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,11 +2146,1490 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/17/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/19/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06/24/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MADISON BEER – the locket tour</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/madison-beer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06/26/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06/27/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/aap-rocky/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>06/29/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ROSALÍA – LUX TOUR 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rosalia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ROSALÍA – LUX TOUR 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rosalia-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HILARY DUFF – the lucky me tour</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/hilary-duff/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HILARY DUFF – the lucky me tour</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>YOUNG THE GIANT – Victory Garden Tour</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/young-the-giant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/18/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EVANESCENCE</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/evanescence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/31/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/motionless-in-white/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ive/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08/13/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/melanie-martinez/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/omar-courtz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/chicago-styx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09/11/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SODA STEREO – ECOS TOUR</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/soda-stereo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>09/23/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ROBYN – The Sexistential Tour</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/robyn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ROBYN – The Sexistential Tour</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/robyn-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/lily-allen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BILLY STRINGS</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/billy-strings-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>KLANGKUENSTLER – OUTWORLD – Klangkuenstler All Night Long</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/klangkuenstler/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mumford-sons/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SOMBR – You Are The Reason Tour</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/sombr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10/16/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JUANES</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/juanes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10/20/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/monsta-x/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10/22/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DOJA CAT – Tour Ma Vie World Tour</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/doja-cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GORILLAZ – The Mountain Tour</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/gorillaz-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DON OMAR – The Last King World Tour</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/don-omar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MON LAFERTE – Femme Fatale Tour</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mon-laferte/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>11/15/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rawayana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>11/18/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TEDDY SWIMS – The UGLY Tour</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/teddy-swims/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>05/22/2027</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NIALL HORAN – Dinner Party Live On Tour</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/niall-horan/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -603,14 +3640,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -643,11 +3680,174 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs LAFC</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-lafc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07/22/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-st-louis-city-sc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07/25/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Campeón de Campeones 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/campeon-de-campeones-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs FC Dallas</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-fc-dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08/19/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-jose-earthquakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs New England Revolution</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-england-revolution</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -658,14 +3858,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,11 +3898,846 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>05/29/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VIP Fan Day MexTour Live</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/646/vip-fan-day-mextour-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>05/30/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mexico vs Australia</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/635/mexico-vs-australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/14/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/601/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Foodieland</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/637/foodieland</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Foodieland</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/638/foodieland</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Foodieland</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/639/foodieland</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DRUM CORPS AT THE ROSE BOWL</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/644/drum-corps-at-the-rose-bowl</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/602/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Head in the Clouds</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/642/head-in-the-clouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/603/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NOAH KAHAN - THE GREAT DIVIDE TOUR</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/633/noah-kahan-the-great-divide-tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08/22/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/640/just-like-heaven</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GUNS N’ ROSES</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/579/guns-n'-roses</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SAN DIEGO STATE VS UCLA</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/594/san-diego-state-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>09/13/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/604/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PURDUE VS UCLA</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/595/purdue-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/605/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WISCONSIN VS UCLA</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/627/wisconsin-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MICHIGAN STATE VS UCLA</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/628/michigan-state-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NEVADA VS UCLA</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/629/nevada-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/606/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ILLINOIS VS UCLA</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/630/illinois-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11/28/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>USC VS UCLA</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/631/usc-vs-ucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12/13/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/607/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12/26/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/484/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12/27/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/485/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12/28/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/486/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>01/02/2027</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/487/holiday-tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>01/02/2027</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS (duplicate)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/647/holiday-tours-(duplicate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>01/17/2027</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rose Bowl Half Marathon &amp; 5K</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/626/rose-bowl-half-marathon-and-5k</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -713,14 +4748,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,11 +4788,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -768,14 +4854,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -808,11 +4894,258 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FIFA Fan Festival™ Los Angeles</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/fifa-fan-festival-los-angeles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>America250 July 4 Concert</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/america250-july-4-concert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08/29/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Jose State vs USC</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/sanjosestate-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fresno State vs USC</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/fresno-state-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Louisiana vs USC</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/louisiana-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oregon vs USC</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/oregon-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Washington vs USC</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/washington-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ohio State vs USC</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/ohio-state-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11/21/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Maryland vs USC</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/maryland-vs-usc-2026/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1093,6 +1093,573 @@
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>https://www.sofistadium.com/events/detail/chris-brown-usher-september-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-september-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-september-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bruno Mars – The Romantic Tour with Anderson.Paak as DJ Pee.Wee and Raye</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/bruno-mars-october-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Chargers vs. Broncos – Week 5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-broncos-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Rams vs. Bills – Week 5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-bills-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10/18/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Rams vs. Cardinals – Week 6</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-cardinals-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11/01/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Rams vs. Chargers – Week 8</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-chargers-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Chargers vs. Texans – Week 9</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-texans-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>11/15/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The R&amp;B Tour - Starring Usher Raymond &amp; Chris Brown</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chris-brown-usher-november-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>11/22/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1:05 PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Chargers vs. Jets – Week 11</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-jets-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11/25/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Rams vs. Packers – Week 12</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-packers-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>11/29/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5:20 PM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chargers vs. Patriots – Week 12</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-patriots-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Rams vs. Chiefs – Week 13</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-chiefs-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12/17/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5:15 PM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chargers vs. 49ers – Week 15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-49ers-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>12/20/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1:25 PM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Rams vs. Cowboys – Week 15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-cowboys-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chargers vs. Chiefs – Week 17</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/chargers-chiefs-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Rams vs. Seahawks – Week 18</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/rams-seahawks-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Super Bowl LXI</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofistadium.com/events/detail/super-bowl-lxi</t>
         </is>
       </c>
     </row>
@@ -1121,6 +1688,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5211,11 +5799,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -8777,17 +9365,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8797,19 +9385,19 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Sporting San Miguelito</t>
+          <t>MORAT</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-san-miguelito</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8824,17 +9412,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vegas Golden Knights vs Los Angeles Kings</t>
+          <t>LA Galaxy vs Sporting San Miguelito</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsknights022526</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-san-miguelito</t>
         </is>
       </c>
     </row>
@@ -8846,66 +9434,66 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>02/24/2026</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Orlando Magic vs Los Angeles Lakers</t>
+          <t>Vegas Golden Knights vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersmagic022426</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsknights022526</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>02/23/2026</t>
+          <t>02/24/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GHOST: Skeletour World Tour 2026</t>
+          <t>Orlando Magic vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2964?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ghost_260223</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersmagic022426</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8920,56 +9508,56 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>GHOST: Skeletour World Tour 2026</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-8/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2964?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ghost_260223</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>02/23/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Orlando Magic vs LA Clippers</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2688?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260222</t>
+          <t>https://thekiaforum.com/event/lady-gaga-8/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8984,24 +9572,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>Orlando Magic vs LA Clippers</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-7/</t>
+          <t>https://intuitdome.com/events/event-schedule/2688?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260222</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9016,24 +9604,24 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LA Galaxy vs New York City FC</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-york-city-fc</t>
+          <t>https://thekiaforum.com/event/lady-gaga-7/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9048,17 +9636,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>LA Galaxy vs New York City FC</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/585/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-york-city-fc</t>
         </is>
       </c>
     </row>
@@ -9080,24 +9668,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/588/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/585/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9112,24 +9700,24 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Boston Celtics vs Los Angeles Lakers</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersceltics022226</t>
+          <t>https://www.rosebowlstadium.com/events/details/588/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9144,56 +9732,56 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ViVE 2026</t>
+          <t>Boston Celtics vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/vive-2026</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersceltics022226</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>8 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Los Bukis</t>
+          <t>ViVE 2026</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/los-bukis-february-21-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/vive-2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9208,24 +9796,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8 PM</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Los Tigres del Norte</t>
+          <t>Los Bukis</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2912?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=los_tigres_del_norte_260221</t>
+          <t>https://www.sofistadium.com/events/detail/los-bukis-february-21-2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9240,17 +9828,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Los Tigres del Norte</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/584/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2912?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=los_tigres_del_norte_260221</t>
         </is>
       </c>
     </row>
@@ -9272,56 +9860,56 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/587/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/584/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>8 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Los Bukis</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/los-bukis-2026</t>
+          <t>https://www.rosebowlstadium.com/events/details/587/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9336,24 +9924,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8 PM</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Harlem Globetrotters</t>
+          <t>Los Bukis</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2904</t>
+          <t>https://www.sofistadium.com/events/detail/los-bukis-2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9368,24 +9956,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SABATON</t>
+          <t>Harlem Globetrotters</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/sabaton/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2904</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9400,17 +9988,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>SABATON</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/583/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://thekiaforum.com/event/sabaton/</t>
         </is>
       </c>
     </row>
@@ -9432,24 +10020,24 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/586/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/583/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9464,56 +10052,56 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Los Angeles Clippers vs Los Angeles Lakers</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersclippers022026</t>
+          <t>https://www.rosebowlstadium.com/events/details/586/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Denver Nuggets vs LA Clippers</t>
+          <t>Los Angeles Clippers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2687?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260219</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersclippers022026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9528,17 +10116,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>Denver Nuggets vs LA Clippers</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-5/</t>
+          <t>https://intuitdome.com/events/event-schedule/2687?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260219</t>
         </is>
       </c>
     </row>
@@ -9550,12 +10138,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>02/18/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9570,7 +10158,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-6/</t>
+          <t>https://thekiaforum.com/event/lady-gaga-5/</t>
         </is>
       </c>
     </row>
@@ -9582,12 +10170,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/18/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9597,51 +10185,51 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CARDI B</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/cardi-b-2/</t>
+          <t>https://thekiaforum.com/event/lady-gaga-6/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>75th NBA All-Star Game</t>
+          <t>CARDI B</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3002?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_game_260215</t>
+          <t>https://thekiaforum.com/event/cardi-b-2/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9656,56 +10244,56 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CARDI B</t>
+          <t>75th NBA All-Star Game</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/cardi-b/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3002?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_game_260215</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/15/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>All-Star Saturday</t>
+          <t>CARDI B</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3003?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_saturday_260214</t>
+          <t>https://thekiaforum.com/event/cardi-b/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9720,56 +10308,56 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>DJ CASSIDY'S PASS THE MIC LIVE!</t>
+          <t>All-Star Saturday</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/dj-cassidys-pass-the-mic-live/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3003?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_saturday_260214</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Castrol Rising Stars</t>
+          <t>DJ CASSIDY'S PASS THE MIC LIVE!</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3004?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=castrol_rising_stars_260213</t>
+          <t>https://thekiaforum.com/event/dj-cassidys-pass-the-mic-live/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9784,17 +10372,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HBCU CLASSIC PRESENTED BY AT&amp;T</t>
+          <t>Castrol Rising Stars</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/hbcu-classic-presented-by-att/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3004?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=castrol_rising_stars_260213</t>
         </is>
       </c>
     </row>
@@ -9821,19 +10409,19 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RUFFLES CELEBRITY GAME</t>
+          <t>HBCU CLASSIC PRESENTED BY AT&amp;T</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ruffles-celebrity-game/</t>
+          <t>https://thekiaforum.com/event/hbcu-classic-presented-by-att/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9853,29 +10441,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Banda MS de Sergio Lizarraga</t>
+          <t>RUFFLES CELEBRITY GAME</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/bandams021326</t>
+          <t>https://thekiaforum.com/event/ruffles-celebrity-game/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9885,19 +10473,19 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>NBA ALL-STAR PITCH COMPETITION</t>
+          <t>Banda MS de Sergio Lizarraga</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/nba-all-star-pitch-competition/</t>
+          <t>https://www.cryptoarena.com/events/detail/bandams021326</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9912,24 +10500,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Dallas Mavericks vs Los Angeles Lakers</t>
+          <t>NBA ALL-STAR PITCH COMPETITION</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersmavs021226</t>
+          <t>https://thekiaforum.com/event/nba-all-star-pitch-competition/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9944,49 +10532,49 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>NBA Crossover: The Ultimate Fan Experience</t>
+          <t>Dallas Mavericks vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/nba-crossover-ultimate-fan-experience</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersmavs021226</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>San Antonio Spurs vs Los Angeles Lakers</t>
+          <t>NBA Crossover: The Ultimate Fan Experience</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersspurs021026</t>
+          <t>https://www.laconventioncenter.com/events/detail/nba-crossover-ultimate-fan-experience</t>
         </is>
       </c>
     </row>
@@ -9998,91 +10586,91 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
+          <t>San Antonio Spurs vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersthuner020926</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersspurs021026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/597/rose-bowl-flea-market</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersthuner020926</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Golden State Warriors vs Los Angeles Lakers</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerswarriors020726</t>
+          <t>https://www.rosebowlstadium.com/events/details/597/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
@@ -10094,66 +10682,66 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers vs Los Angeles Lakers</t>
+          <t>Golden State Warriors vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakers76ers020526</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerswarriors020726</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers vs LA Clippers</t>
+          <t>Philadelphia 76ers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2662?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260204</t>
+          <t>https://www.cryptoarena.com/events/detail/lakers76ers020526</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10168,56 +10756,56 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Seattle Kraken vs Los Angeles Kings</t>
+          <t>Cleveland Cavaliers vs LA Clippers</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingskraken020426</t>
+          <t>https://intuitdome.com/events/event-schedule/2662?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260204</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers vs LA Clippers</t>
+          <t>Seattle Kraken vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2686?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260202</t>
+          <t>https://www.cryptoarena.com/events/detail/kingskraken020426</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>L.A. Memorial Coliseum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10232,17 +10820,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>LAFC vs Inter Miami CF</t>
+          <t>Philadelphia 76ers vs LA Clippers</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/lafc-vs-intermiami-2026/</t>
+          <t>https://intuitdome.com/events/event-schedule/2686?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260202</t>
         </is>
       </c>
     </row>
@@ -10269,29 +10857,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Night of Hope</t>
+          <t>LAFC vs Inter Miami CF</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/night-of-hope/</t>
+          <t>https://www.lacoliseum.com/events/lafc-vs-intermiami-2026/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>L.A. Memorial Coliseum</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10301,19 +10889,19 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>NEW EDITION</t>
+          <t>Night of Hope</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/new-edition/</t>
+          <t>https://www.lacoliseum.com/events/night-of-hope/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10333,12 +10921,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>IBJJF Jiu Jitsu Championship</t>
+          <t>NEW EDITION</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/ibjjf-jiu-jitsu-championship</t>
+          <t>https://thekiaforum.com/event/new-edition/</t>
         </is>
       </c>
     </row>
@@ -10365,12 +10953,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Grand Archive Phantom Monarch Regional Championships</t>
+          <t>IBJJF Jiu Jitsu Championship</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/grand-archive-phantom-monarch-regional-championships</t>
+          <t>https://www.laconventioncenter.com/events/detail/ibjjf-jiu-jitsu-championship</t>
         </is>
       </c>
     </row>
@@ -10382,12 +10970,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10397,42 +10985,394 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Modern Language Association Annual Convention 2027</t>
+          <t>Grand Archive Phantom Monarch Regional Championships</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/modern-language-association-annual-convention-2027</t>
+          <t>https://www.laconventioncenter.com/events/detail/grand-archive-phantom-monarch-regional-championships</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>01/25/2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>01/24/2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>01/20/2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>01/17/2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Modern Language Association Annual Convention 2027</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/modern-language-association-annual-convention-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>LA Convention Center</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>TBA</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>LA Art Show 2027</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>https://www.laconventioncenter.com/events/detail/la-art-show-2027</t>
         </is>
@@ -10602,6 +11542,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId173"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1585,12 +1585,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>02/14/2027</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chargers vs. Chiefs – Week 17</t>
+          <t>Super Bowl LXI</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-chiefs-2026</t>
+          <t>https://www.sofistadium.com/events/detail/super-bowl-lxi</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Rams vs. Seahawks – Week 18</t>
+          <t>Chargers vs. Chiefs – Week 17</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/rams-seahawks-2027</t>
+          <t>https://www.sofistadium.com/events/detail/chargers-chiefs-2026</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Super Bowl LXI</t>
+          <t>Rams vs. Seahawks – Week 18</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/super-bowl-lxi</t>
+          <t>https://www.sofistadium.com/events/detail/rams-seahawks-2027</t>
         </is>
       </c>
     </row>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1585,12 +1585,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>02/14/2027</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Super Bowl LXI</t>
+          <t>Chargers vs. Chiefs – Week 17</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/super-bowl-lxi</t>
+          <t>https://www.sofistadium.com/events/detail/chargers-chiefs-2026</t>
         </is>
       </c>
     </row>
@@ -1627,24 +1627,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Chargers vs. Chiefs – Week 17</t>
+          <t>Rams vs. Seahawks – Week 18</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-chiefs-2026</t>
+          <t>https://www.sofistadium.com/events/detail/rams-seahawks-2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>02/14/2027</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Rams vs. Seahawks – Week 18</t>
+          <t>Super Bowl LXI</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/rams-seahawks-2027</t>
+          <t>https://www.sofistadium.com/events/detail/super-bowl-lxi</t>
         </is>
       </c>
     </row>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1585,12 +1585,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1612,12 +1612,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5336,14 +5336,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5376,62 +5376,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/02/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5744,14 +5693,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5784,11 +5733,1126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>05/30/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Society of Nuclear Medicine and Molecular Imaging Annual Meeting 2026</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/society-of-nuclear-medicine-and-molecular-imaging-annual-meeting-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FITTED x COD - LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/fitted-cod-los-angeles</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AWS Summit Los Angeles 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/aws-summit-los-angeles-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LA Card Show</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/la-card-show</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HorrorCon Los Angeles</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/horrorcon-los-angeles-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CoreTCG x One Piece Regionals</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/coretcg-one-piece-regionals</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tonight's Conversation: LIVE &amp; UNCUT Los Angeles</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/tonights-conversation-live-uncut-los-angeles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06/19/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SoCal Cup: The Showcase</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/socal-cup-the-showcase-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Anime Expo 2026</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/anime-expo-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Gothic Market Los Angeles 2026</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/gothic-market-los-angeles-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SPOCOM Los Angeles 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/spocom-los-angeles-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Los Angeles Summer International Open IBJJF Jiu-Jitsu Championship</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/los-angeles-summer-international-open-ibjjf-jiu-jitsu-championship</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Collect-A-Con Los Angeles</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/collect-a-con-los-angeles-august-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>08/03/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NALC 74th Biennial Convention</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/nalc-74th-biennial-convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>El Sembrador Ministries - Metanoia Los Angeles</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/el-sembrador-ministries-metanoia-los-angeles</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>08/13/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>KCON LA 2026</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/kcon-la-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>APWU Biennial Convention 2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/apwu-biennial-convention-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>08/22/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Smith Chason College Los Angeles Campus Graduation 2026</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/smith-chason-college-los-angeles-campus-graduation-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09/16/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ASLA 2026 Conference on Landscape Architecture</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/asla-2026-conference-on-landscape-architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Got Sole Los Angeles</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/got-sole-los-angeles</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>09/20/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>California Bridal &amp; Wedding Expo</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/california-bridal-wedding-expo-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>09/20/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Wekfest LA 2026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/wekfest-la-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09/23/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>National Black MBA Annual Conference &amp; Exposition</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/national-black-mba-association-conference-exposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Riftbound Regional Qualifier</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/riftbound-regional-qualifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>38th Annual SCANPH Conference</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/38th-annual-scanph-conference</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Net Zero Conference 2026</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/net-zero-conference-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SCG CON Los Angeles 2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/scg-con-los-angeles-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>American Academy of Otolaryngology: 2026 AAO OTO EXPO</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/american-academy-of-otolaryngology-2026-aao-oto-expo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10/30/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>L.A. Comic Con 2026</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/la-comic-con-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Build Expo 2026</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/build-expo-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12/12/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Spirit Royale Cheer | Marquee Championship Los Angeles</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/spirit-royale-cheer-marquee-los-angeles</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12/18/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Copa Toque Futsal Festival</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/copa-toque-festival-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12/19/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Collect-A-Con Los Angeles</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/collect-a-con-los-angeles-december-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>01/06/2027</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LA Art Show 2027</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/la-art-show-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>01/07/2027</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Modern Language Association Annual Convention 2027</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/modern-language-association-annual-convention-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>01/23/2027</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>The Fit Expo Los Angeles 2027</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/the-fit-expo-los-angeles-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>02/23/2027</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MakeUp + LUXE PACK in Los Angeles 2027</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/makeup-luxe-pack-in-los-angeles-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>04/01/2027</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Star Wars Celebration 2027</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/star-wars-celebration-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>04/15/2027</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ACP Internal Medicine Meeting 2027</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/acp-internal-medicine-meeting-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>05/01/2027</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>American Association of Thoracic Surgery Annual Meeting</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/aats-annual-mtg-2027</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -5336,14 +5336,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5376,11 +5376,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Past Events" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Past Events" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1720,14 +1720,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1760,930 +1760,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>01/13/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>01/16/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>01/17/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>01/20/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>01/21/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>01/24/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>01/25/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>01/28/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01/29/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MORAT</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>06/13/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3671?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260613</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>06/14/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3672?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260614</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>06/20/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>12:30 PM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>BIG3</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3898?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=big3_260620</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>JOJI: SOLARIS</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3506?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260711</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>07/12/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>JOJI: SOLARIS</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3513?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260712</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>07/17/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Forrest Frank</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>07/27/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4:30 PM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>WWE Monday Night RAW</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3937?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wwe_monday_night_raw_260727</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Grupo Frontera</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3520?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=grupo_frontera_260807</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>08/15/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Yeat</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3699?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=yeat_260815</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>08/21/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Ne-Yo &amp; Akon</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>J. Cole</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3492?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>J. Cole</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3498?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>World of Warcraft®: 20 Years of Music</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3683?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=world_of_warcraft_260910</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>09/18/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>8:30 PM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Maná</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>09/19/2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>8:30 PM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Maná</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>09/24/2026</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Kehlani</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/4033?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kehlani_260924</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>aespa LIVE TOUR – SYNK : COMPLæXITY – in Los Angeles</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3850?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=aespa_live_tour_261003</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TLC and Salt-N-Pepa</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3613?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=tlc_salt-n-pepa_261010</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>10/17/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Young Miko</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3707?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=young_miko_261017</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>10/24/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Pokémon Night Out</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3674?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=pokemon_night_out_261024</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>11/22/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Three Days Grace</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2694,14 +1775,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2734,1490 +1815,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>06/13/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06/17/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>06/19/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>06/20/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>06/24/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MADISON BEER – the locket tour</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/madison-beer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>06/26/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>06/27/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/aap-rocky/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>06/29/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ROSALÍA – LUX TOUR 2026</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rosalia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>07/01/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ROSALÍA – LUX TOUR 2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rosalia-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HILARY DUFF – the lucky me tour</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/hilary-duff/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HILARY DUFF – the lucky me tour</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>07/17/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>YOUNG THE GIANT – Victory Garden Tour</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/young-the-giant/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>07/18/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>EVANESCENCE</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/evanescence/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/motionless-in-white/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ive/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>08/11/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>08/12/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>08/13/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>08/14/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/melanie-martinez/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>08/21/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/omar-courtz/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/chicago-styx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>09/11/2026</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>09/12/2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SODA STEREO – ECOS TOUR</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/soda-stereo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>09/23/2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ROBYN – The Sexistential Tour</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/robyn/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>09/24/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ROBYN – The Sexistential Tour</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/robyn-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>09/25/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/lily-allen/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>09/26/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>BILLY STRINGS</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/billy-strings-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>09/30/2026</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>KLANGKUENSTLER – OUTWORLD – Klangkuenstler All Night Long</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/klangkuenstler/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/mumford-sons/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SOMBR – You Are The Reason Tour</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/sombr/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10/16/2026</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>JUANES</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/juanes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>10/20/2026</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/monsta-x/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10/22/2026</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>DOJA CAT – Tour Ma Vie World Tour</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/doja-cat/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>10/24/2026</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>GORILLAZ – The Mountain Tour</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gorillaz-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>DON OMAR – The Last King World Tour</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/don-omar/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>MON LAFERTE – Femme Fatale Tour</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/mon-laferte/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>11/12/2026</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>11/13/2026</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/slayer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>11/14/2026</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/slayer-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>11/15/2026</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rawayana/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>11/18/2026</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TEDDY SWIMS – The UGLY Tour</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/teddy-swims/</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>05/22/2027</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NIALL HORAN – Dinner Party Live On Tour</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/niall-horan/</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4228,14 +1830,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4268,174 +1870,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>07/17/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs LAFC</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-lafc</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07/22/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs St. Louis CITY SC</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-st-louis-city-sc</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>07/25/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Campeón de Campeones 2026</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/campeon-de-campeones-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs FC Dallas</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-fc-dallas</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>08/19/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs San Jose Earthquakes</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-jose-earthquakes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs New England Revolution</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-england-revolution</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5336,14 +2775,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5376,62 +2815,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/02/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5442,14 +2830,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5482,258 +2870,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>FIFA Fan Festival™ Los Angeles</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/fifa-fan-festival-los-angeles/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>America250 July 4 Concert</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/america250-july-4-concert/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>08/29/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>San Jose State vs USC</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/sanjosestate-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Fresno State vs USC</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/fresno-state-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>09/12/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Louisiana vs USC</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/louisiana-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>09/26/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Oregon vs USC</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/oregon-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Washington vs USC</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/washington-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>10/31/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ohio State vs USC</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/ohio-state-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>11/21/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Maryland vs USC</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/maryland-vs-usc-2026/</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Past Events" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Past Events" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1720,14 +1720,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1760,11 +1760,930 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01/17/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01/20/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01/24/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01/25/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MORAT</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3671?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260613</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>06/14/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3672?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260614</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BIG3</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3898?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=big3_260620</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3506?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260711</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3513?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260712</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Forrest Frank</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/27/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WWE Monday Night RAW</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3937?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wwe_monday_night_raw_260727</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Grupo Frontera</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3520?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=grupo_frontera_260807</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Yeat</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3699?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=yeat_260815</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ne-Yo &amp; Akon</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3492?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3498?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>World of Warcraft®: 20 Years of Music</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3683?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=world_of_warcraft_260910</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>09/18/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kehlani</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/4033?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kehlani_260924</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>aespa LIVE TOUR – SYNK : COMPLæXITY – in Los Angeles</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3850?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=aespa_live_tour_261003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TLC and Salt-N-Pepa</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3613?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=tlc_salt-n-pepa_261010</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Young Miko</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3707?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=young_miko_261017</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pokémon Night Out</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3674?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=pokemon_night_out_261024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11/22/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Three Days Grace</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1775,14 +2694,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1815,11 +2734,1490 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/17/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/19/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06/24/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MADISON BEER – the locket tour</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/madison-beer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06/26/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06/27/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/aap-rocky/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>06/29/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ROSALÍA – LUX TOUR 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rosalia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ROSALÍA – LUX TOUR 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rosalia-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HILARY DUFF – the lucky me tour</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/hilary-duff/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HILARY DUFF – the lucky me tour</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>YOUNG THE GIANT – Victory Garden Tour</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/young-the-giant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/18/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EVANESCENCE</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/evanescence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/31/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/motionless-in-white/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ive/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08/13/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/melanie-martinez/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/omar-courtz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/chicago-styx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09/11/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SODA STEREO – ECOS TOUR</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/soda-stereo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>09/23/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ROBYN – The Sexistential Tour</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/robyn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ROBYN – The Sexistential Tour</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/robyn-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/lily-allen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BILLY STRINGS</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/billy-strings-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>KLANGKUENSTLER – OUTWORLD – Klangkuenstler All Night Long</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/klangkuenstler/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mumford-sons/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SOMBR – You Are The Reason Tour</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/sombr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10/16/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JUANES</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/juanes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10/20/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/monsta-x/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10/22/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DOJA CAT – Tour Ma Vie World Tour</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/doja-cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GORILLAZ – The Mountain Tour</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/gorillaz-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DON OMAR – The Last King World Tour</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/don-omar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MON LAFERTE – Femme Fatale Tour</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mon-laferte/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>11/15/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rawayana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>11/18/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TEDDY SWIMS – The UGLY Tour</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/teddy-swims/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>05/22/2027</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NIALL HORAN – Dinner Party Live On Tour</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/niall-horan/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1830,14 +4228,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1870,11 +4268,174 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs LAFC</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-lafc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07/22/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-st-louis-city-sc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07/25/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Campeón de Campeones 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/campeon-de-campeones-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs FC Dallas</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-fc-dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08/19/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-jose-earthquakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs New England Revolution</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-england-revolution</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2775,14 +5336,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2815,11 +5376,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Alex Warren: Finding Family on the Road – With special guests Nat &amp; Alex Wolff</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/alexwarren060626</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2830,14 +5470,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2870,11 +5510,258 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FIFA Fan Festival™ Los Angeles</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/fifa-fan-festival-los-angeles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>America250 July 4 Concert</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/america250-july-4-concert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08/29/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Jose State vs USC</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/sanjosestate-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fresno State vs USC</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/fresno-state-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Louisiana vs USC</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/louisiana-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oregon vs USC</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/oregon-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Washington vs USC</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/washington-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ohio State vs USC</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/ohio-state-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11/21/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Maryland vs USC</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/maryland-vs-usc-2026/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1721,13 +1721,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1767,64 +1767,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>05/21/2026</t>
+          <t>05/25/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Romeo Santos &amp; Prince Royce</t>
+          <t>vs. Colorado Rockies</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/romeosantosprinceroyce052126</t>
+          <t>https://www.mlb.com/gameday/823948</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>05/20/2026</t>
+          <t>05/21/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00PM</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLORENCE + THE MACHINE</t>
+          <t>Romeo Santos &amp; Prince Royce</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/florence-the-machine/</t>
+          <t>https://www.cryptoarena.com/events/detail/romeosantosprinceroyce052126</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/20/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1856,24 +1856,24 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/florence-the-machine-2/</t>
+          <t>https://thekiaforum.com/event/florence-the-machine/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>05/18/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1883,83 +1883,83 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ATD 26 | Association for Talent Development Conference &amp; Expo</t>
+          <t>FLORENCE + THE MACHINE</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/atd-2026-association-for-talent-development-conference</t>
+          <t>https://thekiaforum.com/event/florence-the-machine-2/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>05/17/2026</t>
+          <t>05/18/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks vs Toronto Tempo</t>
+          <t>ATD 26 | Association for Talent Development Conference &amp; Expo</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/sparkstempo051726</t>
+          <t>https://www.laconventioncenter.com/events/detail/atd-2026-association-for-talent-development-conference</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/17/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DEMI LOVATO</t>
+          <t>Los Angeles Sparks vs Toronto Tempo</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/demi-lovato/</t>
+          <t>https://www.cryptoarena.com/events/detail/sparkstempo051726</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1979,29 +1979,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zipangu</t>
+          <t>DEMI LOVATO</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/578/zipangu</t>
+          <t>https://thekiaforum.com/event/demi-lovato/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2011,19 +2011,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LORDE</t>
+          <t>Zipangu</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lorde-3/</t>
+          <t>https://www.rosebowlstadium.com/events/details/578/zipangu</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2038,241 +2038,241 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks vs Toronto Tempo</t>
+          <t>LORDE</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/sparkstempo051526</t>
+          <t>https://thekiaforum.com/event/lorde-3/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>05/14/2026</t>
+          <t>05/15/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LORDE</t>
+          <t>Los Angeles Sparks vs Toronto Tempo</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lorde-2/</t>
+          <t>https://www.cryptoarena.com/events/detail/sparkstempo051526</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>05/13/2026</t>
+          <t>05/14/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks vs Indiana Fever</t>
+          <t>LORDE</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/sparksfever051326</t>
+          <t>https://thekiaforum.com/event/lorde-2/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>05/14/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Netflix is a Joke Presents: Nate Bargatze</t>
+          <t>vs. San Francisco Giants</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3431?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=nate_bargatze_260510</t>
+          <t>https://www.mlb.com/gameday/823950</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>05/13/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Los Angeles Sparks vs Indiana Fever</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/600/rose-bowl-flea-market</t>
+          <t>https://www.cryptoarena.com/events/detail/sparksfever051326</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>05/13/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks vs Las Vegas Aces</t>
+          <t>vs. San Francisco Giants</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/sparksaces051026</t>
+          <t>https://www.mlb.com/gameday/823952</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Netflix is a Joke Presents: Nate Bargatze</t>
+          <t>vs. San Francisco Giants</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3430?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=nate_bargatze_260509</t>
+          <t>https://www.mlb.com/gameday/823951</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Los Angeles Pokémon Regional Championships</t>
+          <t>vs. San Francisco Giants</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/los-angeles-pokemon-regional-championships</t>
+          <t>https://www.mlb.com/gameday/823953</t>
         </is>
       </c>
     </row>
@@ -2284,66 +2284,66 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Netflix is a Joke Presents: Kill Tony</t>
+          <t>Netflix is a Joke Presents: Nate Bargatze</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3435?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kill_tony_260507</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3431?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=nate_bargatze_260510</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Netflix is a Joke Presents: Katt Williams</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3382?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=katt_williams_260505</t>
+          <t>https://www.rosebowlstadium.com/events/details/600/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2353,29 +2353,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>98th Annual AAAE Conference &amp; Exposition</t>
+          <t>Los Angeles Sparks vs Las Vegas Aces</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/98th-annual-aaae-conference-exposition</t>
+          <t>https://www.cryptoarena.com/events/detail/sparksaces051026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2385,125 +2385,125 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Display Week 2026</t>
+          <t>vs. Atlanta Braves</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/society-for-information-display-week-2026</t>
+          <t>https://www.mlb.com/gameday/823954</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CHARLIE PUTH</t>
+          <t>Netflix is a Joke Presents: Nate Bargatze</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/charlie-puth/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3430?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=nate_bargatze_260509</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>04/27/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HelmsBriscoe - 2026 Annual Business Conference (ABC)</t>
+          <t>vs. Atlanta Braves</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/helmsbriscoe-2026-annual-business-conference-abc</t>
+          <t>https://www.mlb.com/gameday/823955</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>04/26/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Real Salt Lake</t>
+          <t>Los Angeles Pokémon Regional Championships</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-real-salt-lake</t>
+          <t>https://www.laconventioncenter.com/events/detail/los-angeles-pokemon-regional-championships</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2513,61 +2513,61 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>04/24/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>THIRD DAY</t>
+          <t>vs. Atlanta Braves</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/third-day/</t>
+          <t>https://www.mlb.com/gameday/823957</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>04/22/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>The NAMA Show 2026</t>
+          <t>Netflix is a Joke Presents: Kill Tony</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/the-nama-show-2026</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3435?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kill_tony_260507</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2577,29 +2577,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ELECTRIC CALLBOY</t>
+          <t>Netflix is a Joke Presents: Katt Williams</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/electric-callboy/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3382?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=katt_williams_260505</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2609,22 +2609,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>04/19/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Masters of Taste</t>
+          <t>98th Annual AAAE Conference &amp; Exposition</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/624/masters-of-taste</t>
+          <t>https://www.laconventioncenter.com/events/detail/98th-annual-aaae-conference-exposition</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>04/16/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2651,19 +2651,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SBMT World Congress 2026</t>
+          <t>Display Week 2026</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/sbmt-world-congress-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/society-for-information-display-week-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2683,243 +2683,243 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AOA of California Trade Show</t>
+          <t>CHARLIE PUTH</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/aoa-of-california-trade-show-2026</t>
+          <t>https://thekiaforum.com/event/charlie-puth/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>12:10 PM</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Golden State Warriors vs LA Clippers</t>
+          <t>vs. Miami Marlins</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2695?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260412</t>
+          <t>https://www.mlb.com/gameday/823958</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>vs. Miami Marlins</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/599/rose-bowl-flea-market</t>
+          <t>https://www.mlb.com/gameday/823956</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>04/27/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Utah Jazz vs Los Angeles Lakers</t>
+          <t>HelmsBriscoe - 2026 Annual Business Conference (ABC)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersjazz041226</t>
+          <t>https://www.laconventioncenter.com/events/detail/helmsbriscoe-2026-annual-business-conference-abc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/27/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>We Them One's Comedy Tour</t>
+          <t>vs. Miami Marlins</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3131?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wethemones_260411</t>
+          <t>https://www.mlb.com/gameday/823961</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/26/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Edmonton Oilers vs Los Angeles Kings</t>
+          <t>LA Galaxy vs Real Salt Lake</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsoilers041126</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-real-salt-lake</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/26/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Los Angeles Career Forum 2026</t>
+          <t>vs. Chicago Cubs</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/los-angeles-career-forum-2026</t>
+          <t>https://www.mlb.com/gameday/823959</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>4:15 PM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>REIK</t>
+          <t>vs. Chicago Cubs</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/reik/</t>
+          <t>https://www.mlb.com/gameday/823960</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2929,61 +2929,61 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>04/24/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Phoenix Suns vs Los Angeles Lakers</t>
+          <t>THIRD DAY</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerssuns041026</t>
+          <t>https://thekiaforum.com/event/third-day/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>04/24/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:15 PM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vancouver Canucks vs Los Angeles Kings</t>
+          <t>vs. Chicago Cubs</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingscanucks040926</t>
+          <t>https://www.mlb.com/gameday/823962</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2993,39 +2993,39 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>04/22/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder vs LA Clippers</t>
+          <t>The NAMA Show 2026</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2694?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260408</t>
+          <t>https://www.laconventioncenter.com/events/detail/the-nama-show-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3035,204 +3035,204 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026 AERA Annual Meeting</t>
+          <t>ELECTRIC CALLBOY</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/2026-aera-annual-meeting</t>
+          <t>https://thekiaforum.com/event/electric-callboy/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/19/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dallas Mavericks vs LA Clippers</t>
+          <t>Masters of Taste</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2672?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260407</t>
+          <t>https://www.rosebowlstadium.com/events/details/624/masters-of-taste</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/16/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
+          <t>SBMT World Congress 2026</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersthunder040726</t>
+          <t>https://www.laconventioncenter.com/events/detail/sbmt-world-congress-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>04/15/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nashville Predators vs Los Angeles Kings</t>
+          <t>AOA of California Trade Show</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingspreds040626</t>
+          <t>https://www.laconventioncenter.com/events/detail/aoa-of-california-trade-show-2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/15/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LANY</t>
+          <t>vs. New York Mets</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3066?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lany_260404</t>
+          <t>https://www.mlb.com/gameday/823963</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Minnesota United FC</t>
+          <t>vs. New York Mets</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-minnesota-united-fc</t>
+          <t>https://www.mlb.com/gameday/823965</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/13/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Toronto Maple Leafs vs Los Angeles Kings</t>
+          <t>vs. New York Mets</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsleafs040426</t>
+          <t>https://www.mlb.com/gameday/823964</t>
         </is>
       </c>
     </row>
@@ -3244,204 +3244,204 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Antonio Spurs vs LA Clippers</t>
+          <t>Golden State Warriors vs LA Clippers</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2671?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260402</t>
+          <t>https://intuitdome.com/events/event-schedule/2695?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260412</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nashville Predators vs Los Angeles Kings</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingspreds040226</t>
+          <t>https://www.rosebowlstadium.com/events/details/599/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L.A. Memorial Coliseum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>March for Babies</t>
+          <t>Utah Jazz vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/march-for-babies-2026/</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersjazz041226</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>St Louis Blues vs Los Angeles Kings</t>
+          <t>vs. Texas Rangers</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsblues040126</t>
+          <t>https://www.mlb.com/gameday/823966</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L.A. Memorial Coliseum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hope Fest LA</t>
+          <t>We Them One's Comedy Tour</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/hopefest-la-2026/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3131?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wethemones_260411</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers vs LA Clippers</t>
+          <t>Edmonton Oilers vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2693?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260331</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsoilers041126</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3451,204 +3451,204 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>JACKSON WANG</t>
+          <t>Los Angeles Career Forum 2026</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/jackson-wang/</t>
+          <t>https://www.laconventioncenter.com/events/detail/los-angeles-career-forum-2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers vs Los Angeles Lakers</t>
+          <t>vs. Texas Rangers</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerscavs033126</t>
+          <t>https://www.mlb.com/gameday/823967</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>03/30/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Washington Wizards vs Los Angeles Lakers</t>
+          <t>REIK</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerswizards033026</t>
+          <t>https://thekiaforum.com/event/reik/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>03/29/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Walk MS: Greater Los Angeles</t>
+          <t>Phoenix Suns vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/589/walk-ms:-greater-los-angeles</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerssuns041026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utah Mammoth vs Los Angeles Kings</t>
+          <t>vs. Texas Rangers</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsmammoth032826</t>
+          <t>https://www.mlb.com/gameday/823968</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Victory Gymnastics - XCEL State Championship</t>
+          <t>Vancouver Canucks vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/victory-gymnastics-xcel-state-championship</t>
+          <t>https://www.cryptoarena.com/events/detail/kingscanucks040926</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>03/27/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Brooklyn Nets vs Los Angeles Lakers</t>
+          <t>Oklahoma City Thunder vs LA Clippers</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersnets032726</t>
+          <t>https://intuitdome.com/events/event-schedule/2694?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260408</t>
         </is>
       </c>
     </row>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>03/27/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3675,108 +3675,108 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>American Pharmacists Association (APhA) Annual Meeting &amp; Exposition 2026</t>
+          <t>2026 AERA Annual Meeting</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/american-pharmacists-association</t>
+          <t>https://www.laconventioncenter.com/events/detail/2026-aera-annual-meeting</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BAD OMENS</t>
+          <t>Dallas Mavericks vs LA Clippers</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/bad-omens/</t>
+          <t>https://intuitdome.com/events/event-schedule/2672?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260407</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>03/25/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Toronto Raptors vs LA Clippers</t>
+          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2670?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260325</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersthunder040726</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>03/25/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HR Star Conference 2026</t>
+          <t>Nashville Predators vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/hr-star-conference-2026</t>
+          <t>https://www.cryptoarena.com/events/detail/kingspreds040626</t>
         </is>
       </c>
     </row>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>03/23/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3803,51 +3803,51 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks vs LA Clippers</t>
+          <t>LANY</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2668?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260323</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3066?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lany_260404</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>03/22/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>B2K &amp; BOW WOW</t>
+          <t>LA Galaxy vs Minnesota United FC</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/b2k-bow-wow/</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-minnesota-united-fc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3857,54 +3857,54 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7 PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gabriel "Fluffy" Iglesias &amp; Jo Koy</t>
+          <t>Toronto Maple Leafs vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/gabriel-fluffy-iglesias-jo-koy</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsleafs040426</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Breakthrough T1D, Walk Los Angeles</t>
+          <t>San Antonio Spurs vs LA Clippers</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/625/breakthrough-t1d-walk-los-angeles</t>
+          <t>https://intuitdome.com/events/event-schedule/2671?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260402</t>
         </is>
       </c>
     </row>
@@ -3916,667 +3916,667 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Buffalo Sabres vs Los Angeles Kings</t>
+          <t>Nashville Predators vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingssabres032126</t>
+          <t>https://www.cryptoarena.com/events/detail/kingspreds040226</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>L.A. Memorial Coliseum</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Peso Pluma</t>
+          <t>March for Babies</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3401?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=peso_pluma_260320</t>
+          <t>https://www.lacoliseum.com/events/march-for-babies-2026/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CONAN GRAY</t>
+          <t>St Louis Blues vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/conan-gray/</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsblues040126</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>L.A. Memorial Coliseum</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>03/19/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Philadelphia Flyers vs Los Angeles Kings</t>
+          <t>Hope Fest LA</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsflyers031926</t>
+          <t>https://www.lacoliseum.com/events/hopefest-la-2026/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>03/16/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>5:20 PM</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>San Antonio Spurs vs LA Clippers</t>
+          <t>vs. Cleveland Guardians</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2692?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260316</t>
+          <t>https://www.mlb.com/gameday/823970</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>03/15/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AEW presents REVOLUTION</t>
+          <t>Portland Trail Blazers vs LA Clippers</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/aew031526</t>
+          <t>https://intuitdome.com/events/event-schedule/2693?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260331</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sacramento Kings vs LA Clippers</t>
+          <t>JACKSON WANG</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2691?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260314</t>
+          <t>https://thekiaforum.com/event/jackson-wang/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6:30 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Sporting KC</t>
+          <t>Cleveland Cavaliers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-kc</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerscavs033126</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Denver Nuggets vs Los Angeles Lakers</t>
+          <t>vs. Cleveland Guardians</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersnuggets031426</t>
+          <t>https://www.mlb.com/gameday/823969</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>03/13/2026</t>
+          <t>03/30/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Chicago Bulls vs LA Clippers</t>
+          <t>Washington Wizards vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2666?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260313</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerswizards033026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>03/13/2026</t>
+          <t>03/30/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>vs. Cleveland Guardians</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/miguel/</t>
+          <t>https://www.mlb.com/gameday/823972</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>03/12/2026</t>
+          <t>03/29/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chicago Bulls vs Los Angeles Lakers</t>
+          <t>Walk MS: Greater Los Angeles</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersbulls031226</t>
+          <t>https://www.rosebowlstadium.com/events/details/589/walk-ms:-greater-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>03/11/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves vs LA Clippers</t>
+          <t>Utah Mammoth vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2690?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260311</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsmammoth032826</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves vs Los Angeles Lakers</t>
+          <t>Victory Gymnastics - XCEL State Championship</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerswolves031026</t>
+          <t>https://www.laconventioncenter.com/events/detail/victory-gymnastics-xcel-state-championship</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>New York Knicks vs LA Clippers</t>
+          <t>vs. Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2665?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260309</t>
+          <t>https://www.mlb.com/gameday/823973</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>03/27/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Brooklyn Nets vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/598/rose-bowl-flea-market</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersnets032726</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>03/27/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>New York Knicks vs Los Angeles Lakers</t>
+          <t>American Pharmacists Association (APhA) Annual Meeting &amp; Exposition 2026</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersknicks030826</t>
+          <t>https://www.laconventioncenter.com/events/detail/american-pharmacists-association</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>03/27/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>California Bridal &amp; Wedding Expo</t>
+          <t>vs. Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/california-bridal-wedding-expo-14</t>
+          <t>https://www.mlb.com/gameday/823971</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sip &amp; Stroll at SoFi Stadium</t>
+          <t>BAD OMENS</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/sofi-tour-sip-wine-stroll-march-29</t>
+          <t>https://thekiaforum.com/event/bad-omens/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>EXCISION</t>
+          <t>vs. Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/excision/</t>
+          <t>https://www.mlb.com/gameday/823974</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/25/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Montreal Canadiens vs Los Angeles Kings</t>
+          <t>Toronto Raptors vs LA Clippers</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingscanadiens030726</t>
+          <t>https://intuitdome.com/events/event-schedule/2670?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260325</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/25/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4603,275 +4603,275 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Black Men in White Coats Youth Summit 2026</t>
+          <t>HR Star Conference 2026</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/black-men-in-white-coats-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/hr-star-conference-2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>03/23/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>EXCISION</t>
+          <t>Milwaukee Bucks vs LA Clippers</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/excision-2/</t>
+          <t>https://intuitdome.com/events/event-schedule/2668?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260323</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>03/22/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Indiana Pacers vs Los Angeles Lakers</t>
+          <t>B2K &amp; BOW WOW</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerspacer030626</t>
+          <t>https://thekiaforum.com/event/b2k-bow-wow/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7 PM</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Victory Gymnastics - Victory Classic</t>
+          <t>Gabriel "Fluffy" Iglesias &amp; Jo Koy</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/victory-gymnastics-victory-classic</t>
+          <t>https://www.sofistadium.com/events/detail/gabriel-fluffy-iglesias-jo-koy</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York Islanders vs Los Angeles Kings</t>
+          <t>Breakthrough T1D, Walk Los Angeles</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsislanders030526</t>
+          <t>https://www.rosebowlstadium.com/events/details/625/breakthrough-t1d-walk-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Indiana Pacers vs LA Clippers</t>
+          <t>Buffalo Sabres vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2664?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260304</t>
+          <t>https://www.cryptoarena.com/events/detail/kingssabres032126</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MakeUp + Luxe Pack in Los Angeles 2026</t>
+          <t>Peso Pluma</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/makeup-in-los-angeles-2026</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3401?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=peso_pluma_260320</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans vs Los Angeles Lakers</t>
+          <t>CONAN GRAY</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerspelicans030326</t>
+          <t>https://thekiaforum.com/event/conan-gray/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>03/19/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Catersource &amp; The Special Event Expo</t>
+          <t>Philadelphia Flyers vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/catersource-the-special-event-expo</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsflyers031926</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4881,29 +4881,29 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>03/16/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colorado Avalanche vs Los Angeles Kings</t>
+          <t>San Antonio Spurs vs LA Clippers</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsavs030226</t>
+          <t>https://intuitdome.com/events/event-schedule/2692?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260316</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4913,93 +4913,93 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>03/15/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans vs LA Clippers</t>
+          <t>AEW presents REVOLUTION</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2689?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260301</t>
+          <t>https://www.cryptoarena.com/events/detail/aew031526</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>The Michael J. Fox Foundation’s Los Angeles Run/Walk</t>
+          <t>Sacramento Kings vs LA Clippers</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/623/the-michael-j.-fox-foundation's-los-angeles-runwalk</t>
+          <t>https://intuitdome.com/events/event-schedule/2691?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260314</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>6:30 PM</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sacramento Kings vs Los Angeles Lakers</t>
+          <t>LA Galaxy vs Sporting KC</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerskings030126</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-kc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5009,39 +5009,39 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ricardo Arjona</t>
+          <t>Denver Nuggets vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2819?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ricardo_arjona_260228</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersnuggets031426</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/13/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5051,204 +5051,204 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Charlotte FC</t>
+          <t>Chicago Bulls vs LA Clippers</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-charlotte-fc-1</t>
+          <t>https://intuitdome.com/events/event-schedule/2666?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260313</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/13/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Calgary Flames vs Los Angeles Kings</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsflames022826</t>
+          <t>https://thekiaforum.com/event/miguel/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/12/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>El Sembrador Ministries - Metanoia de Mujeres</t>
+          <t>Chicago Bulls vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/el-sembrador-ministries-metanoia-de-mujeres-2</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersbulls031226</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Spotlight Card Show</t>
+          <t>Minnesota Timberwolves vs LA Clippers</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/spotlight-card-show</t>
+          <t>https://intuitdome.com/events/event-schedule/2690?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260311</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00PM</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Import Expo x Cali Creaming</t>
+          <t>Minnesota Timberwolves vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/import-expo-x-cali-creaming</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerswolves031026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>02/27/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>BRANDI CARLILE</t>
+          <t>New York Knicks vs LA Clippers</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/brandi-carlile/</t>
+          <t>https://intuitdome.com/events/event-schedule/2665?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260309</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves vs LA Clippers</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2663?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260226</t>
+          <t>https://www.rosebowlstadium.com/events/details/598/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
@@ -5260,172 +5260,172 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Edmonton Oilers vs Los Angeles Kings</t>
+          <t>New York Knicks vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsoilers022626</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersknicks030826</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Sporting San Miguelito</t>
+          <t>California Bridal &amp; Wedding Expo</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-san-miguelito</t>
+          <t>https://www.laconventioncenter.com/events/detail/california-bridal-wedding-expo-14</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>6 PM</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vegas Golden Knights vs Los Angeles Kings</t>
+          <t>Sip &amp; Stroll at SoFi Stadium</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsknights022526</t>
+          <t>https://www.sofistadium.com/events/detail/sofi-tour-sip-wine-stroll-march-29</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>02/24/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Orlando Magic vs Los Angeles Lakers</t>
+          <t>EXCISION</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersmagic022426</t>
+          <t>https://thekiaforum.com/event/excision/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>02/23/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GHOST: Skeletour World Tour 2026</t>
+          <t>Montreal Canadiens vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2964?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ghost_260223</t>
+          <t>https://www.cryptoarena.com/events/detail/kingscanadiens030726</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>02/23/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5435,317 +5435,317 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>Black Men in White Coats Youth Summit 2026</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-8/</t>
+          <t>https://www.laconventioncenter.com/events/detail/black-men-in-white-coats-2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Orlando Magic vs LA Clippers</t>
+          <t>EXCISION</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2688?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260222</t>
+          <t>https://thekiaforum.com/event/excision-2/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>Indiana Pacers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-7/</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerspacer030626</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LA Galaxy vs New York City FC</t>
+          <t>Victory Gymnastics - Victory Classic</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-york-city-fc</t>
+          <t>https://www.laconventioncenter.com/events/detail/victory-gymnastics-victory-classic</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>New York Islanders vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/585/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsislanders030526</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Indiana Pacers vs LA Clippers</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/588/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://intuitdome.com/events/event-schedule/2664?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260304</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Boston Celtics vs Los Angeles Lakers</t>
+          <t>MakeUp + Luxe Pack in Los Angeles 2026</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersceltics022226</t>
+          <t>https://www.laconventioncenter.com/events/detail/makeup-in-los-angeles-2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ViVE 2026</t>
+          <t>New Orleans Pelicans vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/vive-2026</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerspelicans030326</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>8 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Los Bukis</t>
+          <t>Catersource &amp; The Special Event Expo</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/los-bukis-february-21-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/catersource-the-special-event-expo</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Los Tigres del Norte</t>
+          <t>Colorado Avalanche vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2912?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=los_tigres_del_norte_260221</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsavs030226</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>New Orleans Pelicans vs LA Clippers</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/584/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://intuitdome.com/events/event-schedule/2689?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260301</t>
         </is>
       </c>
     </row>
@@ -5772,59 +5772,59 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>The Michael J. Fox Foundation’s Los Angeles Run/Walk</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/587/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/623/the-michael-j.-fox-foundation's-los-angeles-runwalk</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>8 PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Los Bukis</t>
+          <t>Sacramento Kings vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/los-bukis-2026</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerskings030126</t>
         </is>
       </c>
     </row>
@@ -5836,187 +5836,187 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Harlem Globetrotters</t>
+          <t>Ricardo Arjona</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2904</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2819?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ricardo_arjona_260228</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SABATON</t>
+          <t>LA Galaxy vs Charlotte FC</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/sabaton/</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-charlotte-fc-1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Calgary Flames vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/583/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsflames022826</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>El Sembrador Ministries - Metanoia de Mujeres</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/586/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.laconventioncenter.com/events/detail/el-sembrador-ministries-metanoia-de-mujeres-2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Los Angeles Clippers vs Los Angeles Lakers</t>
+          <t>Spotlight Card Show</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersclippers022026</t>
+          <t>https://www.laconventioncenter.com/events/detail/spotlight-card-show</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Denver Nuggets vs LA Clippers</t>
+          <t>Import Expo x Cali Creaming</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2687?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260219</t>
+          <t>https://www.laconventioncenter.com/events/detail/import-expo-x-cali-creaming</t>
         </is>
       </c>
     </row>
@@ -6028,12 +6028,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/27/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6043,268 +6043,268 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>BRANDI CARLILE</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-5/</t>
+          <t>https://thekiaforum.com/event/brandi-carlile/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>02/18/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>Minnesota Timberwolves vs LA Clippers</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-6/</t>
+          <t>https://intuitdome.com/events/event-schedule/2663?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260226</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CARDI B</t>
+          <t>Edmonton Oilers vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/cardi-b-2/</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsoilers022626</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>75th NBA All-Star Game</t>
+          <t>LA Galaxy vs Sporting San Miguelito</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3002?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_game_260215</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-san-miguelito</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CARDI B</t>
+          <t>Vegas Golden Knights vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/cardi-b/</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsknights022526</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/24/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>All-Star Saturday</t>
+          <t>Orlando Magic vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3003?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_saturday_260214</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersmagic022426</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/23/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>DJ CASSIDY'S PASS THE MIC LIVE!</t>
+          <t>GHOST: Skeletour World Tour 2026</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/dj-cassidys-pass-the-mic-live/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2964?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ghost_260223</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>02/23/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Castrol Rising Stars</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3004?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=castrol_rising_stars_260213</t>
+          <t>https://thekiaforum.com/event/lady-gaga-8/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HBCU CLASSIC PRESENTED BY AT&amp;T</t>
+          <t>Orlando Magic vs LA Clippers</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/hbcu-classic-presented-by-att/</t>
+          <t>https://intuitdome.com/events/event-schedule/2688?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260222</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6331,243 +6331,243 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RUFFLES CELEBRITY GAME</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ruffles-celebrity-game/</t>
+          <t>https://thekiaforum.com/event/lady-gaga-7/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Banda MS de Sergio Lizarraga</t>
+          <t>LA Galaxy vs New York City FC</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/bandams021326</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-york-city-fc</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>NBA ALL-STAR PITCH COMPETITION</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/nba-all-star-pitch-competition/</t>
+          <t>https://www.rosebowlstadium.com/events/details/585/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Dallas Mavericks vs Los Angeles Lakers</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersmavs021226</t>
+          <t>https://www.rosebowlstadium.com/events/details/588/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>NBA Crossover: The Ultimate Fan Experience</t>
+          <t>Boston Celtics vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/nba-crossover-ultimate-fan-experience</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersceltics022226</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>San Antonio Spurs vs Los Angeles Lakers</t>
+          <t>ViVE 2026</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersspurs021026</t>
+          <t>https://www.laconventioncenter.com/events/detail/vive-2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8 PM</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
+          <t>Los Bukis</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersthuner020926</t>
+          <t>https://www.sofistadium.com/events/detail/los-bukis-february-21-2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Los Tigres del Norte</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/597/rose-bowl-flea-market</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2912?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=los_tigres_del_norte_260221</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6577,295 +6577,295 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Golden State Warriors vs Los Angeles Lakers</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerswarriors020726</t>
+          <t>https://www.rosebowlstadium.com/events/details/584/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers vs Los Angeles Lakers</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakers76ers020526</t>
+          <t>https://www.rosebowlstadium.com/events/details/587/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>8 PM</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers vs LA Clippers</t>
+          <t>Los Bukis</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2662?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260204</t>
+          <t>https://www.sofistadium.com/events/detail/los-bukis-2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Seattle Kraken vs Los Angeles Kings</t>
+          <t>Harlem Globetrotters</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingskraken020426</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2904</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers vs LA Clippers</t>
+          <t>SABATON</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2686?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260202</t>
+          <t>https://thekiaforum.com/event/sabaton/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>L.A. Memorial Coliseum</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>LAFC vs Inter Miami CF</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/lafc-vs-intermiami-2026/</t>
+          <t>https://www.rosebowlstadium.com/events/details/583/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>L.A. Memorial Coliseum</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Night of Hope</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/night-of-hope/</t>
+          <t>https://www.rosebowlstadium.com/events/details/586/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>NEW EDITION</t>
+          <t>Los Angeles Clippers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/new-edition/</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersclippers022026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>IBJJF Jiu Jitsu Championship</t>
+          <t>Denver Nuggets vs LA Clippers</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/ibjjf-jiu-jitsu-championship</t>
+          <t>https://intuitdome.com/events/event-schedule/2687?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260219</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6875,19 +6875,19 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Grand Archive Phantom Monarch Regional Championships</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/grand-archive-phantom-monarch-regional-championships</t>
+          <t>https://thekiaforum.com/event/lady-gaga-5/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/18/2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -6907,42 +6907,874 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Modern Language Association Annual Convention 2027</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/modern-language-association-annual-convention-2027</t>
+          <t>https://thekiaforum.com/event/lady-gaga-6/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>Kia Forum</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>CARDI B</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/cardi-b-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>02/15/2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>75th NBA All-Star Game</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3002?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_game_260215</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Kia Forum</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>02/15/2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>CARDI B</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/cardi-b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>02/14/2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>All-Star Saturday</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3003?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_saturday_260214</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Kia Forum</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>02/14/2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>DJ CASSIDY'S PASS THE MIC LIVE!</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/dj-cassidys-pass-the-mic-live/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>02/13/2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Castrol Rising Stars</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3004?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=castrol_rising_stars_260213</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Kia Forum</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>02/13/2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>HBCU CLASSIC PRESENTED BY AT&amp;T</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/hbcu-classic-presented-by-att/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Kia Forum</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>02/13/2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>RUFFLES CELEBRITY GAME</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ruffles-celebrity-game/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Crypto.com Arena</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>02/13/2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Banda MS de Sergio Lizarraga</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/bandams021326</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Kia Forum</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>NBA ALL-STAR PITCH COMPETITION</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/nba-all-star-pitch-competition/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Crypto.com Arena</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>7:00PM</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks vs Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/lakersmavs021226</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>NBA Crossover: The Ultimate Fan Experience</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/nba-crossover-ultimate-fan-experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Crypto.com Arena</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>7:30PM</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs vs Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/lakersspurs021026</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Crypto.com Arena</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>7:00PM</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/lakersthuner020926</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Rose Bowl Stadium</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>ROSE BOWL FLEA MARKET</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/597/rose-bowl-flea-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Crypto.com Arena</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>5:30PM</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Golden State Warriors vs Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/lakerswarriors020726</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Crypto.com Arena</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>7:00PM</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers vs Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/lakers76ers020526</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers vs LA Clippers</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/event-schedule/2662?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260204</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Crypto.com Arena</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>7:00PM</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Seattle Kraken vs Los Angeles Kings</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/kingskraken020426</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers vs LA Clippers</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/event-schedule/2686?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260202</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>L.A. Memorial Coliseum</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>LAFC vs Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/lafc-vs-intermiami-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>L.A. Memorial Coliseum</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Night of Hope</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/night-of-hope/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Kia Forum</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>01/31/2026</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>NEW EDITION</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/new-edition/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>LA Convention Center</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>01/31/2026</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>IBJJF Jiu Jitsu Championship</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/ibjjf-jiu-jitsu-championship</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>LA Convention Center</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>01/31/2026</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Grand Archive Phantom Monarch Regional Championships</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/grand-archive-phantom-monarch-regional-championships</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>LA Convention Center</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Modern Language Association Annual Convention 2027</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/modern-language-association-annual-convention-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>LA Convention Center</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>TBA</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E189" t="inlineStr">
         <is>
           <t>LA Art Show 2027</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>https://www.laconventioncenter.com/events/detail/la-art-show-2027</t>
         </is>
@@ -7112,6 +7944,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12345,7 +13203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12385,39 +13243,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>vs. Arizona Diamondbacks</t>
+          <t>vs. Colorado Rockies</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823974</t>
+          <t>https://www.mlb.com/gameday/823949</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>03/27/2026</t>
+          <t>05/27/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -12427,51 +13285,51 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>vs. Arizona Diamondbacks</t>
+          <t>vs. Colorado Rockies</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823971</t>
+          <t>https://www.mlb.com/gameday/823947</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>05/29/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>7:15 PM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>vs. Arizona Diamondbacks</t>
+          <t>vs. Philadelphia Phillies</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823973</t>
+          <t>https://www.mlb.com/gameday/823946</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03/30/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12481,78 +13339,78 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>vs. Cleveland Guardians</t>
+          <t>vs. Philadelphia Phillies</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823972</t>
+          <t>https://www.mlb.com/gameday/823945</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>05/31/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>vs. Cleveland Guardians</t>
+          <t>vs. Philadelphia Phillies</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823969</t>
+          <t>https://www.mlb.com/gameday/823944</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5:20 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>vs. Cleveland Guardians</t>
+          <t>vs. Los Angeles Angels</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823970</t>
+          <t>https://www.mlb.com/gameday/823943</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -12562,78 +13420,78 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>vs. Texas Rangers</t>
+          <t>vs. Los Angeles Angels</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823968</t>
+          <t>https://www.mlb.com/gameday/823942</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>vs. Texas Rangers</t>
+          <t>vs. Los Angeles Angels</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823967</t>
+          <t>https://www.mlb.com/gameday/823941</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>06/15/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>vs. Texas Rangers</t>
+          <t>vs. Tampa Bay Rays</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823966</t>
+          <t>https://www.mlb.com/gameday/823938</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04/13/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12643,51 +13501,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>vs. New York Mets</t>
+          <t>vs. Tampa Bay Rays</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823964</t>
+          <t>https://www.mlb.com/gameday/823939</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>06/17/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>12:10 PM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>vs. New York Mets</t>
+          <t>vs. Tampa Bay Rays</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823965</t>
+          <t>https://www.mlb.com/gameday/823940</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -12697,105 +13555,105 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>vs. New York Mets</t>
+          <t>vs. Baltimore Orioles</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823963</t>
+          <t>https://www.mlb.com/gameday/823936</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04/24/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7:15 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>vs. Chicago Cubs</t>
+          <t>vs. Baltimore Orioles</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823962</t>
+          <t>https://www.mlb.com/gameday/823937</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>06/21/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4:15 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>vs. Chicago Cubs</t>
+          <t>vs. Baltimore Orioles</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823960</t>
+          <t>https://www.mlb.com/gameday/823934</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>04/26/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>vs. Chicago Cubs</t>
+          <t>vs. San Diego Padres</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823959</t>
+          <t>https://www.mlb.com/gameday/823935</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04/27/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12805,24 +13663,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>vs. Miami Marlins</t>
+          <t>vs. San Diego Padres</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823961</t>
+          <t>https://www.mlb.com/gameday/823933</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12832,51 +13690,51 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>vs. Miami Marlins</t>
+          <t>vs. San Diego Padres</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823956</t>
+          <t>https://www.mlb.com/gameday/823932</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12:10 PM</t>
+          <t>4:20 PM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>vs. Miami Marlins</t>
+          <t>vs. San Diego Padres</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823958</t>
+          <t>https://www.mlb.com/gameday/823931</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12886,78 +13744,78 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>vs. Atlanta Braves</t>
+          <t>vs. Colorado Rockies</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823957</t>
+          <t>https://www.mlb.com/gameday/823930</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>vs. Atlanta Braves</t>
+          <t>vs. Colorado Rockies</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823955</t>
+          <t>https://www.mlb.com/gameday/823929</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>vs. Atlanta Braves</t>
+          <t>vs. Colorado Rockies</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823954</t>
+          <t>https://www.mlb.com/gameday/823928</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12967,78 +13825,78 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>vs. San Francisco Giants</t>
+          <t>vs. Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823953</t>
+          <t>https://www.mlb.com/gameday/823927</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>vs. San Francisco Giants</t>
+          <t>vs. Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823951</t>
+          <t>https://www.mlb.com/gameday/823926</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>05/13/2026</t>
+          <t>07/12/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>vs. San Francisco Giants</t>
+          <t>vs. Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823952</t>
+          <t>https://www.mlb.com/gameday/823925</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>05/14/2026</t>
+          <t>07/28/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -13048,51 +13906,51 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>vs. San Francisco Giants</t>
+          <t>vs. Seattle Mariners</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823950</t>
+          <t>https://www.mlb.com/gameday/823923</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>05/25/2026</t>
+          <t>07/29/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>vs. Colorado Rockies</t>
+          <t>vs. Seattle Mariners</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823948</t>
+          <t>https://www.mlb.com/gameday/823924</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>07/30/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -13102,24 +13960,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>vs. Colorado Rockies</t>
+          <t>vs. Seattle Mariners</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823949</t>
+          <t>https://www.mlb.com/gameday/823921</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>05/27/2026</t>
+          <t>07/31/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -13129,105 +13987,105 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>vs. Colorado Rockies</t>
+          <t>vs. Boston Red Sox</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823947</t>
+          <t>https://www.mlb.com/gameday/823922</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>05/29/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7:15 PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>vs. Philadelphia Phillies</t>
+          <t>vs. Boston Red Sox</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823946</t>
+          <t>https://www.mlb.com/gameday/823920</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>08/02/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>4:20 PM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>vs. Philadelphia Phillies</t>
+          <t>vs. Boston Red Sox</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823945</t>
+          <t>https://www.mlb.com/gameday/823919</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>05/31/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>vs. Philadelphia Phillies</t>
+          <t>vs. Kansas City Royals</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823944</t>
+          <t>https://www.mlb.com/gameday/823918</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/11/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -13237,24 +14095,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>vs. Los Angeles Angels</t>
+          <t>vs. Kansas City Royals</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823943</t>
+          <t>https://www.mlb.com/gameday/823917</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>08/12/2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -13264,51 +14122,51 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>vs. Los Angeles Angels</t>
+          <t>vs. Kansas City Royals</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823942</t>
+          <t>https://www.mlb.com/gameday/823916</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>08/13/2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>vs. Los Angeles Angels</t>
+          <t>vs. Milwaukee Brewers</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823941</t>
+          <t>https://www.mlb.com/gameday/823915</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>06/15/2026</t>
+          <t>08/14/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -13318,66 +14176,66 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>vs. Tampa Bay Rays</t>
+          <t>vs. Milwaukee Brewers</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823938</t>
+          <t>https://www.mlb.com/gameday/823913</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>08/15/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>4:15 PM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>vs. Tampa Bay Rays</t>
+          <t>vs. Milwaukee Brewers</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823939</t>
+          <t>https://www.mlb.com/gameday/823914</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>06/17/2026</t>
+          <t>08/16/2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12:10 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>vs. Tampa Bay Rays</t>
+          <t>vs. Milwaukee Brewers</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823940</t>
+          <t>https://www.mlb.com/gameday/823912</t>
         </is>
       </c>
     </row>
@@ -13389,7 +14247,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>08/21/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -13399,12 +14257,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>vs. Baltimore Orioles</t>
+          <t>vs. Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823936</t>
+          <t>https://www.mlb.com/gameday/823911</t>
         </is>
       </c>
     </row>
@@ -13416,22 +14274,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>08/22/2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>vs. Baltimore Orioles</t>
+          <t>vs. Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823937</t>
+          <t>https://www.mlb.com/gameday/823910</t>
         </is>
       </c>
     </row>
@@ -13443,7 +14301,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>06/21/2026</t>
+          <t>08/23/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -13453,24 +14311,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>vs. Baltimore Orioles</t>
+          <t>vs. Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823934</t>
+          <t>https://www.mlb.com/gameday/823909</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -13480,24 +14338,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>vs. San Diego Padres</t>
+          <t>vs. St. Louis Cardinals</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823935</t>
+          <t>https://www.mlb.com/gameday/823908</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13507,24 +14365,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>vs. San Diego Padres</t>
+          <t>vs. St. Louis Cardinals</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823933</t>
+          <t>https://www.mlb.com/gameday/823906</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13534,78 +14392,78 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>vs. San Diego Padres</t>
+          <t>vs. St. Louis Cardinals</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823932</t>
+          <t>https://www.mlb.com/gameday/823907</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4:20 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>vs. San Diego Padres</t>
+          <t>vs. Washington Nationals</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823931</t>
+          <t>https://www.mlb.com/gameday/823905</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>vs. Colorado Rockies</t>
+          <t>vs. Washington Nationals</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823930</t>
+          <t>https://www.mlb.com/gameday/823904</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13615,51 +14473,51 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>vs. Colorado Rockies</t>
+          <t>vs. Washington Nationals</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823929</t>
+          <t>https://www.mlb.com/gameday/823903</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>vs. Colorado Rockies</t>
+          <t>vs. Cincinnati Reds</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823928</t>
+          <t>https://www.mlb.com/gameday/823902</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -13669,132 +14527,132 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>vs. Arizona Diamondbacks</t>
+          <t>vs. Cincinnati Reds</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823927</t>
+          <t>https://www.mlb.com/gameday/823901</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>vs. Arizona Diamondbacks</t>
+          <t>vs. Cincinnati Reds</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823926</t>
+          <t>https://www.mlb.com/gameday/823900</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>vs. Arizona Diamondbacks</t>
+          <t>vs. San Francisco Giants</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823925</t>
+          <t>https://www.mlb.com/gameday/823898</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>07/28/2026</t>
+          <t>09/19/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>vs. Seattle Mariners</t>
+          <t>vs. San Francisco Giants</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823923</t>
+          <t>https://www.mlb.com/gameday/823899</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>07/29/2026</t>
+          <t>09/20/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>vs. Seattle Mariners</t>
+          <t>vs. San Francisco Giants</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823924</t>
+          <t>https://www.mlb.com/gameday/823896</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>07/30/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -13804,24 +14662,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>vs. Seattle Mariners</t>
+          <t>vs. San Diego Padres</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823921</t>
+          <t>https://www.mlb.com/gameday/823897</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -13831,739 +14689,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>vs. Boston Red Sox</t>
+          <t>vs. San Diego Padres</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823922</t>
+          <t>https://www.mlb.com/gameday/823894</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>vs. Boston Red Sox</t>
+          <t>vs. San Diego Padres</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823920</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>08/02/2026</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>4:20 PM</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>vs. Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823919</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>vs. Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823918</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>08/11/2026</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>vs. Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823917</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>08/12/2026</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>vs. Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823916</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>08/13/2026</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823915</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>08/14/2026</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823913</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>08/15/2026</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>4:15 PM</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823914</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>08/16/2026</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823912</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>08/21/2026</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>vs. Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823911</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>08/22/2026</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>vs. Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823910</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>08/23/2026</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>vs. Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823909</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>vs. St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823908</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>09/02/2026</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>vs. St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823906</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>vs. St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823907</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>vs. Washington Nationals</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823905</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>vs. Washington Nationals</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823904</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>vs. Washington Nationals</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823903</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>vs. Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823902</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>09/08/2026</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>vs. Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823901</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>vs. Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823900</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>09/18/2026</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>vs. San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823898</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>09/19/2026</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>vs. San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823899</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>09/20/2026</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>vs. San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823896</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>09/22/2026</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823897</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>09/23/2026</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823894</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>09/24/2026</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>https://www.mlb.com/gameday/823895</t>
         </is>
@@ -14626,32 +14782,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -16,7 +16,8 @@
     <sheet name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Dodger Stadium" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Past Events" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Hollywood Bowl" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Past Events" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1721,6 +1722,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>No events found</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1722,14 +1722,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1762,11 +1762,2834 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>05/30/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pitbull – Lil Jon</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4278/2026-05-30/pitbull</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The Human League – Soft Cell, Alison Moyet</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4283/2026-06-04/the-human-league</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>37th Mariachi USA with Fireworks</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4274/2026-06-06/37th-mariachi-usa-with-fireworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Paul Simon</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4359/2026-06-07/paul-simon</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rod Stewart – Richard Marx</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4258/2026-06-10/rod-stewart</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Blue Note Jazz Festival – Day One: Saturday</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4273/2026-06-13/blue-note-jazz-festival</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06/14/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Blue Note Jazz Festival – Day Two: Sunday</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4291/2026-06-14/blue-note-jazz-festival</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06/19/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chance the Rapper – A Juneteenth Celebration</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4292/2026-06-19/chance-the-rapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Opening Night at the Bowl: The Best of Broadway</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4247/2026-06-20/opening-night-at-the-bowl-the-best-of-broadway</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06/21/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Reggae Night XXIV – Ziggy Marley, Burning Spear, Zuri Marley, KCRW Festival</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4293/2026-06-21/reggae-night-xxiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>06/24/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>The Tabernacle Choir at Temple Square: Songs of Hope Benefit Concert</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4838/2026-06-24/the-tabernacle-choir-at-temple-square-songs-of-hope-benefit-concert</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06/25/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>The Tabernacle Choir at Temple Square: Songs of Hope Benefit Concert</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4839/2026-06-25/the-tabernacle-choir-at-temple-square-songs-of-hope-benefit-concert</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>06/27/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A Roots Picnic Experience – A Great Night in Hip-Hop</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4248/2026-06-27/a-roots-picnic-experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>July Fourth Fireworks Spectacular with The Beach Boys – with Special Guest John Stamos</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4249/2026-07-02/july-fourth-fireworks-spectacular-with-the-beach-boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>July Fourth Fireworks Spectacular with The Beach Boys – with Special Guest John Stamos</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4250/2026-07-03/july-fourth-fireworks-spectacular-with-the-beach-boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>July Fourth Fireworks Spectacular with The Beach Boys – with Special Guest John Stamos</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4251/2026-07-04/july-fourth-fireworks-spectacular-with-the-beach-boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Herb Alpert &amp; The Tijuana Brass &amp; Other Delights</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4294/2026-07-05/herb-alpert-the-tijuana-brass-other-delights</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Wilkins Conducts Bernstein &amp; Ellington</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4295/2026-07-08/wilkins-conducts-bernstein-ellington</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>The Classical World Cup</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4296/2026-07-09/the-classical-world-cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Music from the Films of Wes Anderson</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4288/2026-07-10/music-from-the-films-of-wes-anderson</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Music from the Films of Wes Anderson</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4289/2026-07-11/music-from-the-films-of-wes-anderson</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Music from the Films of Wes Anderson – KCRW Festival</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4534/2026-07-12/music-from-the-films-of-wes-anderson</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tchaikovsky &amp; Beethoven</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4297/2026-07-14/tchaikovsky-beethoven</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>07/15/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Salsa Spectacular: Nathy Peluso &amp; Grupo Niche</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4298/2026-07-15/salsa-spectacular-nathy-peluso-grupo-niche</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>07/16/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mozart &amp; Brahms</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4299/2026-07-16/mozart-brahms</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Let the Sunshine In: The Music of ’69</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4300/2026-07-17/let-the-sunshine-in-the-music-of-69</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>07/18/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Blues Traveler • Gin Blossoms – Spin Doctors</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4301/2026-07-18/blues-traveler-gin-blossoms</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>07/19/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bob Moses and Cannons: Afterglow Tour – Oxis, KCRW Festival</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4302/2026-07-19/bob-moses-and-cannons-afterglow-tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>07/21/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Joe Hisaishi Film Music Concert – Featuring Studio Ghibli &amp; More</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4303/2026-07-21/joe-hisaishi-film-music-concert</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>07/22/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Joe Hisaishi Film Music Concert – Featuring Studio Ghibli &amp; More</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4304/2026-07-22/joe-hisaishi-film-music-concert</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Joe Hisaishi Film Music Concert – Featuring Studio Ghibli &amp; More</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4305/2026-07-23/joe-hisaishi-film-music-concert</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>07/24/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Smokey Robinson &amp; Gladys Knight: Just the Two of Us</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4259/2026-07-24/smokey-robinson-gladys-knight-just-the-two-of-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>07/25/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Smokey Robinson &amp; Gladys Knight: Just the Two of Us</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4260/2026-07-25/smokey-robinson-gladys-knight-just-the-two-of-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>07/26/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Boris Brejcha with the Hollywood Bowl Orchestra – KCRW Festival</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4308/2026-07-26/boris-brejcha-with-the-hollywood-bowl-orchestra</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>07/28/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Rhapsody in Blue&amp; Shostakovich</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4309/2026-07-28/rhapsody-in-blue-shostakovich</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>07/29/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tower of Power and Preservation Hall Jazz Band</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4310/2026-07-29/tower-of-power-and-preservation-hall-jazz-band</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>07/30/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pictures at an Exhibition</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4311/2026-07-30/pictures-at-an-exhibition</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>07/31/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Tchaikovsky Spectacular with Fireworks</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4312/2026-07-31/tchaikovsky-spectacular-with-fireworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tchaikovsky Spectacular with Fireworks</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4313/2026-08-01/tchaikovsky-spectacular-with-fireworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>08/02/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>St. Vincent with the Hollywood Bowl Orchestra – Anoushka Shankar, KCRW Festival</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4314/2026-08-02/st-vincent-with-the-hollywood-bowl-orchestra</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mendelssohn &amp; Haydn</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4315/2026-08-04/mendelssohn-haydn</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ZZ Top – with Special Guest Cheap Trick</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4354/2026-08-05/zz-top</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Brahms &amp; Bizet</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4316/2026-08-06/brahms-bizet</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Counting Crows</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4317/2026-08-07/counting-crows</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Counting Crows</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4349/2026-08-08/counting-crows</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragonin Concert</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4319/2026-08-09/how-to-train-your-dragon-in-concert</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>John Mellencamp</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4277/2026-08-10/john-mellencamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mozart Under the Stars</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4320/2026-08-11/mozart-under-the-stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>08/13/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Santana – The Doobie Brothers</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4364/2026-08-13/santana</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Al Green – The Womack Sisters</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4321/2026-08-14/al-green</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Top Gun: Maverickin Concert</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4353/2026-08-15/top-gun-maverick-in-concert</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>08/16/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>YOASOBI</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4844/2026-08-16/yoasobi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>The Black Crowes &amp; Tedeschi Trucks Band – Whiskey Myers</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4352/2026-08-17/the-black-crowes-tedeschi-trucks-band</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>08/18/2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Gershwin, Bernstein &amp; More</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4323/2026-08-18/gershwin-bernstein-more</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>08/19/2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Herbie Hancock Celebrates Miles Davis</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4324/2026-08-19/herbie-hancock-celebrates-miles-davis</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>08/20/2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Celebrating Gustavo at the Bowl: Beethoven 9</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4325/2026-08-20/celebrating-gustavo-at-the-bowl-beethoven-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Celebrating Gustavo at the Bowl: Dudamel's Playlist</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4326/2026-08-21/celebrating-gustavo-at-the-bowl-dudamels-playlist</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>08/22/2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Celebrating Gustavo at the Bowl: Foo Fighters with the LA Phil and YOLA</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4287/2026-08-22/celebrating-gustavo-at-the-bowl-foo-fighters-with-the-la-phil-and-yola</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>08/23/2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Celebrating Gustavo at the Bowl: A Musical Legacy</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4361/2026-08-23/celebrating-gustavo-at-the-bowl-a-musical-legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>08/25/2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Beethoven’s Fifth</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4330/2026-08-25/beethovens-fifth</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>08/27/2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Rachmaninoff &amp; Adams</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4327/2026-08-27/rachmaninoff-adams</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>David Byrne: Who is the Sky?</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4328/2026-08-28/david-byrne-who-is-the-sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>08/29/2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>David Byrne: Who is the Sky?</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4329/2026-08-29/david-byrne-who-is-the-sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>08/30/2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Smooth Summer Jazz – The Commodores • Boney James, Sheila E.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4252/2026-08-30/smooth-summer-jazz</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>08/31/2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MUSE – Portugal. The Man, The Temper Trap</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4837/2026-08-31/muse</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Dvořák &amp; Bruch</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4331/2026-09-01/dvorak-bruch</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Amadeusin Concert</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4332/2026-09-03/amadeus-in-concert</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Maestro of the Movies:A Tribute to John Williams</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4333/2026-09-04/maestro-of-the-movies-a-tribute-to-john-williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Maestro of the Movies:A Tribute to John Williams</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4334/2026-09-05/maestro-of-the-movies-a-tribute-to-john-williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Maestro of the Movies:A Tribute to John Williams</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4335/2026-09-06/maestro-of-the-movies-a-tribute-to-john-williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Los Angeles Ballet at the Bowl</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4336/2026-09-08/los-angeles-ballet-at-the-bowl</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Buddy Guy 90 – with Special Guests Christone “Kingfish” Ingram and his Delta Jam</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4337/2026-09-09/buddy-guy-90</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ravel, Debussy &amp; Saint-Saëns</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4338/2026-09-10/ravel-debussy-saint-saens</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>09/11/2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Fireworks Finale:OneRepublic</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4339/2026-09-11/fireworks-finale-onerepublic</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Fireworks Finale:OneRepublic</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4340/2026-09-12/fireworks-finale-onerepublic</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>09/13/2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Lucy Dacus with the Hollywood Bowl Orchestra – Cat Power, KCRW Festival</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4341/2026-09-13/lucy-dacus-with-the-hollywood-bowl-orchestra</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>09/15/2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Andrea Bocelli</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4356/2026-09-15/andrea-bocelli</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>09/16/2026</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Andrea Bocelli</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4357/2026-09-16/andrea-bocelli</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>09/18/2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Orville Peck</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4355/2026-09-18/orville-peck</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Squeeze – with special guest ADAM ANT, and The English Beat</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4343/2026-09-19/squeeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>09/20/2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Gregory Alan Isakov with the Hollywood Bowl Orchestra – José González</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4344/2026-09-20/gregory-alan-isakov-with-the-hollywood-bowl-orchestra</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>09/23/2026</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jazz at Lincoln Center Orchestra with Wynton Marsalis – John Coltrane 100th Celebration with Lakecia Benjamin</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4345/2026-09-23/jazz-at-lincoln-center-orchestra-with-wynton-marsalis</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jon Bellion</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4509/2026-09-24/jon-bellion</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>The Concert:A Tribute to ABBA – MenAlive</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4254/2026-09-25/the-concert-a-tribute-to-abba</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Rodgers &amp; Hammerstein’s The Sound of Music Sing-A-Long</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4342/2026-09-26/rodgers-hammersteins-the-sound-of-music-sing-a-long</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>09/27/2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jon Batiste</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4346/2026-09-27/jon-batiste</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lauren Halsey'semajendatwith Erykah Badu – and DJ Pee .Wee (Anderson .Paak), and Charles Gaines Collective with Black Nile</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4843/2026-09-29/lauren-halseys-emajendat-with-erykah-badu</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Rubén Blades &amp; Roberto Delgado Big Band: Fotografías Tour – Silvana Estrada</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4347/2026-09-30/ruben-blades-roberto-delgado-big-band-fotografias-tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>“The Hayley Williams Show”</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4885/2026-10-05/the-hayley-williams-show</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>“The Hayley Williams Show”</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4888/2026-10-06/the-hayley-williams-show</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Empire of the Sun – Polo &amp; Pan, Midnight Gen</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4537/2026-10-08/empire-of-the-sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Mac DeMarco</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4363/2026-10-09/mac-demarco</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jack Johnson – Hermanos Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4256/2026-10-10/jack-johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jack Johnson – Hermanos Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4257/2026-10-11/jack-johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>10/15/2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Cynthia Erivo</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4891/2026-10-15/cynthia-erivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SmartLess Live with Jason Bateman, Sean Hayes, &amp; Will Arnett</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4841/2026-10-17/smartless-live-with-jason-bateman-sean-hayes-will-arnett</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>10/21/2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>My Chemical Romance</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4231/2026-10-21/my-chemical-romance</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>10/23/2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>My Chemical Romance</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4232/2026-10-23/my-chemical-romance</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>My Chemical Romance</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4233/2026-10-24/my-chemical-romance</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>10/30/2026</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>My Chemical Romance – The Used</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4263/2026-10-30/my-chemical-romance</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>My Chemical Romance – Thrice</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodbowl.com/events/performances/4264/2026-10-31/my-chemical-romance</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId101"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Dodger Stadium" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Hollywood Bowl" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Past Events" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dodger Stadium" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hollywood Bowl" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Past Events" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4600,7 +4600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9062,17 +9062,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9082,19 +9082,19 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Sporting San Miguelito</t>
+          <t>MORAT</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-san-miguelito</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9109,17 +9109,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Vegas Golden Knights vs Los Angeles Kings</t>
+          <t>LA Galaxy vs Sporting San Miguelito</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsknights022526</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-san-miguelito</t>
         </is>
       </c>
     </row>
@@ -9131,66 +9131,66 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>02/24/2026</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Orlando Magic vs Los Angeles Lakers</t>
+          <t>Vegas Golden Knights vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersmagic022426</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsknights022526</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>02/23/2026</t>
+          <t>02/24/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>GHOST: Skeletour World Tour 2026</t>
+          <t>Orlando Magic vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2964?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ghost_260223</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersmagic022426</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9205,56 +9205,56 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>GHOST: Skeletour World Tour 2026</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-8/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2964?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ghost_260223</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>02/23/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Orlando Magic vs LA Clippers</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2688?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260222</t>
+          <t>https://thekiaforum.com/event/lady-gaga-8/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9269,24 +9269,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>Orlando Magic vs LA Clippers</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-7/</t>
+          <t>https://intuitdome.com/events/event-schedule/2688?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260222</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9301,24 +9301,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>LA Galaxy vs New York City FC</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-york-city-fc</t>
+          <t>https://thekiaforum.com/event/lady-gaga-7/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9333,17 +9333,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>LA Galaxy vs New York City FC</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/585/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-york-city-fc</t>
         </is>
       </c>
     </row>
@@ -9365,24 +9365,24 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/588/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/585/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9397,24 +9397,24 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Boston Celtics vs Los Angeles Lakers</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersceltics022226</t>
+          <t>https://www.rosebowlstadium.com/events/details/588/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9429,56 +9429,56 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ViVE 2026</t>
+          <t>Boston Celtics vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/vive-2026</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersceltics022226</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>8 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Los Bukis</t>
+          <t>ViVE 2026</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/los-bukis-february-21-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/vive-2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9493,24 +9493,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8 PM</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Los Tigres del Norte</t>
+          <t>Los Bukis</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2912?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=los_tigres_del_norte_260221</t>
+          <t>https://www.sofistadium.com/events/detail/los-bukis-february-21-2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9525,17 +9525,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Los Tigres del Norte</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/584/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2912?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=los_tigres_del_norte_260221</t>
         </is>
       </c>
     </row>
@@ -9557,56 +9557,56 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/587/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/584/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>8 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Los Bukis</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/los-bukis-2026</t>
+          <t>https://www.rosebowlstadium.com/events/details/587/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9621,24 +9621,24 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8 PM</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Harlem Globetrotters</t>
+          <t>Los Bukis</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2904</t>
+          <t>https://www.sofistadium.com/events/detail/los-bukis-2026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9653,24 +9653,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SABATON</t>
+          <t>Harlem Globetrotters</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/sabaton/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2904</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>SABATON</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/583/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://thekiaforum.com/event/sabaton/</t>
         </is>
       </c>
     </row>
@@ -9717,24 +9717,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/586/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/583/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9749,56 +9749,56 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Los Angeles Clippers vs Los Angeles Lakers</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersclippers022026</t>
+          <t>https://www.rosebowlstadium.com/events/details/586/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Denver Nuggets vs LA Clippers</t>
+          <t>Los Angeles Clippers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2687?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260219</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersclippers022026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -9813,17 +9813,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>Denver Nuggets vs LA Clippers</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-5/</t>
+          <t>https://intuitdome.com/events/event-schedule/2687?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260219</t>
         </is>
       </c>
     </row>
@@ -9835,12 +9835,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>02/18/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-6/</t>
+          <t>https://thekiaforum.com/event/lady-gaga-5/</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/18/2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9882,51 +9882,51 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CARDI B</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/cardi-b-2/</t>
+          <t>https://thekiaforum.com/event/lady-gaga-6/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>75th NBA All-Star Game</t>
+          <t>CARDI B</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3002?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_game_260215</t>
+          <t>https://thekiaforum.com/event/cardi-b-2/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9941,56 +9941,56 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>CARDI B</t>
+          <t>75th NBA All-Star Game</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/cardi-b/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3002?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_game_260215</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/15/2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>All-Star Saturday</t>
+          <t>CARDI B</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3003?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_saturday_260214</t>
+          <t>https://thekiaforum.com/event/cardi-b/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10005,56 +10005,56 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>DJ CASSIDY'S PASS THE MIC LIVE!</t>
+          <t>All-Star Saturday</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/dj-cassidys-pass-the-mic-live/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3003?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_saturday_260214</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Castrol Rising Stars</t>
+          <t>DJ CASSIDY'S PASS THE MIC LIVE!</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3004?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=castrol_rising_stars_260213</t>
+          <t>https://thekiaforum.com/event/dj-cassidys-pass-the-mic-live/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10069,17 +10069,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>HBCU CLASSIC PRESENTED BY AT&amp;T</t>
+          <t>Castrol Rising Stars</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/hbcu-classic-presented-by-att/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3004?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=castrol_rising_stars_260213</t>
         </is>
       </c>
     </row>
@@ -10106,19 +10106,19 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RUFFLES CELEBRITY GAME</t>
+          <t>HBCU CLASSIC PRESENTED BY AT&amp;T</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ruffles-celebrity-game/</t>
+          <t>https://thekiaforum.com/event/hbcu-classic-presented-by-att/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10138,29 +10138,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Banda MS de Sergio Lizarraga</t>
+          <t>RUFFLES CELEBRITY GAME</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/bandams021326</t>
+          <t>https://thekiaforum.com/event/ruffles-celebrity-game/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10170,19 +10170,19 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>NBA ALL-STAR PITCH COMPETITION</t>
+          <t>Banda MS de Sergio Lizarraga</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/nba-all-star-pitch-competition/</t>
+          <t>https://www.cryptoarena.com/events/detail/bandams021326</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10197,24 +10197,24 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Dallas Mavericks vs Los Angeles Lakers</t>
+          <t>NBA ALL-STAR PITCH COMPETITION</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersmavs021226</t>
+          <t>https://thekiaforum.com/event/nba-all-star-pitch-competition/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10229,49 +10229,49 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>NBA Crossover: The Ultimate Fan Experience</t>
+          <t>Dallas Mavericks vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/nba-crossover-ultimate-fan-experience</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersmavs021226</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>San Antonio Spurs vs Los Angeles Lakers</t>
+          <t>NBA Crossover: The Ultimate Fan Experience</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersspurs021026</t>
+          <t>https://www.laconventioncenter.com/events/detail/nba-crossover-ultimate-fan-experience</t>
         </is>
       </c>
     </row>
@@ -10283,91 +10283,91 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
+          <t>San Antonio Spurs vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersthuner020926</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersspurs021026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/597/rose-bowl-flea-market</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersthuner020926</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Golden State Warriors vs Los Angeles Lakers</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerswarriors020726</t>
+          <t>https://www.rosebowlstadium.com/events/details/597/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
@@ -10379,66 +10379,66 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers vs Los Angeles Lakers</t>
+          <t>Golden State Warriors vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakers76ers020526</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerswarriors020726</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers vs LA Clippers</t>
+          <t>Philadelphia 76ers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2662?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260204</t>
+          <t>https://www.cryptoarena.com/events/detail/lakers76ers020526</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10453,56 +10453,56 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Seattle Kraken vs Los Angeles Kings</t>
+          <t>Cleveland Cavaliers vs LA Clippers</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingskraken020426</t>
+          <t>https://intuitdome.com/events/event-schedule/2662?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260204</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers vs LA Clippers</t>
+          <t>Seattle Kraken vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2686?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260202</t>
+          <t>https://www.cryptoarena.com/events/detail/kingskraken020426</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>L.A. Memorial Coliseum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -10517,17 +10517,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>LAFC vs Inter Miami CF</t>
+          <t>Philadelphia 76ers vs LA Clippers</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/lafc-vs-intermiami-2026/</t>
+          <t>https://intuitdome.com/events/event-schedule/2686?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260202</t>
         </is>
       </c>
     </row>
@@ -10554,29 +10554,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Night of Hope</t>
+          <t>LAFC vs Inter Miami CF</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/night-of-hope/</t>
+          <t>https://www.lacoliseum.com/events/lafc-vs-intermiami-2026/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>L.A. Memorial Coliseum</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10586,19 +10586,19 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>NEW EDITION</t>
+          <t>Night of Hope</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/new-edition/</t>
+          <t>https://www.lacoliseum.com/events/night-of-hope/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>IBJJF Jiu Jitsu Championship</t>
+          <t>NEW EDITION</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/ibjjf-jiu-jitsu-championship</t>
+          <t>https://thekiaforum.com/event/new-edition/</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Grand Archive Phantom Monarch Regional Championships</t>
+          <t>IBJJF Jiu Jitsu Championship</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/grand-archive-phantom-monarch-regional-championships</t>
+          <t>https://www.laconventioncenter.com/events/detail/ibjjf-jiu-jitsu-championship</t>
         </is>
       </c>
     </row>
@@ -10667,12 +10667,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10682,42 +10682,394 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Modern Language Association Annual Convention 2027</t>
+          <t>Grand Archive Phantom Monarch Regional Championships</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/modern-language-association-annual-convention-2027</t>
+          <t>https://www.laconventioncenter.com/events/detail/grand-archive-phantom-monarch-regional-championships</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>01/25/2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>01/24/2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>01/20/2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>01/17/2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Intuit Dome</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
           <t>LA Convention Center</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Modern Language Association Annual Convention 2027</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/modern-language-association-annual-convention-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>LA Convention Center</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C202" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>TBA</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="E202" t="inlineStr">
         <is>
           <t>LA Art Show 2027</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>https://www.laconventioncenter.com/events/detail/la-art-show-2027</t>
         </is>
@@ -10915,6 +11267,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId201"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10926,14 +11289,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10966,930 +11329,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>01/13/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>01/16/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>01/17/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>01/20/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>01/21/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>01/24/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>01/25/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>01/28/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01/29/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MORAT</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>06/13/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3671?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260613</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>06/14/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3672?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260614</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>06/20/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>12:30 PM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>BIG3</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3898?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=big3_260620</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>JOJI: SOLARIS</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3506?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260711</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>07/12/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>JOJI: SOLARIS</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3513?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260712</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>07/17/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Forrest Frank</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>07/27/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4:30 PM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>WWE Monday Night RAW</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3937?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wwe_monday_night_raw_260727</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Grupo Frontera</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3520?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=grupo_frontera_260807</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>08/15/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Yeat</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3699?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=yeat_260815</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>08/21/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Ne-Yo &amp; Akon</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>J. Cole</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3492?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>J. Cole</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3498?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>World of Warcraft®: 20 Years of Music</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3683?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=world_of_warcraft_260910</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>09/18/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>8:30 PM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Maná</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>09/19/2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>8:30 PM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Maná</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>09/24/2026</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Kehlani</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/4033?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kehlani_260924</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>aespa LIVE TOUR – SYNK : COMPLæXITY – in Los Angeles</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3850?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=aespa_live_tour_261003</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TLC and Salt-N-Pepa</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3613?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=tlc_salt-n-pepa_261010</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>10/17/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Young Miko</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3707?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=young_miko_261017</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>10/24/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Pokémon Night Out</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3674?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=pokemon_night_out_261024</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>11/22/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Three Days Grace</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11900,14 +11344,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11940,1602 +11384,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>06/13/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06/17/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>06/19/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>06/20/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>06/24/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MADISON BEER – the locket tour</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/madison-beer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>06/26/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>06/27/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/aap-rocky/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>06/29/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ROSALÍA – LUX TOUR 2026</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rosalia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>07/01/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ROSALÍA – LUX TOUR 2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rosalia-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HILARY DUFF – the lucky me tour</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/hilary-duff/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HILARY DUFF – the lucky me tour</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>07/17/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>YOUNG THE GIANT – Victory Garden Tour</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/young-the-giant/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>07/18/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>EVANESCENCE</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/evanescence/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/motionless-in-white/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ive/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>08/11/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>08/12/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>08/13/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>08/14/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/melanie-martinez/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>08/21/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/omar-courtz/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/chicago-styx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>09/11/2026</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>09/12/2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SODA STEREO – ECOS TOUR</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/soda-stereo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>09/23/2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ROBYN – The Sexistential Tour</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/robyn/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>09/24/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ROBYN – The Sexistential Tour</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/robyn-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>09/25/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/lily-allen/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>09/26/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>BILLY STRINGS</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/billy-strings-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>09/30/2026</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>KLANGKUENSTLER – OUTWORLD – Klangkuenstler All Night Long</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/klangkuenstler/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/mumford-sons/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SOMBR – You Are The Reason Tour</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/sombr/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10/16/2026</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>JUANES</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/juanes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>10/20/2026</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/monsta-x/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10/22/2026</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>DOJA CAT – Tour Ma Vie World Tour</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/doja-cat/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>10/24/2026</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>GORILLAZ – The Mountain Tour</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gorillaz-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>DON OMAR – The Last King World Tour</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/don-omar/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>MON LAFERTE – Femme Fatale Tour</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/mon-laferte/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>11/12/2026</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>11/13/2026</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/slayer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>11/14/2026</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/slayer-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>11/15/2026</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rawayana/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>11/18/2026</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TEDDY SWIMS – The UGLY Tour</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/teddy-swims/</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>12/14/2026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gracie-abrams-5/</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>12/18/2026</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gracie-abrams-6/</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>12/19/2026</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gracie-abrams-4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>12/20/2026</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gracie-abrams-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>05/22/2027</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NIALL HORAN – Dinner Party Live On Tour</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/niall-horan/</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13546,14 +11399,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13586,174 +11439,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>07/17/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs LAFC</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-lafc</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07/22/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs St. Louis CITY SC</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-st-louis-city-sc</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>07/25/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Campeón de Campeones 2026</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/campeon-de-campeones-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs FC Dallas</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-fc-dallas</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>08/19/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs San Jose Earthquakes</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-jose-earthquakes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs New England Revolution</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-england-revolution</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14654,14 +12344,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14694,90 +12384,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/02/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Alex Warren: Finding Family on the Road – With special guests Nat &amp; Alex Wolff</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/alexwarren060626</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14788,14 +12399,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14828,258 +12439,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>FIFA Fan Festival™ Los Angeles</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/fifa-fan-festival-los-angeles/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>America250 July 4 Concert</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/america250-july-4-concert/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>08/29/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>San Jose State vs USC</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/sanjosestate-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Fresno State vs USC</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/fresno-state-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>09/12/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Louisiana vs USC</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/louisiana-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>09/26/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Oregon vs USC</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/oregon-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Washington vs USC</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/washington-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>10/31/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ohio State vs USC</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/ohio-state-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>11/21/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Maryland vs USC</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/maryland-vs-usc-2026/</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16288,14 +13652,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16328,1490 +13692,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>05/29/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:15 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vs. Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823946</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>05/30/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>vs. Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823945</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>05/31/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>vs. Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823944</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>vs. Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823943</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>vs. Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823942</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vs. Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823941</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>06/15/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>vs. Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823938</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>06/16/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>vs. Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823939</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>06/17/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>12:10 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>vs. Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823940</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>06/19/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>vs. Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823936</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>06/20/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>vs. Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823937</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>06/21/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>vs. Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823934</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>07/02/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823935</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>07/03/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823933</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823932</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4:20 PM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823931</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>vs. Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823930</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>vs. Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823929</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>vs. Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823928</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>vs. Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823927</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>vs. Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823926</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>07/12/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>vs. Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823925</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>07/28/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>vs. Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823923</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>07/29/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>vs. Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823924</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>07/30/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>vs. Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823921</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>vs. Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823922</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>vs. Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823920</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>08/02/2026</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>4:20 PM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>vs. Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823919</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>vs. Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823918</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>08/11/2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>vs. Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823917</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>08/12/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>vs. Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823916</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>08/13/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823915</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>08/14/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823913</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>08/15/2026</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>4:15 PM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823914</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>08/16/2026</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823912</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>08/21/2026</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>vs. Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823911</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>08/22/2026</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>vs. Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823910</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>08/23/2026</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>vs. Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823909</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>vs. St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823908</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>09/02/2026</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>vs. St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823906</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>vs. St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823907</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>vs. Washington Nationals</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823905</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>vs. Washington Nationals</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823904</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>vs. Washington Nationals</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823903</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>vs. Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823902</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>09/08/2026</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>vs. Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823901</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>vs. Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823900</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>09/18/2026</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>vs. San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823898</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>09/19/2026</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>vs. San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823899</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>09/20/2026</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>vs. San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823896</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>09/22/2026</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823897</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>09/23/2026</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823894</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>09/24/2026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823895</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dodger Stadium" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hollywood Bowl" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Past Events" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dodger Stadium" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Hollywood Bowl" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Past Events" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11289,14 +11289,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11329,11 +11329,930 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01/17/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01/20/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01/24/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01/25/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Olivia Rodrigo</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MORAT</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3671?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260613</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>06/14/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3672?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260614</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BIG3</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3898?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=big3_260620</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3506?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260711</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>JOJI: SOLARIS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3513?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260712</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Forrest Frank</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/27/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WWE Monday Night RAW</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3937?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wwe_monday_night_raw_260727</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Grupo Frontera</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3520?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=grupo_frontera_260807</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Yeat</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3699?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=yeat_260815</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ne-Yo &amp; Akon</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3492?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3498?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>World of Warcraft®: 20 Years of Music</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3683?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=world_of_warcraft_260910</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>09/18/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Maná</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kehlani</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/4033?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kehlani_260924</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>aespa LIVE TOUR – SYNK : COMPLæXITY – in Los Angeles</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3850?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=aespa_live_tour_261003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TLC and Salt-N-Pepa</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3613?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=tlc_salt-n-pepa_261010</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Young Miko</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3707?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=young_miko_261017</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pokémon Night Out</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3674?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=pokemon_night_out_261024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11/22/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Three Days Grace</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11344,14 +12263,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11384,11 +12303,1602 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RUSH – Fifty Something</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rush-4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/17/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/19/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06/24/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MADISON BEER – the locket tour</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/madison-beer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06/26/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06/27/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/aap-rocky/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>06/29/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ROSALÍA – LUX TOUR 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rosalia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ROSALÍA – LUX TOUR 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rosalia-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HILARY DUFF – the lucky me tour</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/hilary-duff/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HILARY DUFF – the lucky me tour</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>YOUNG THE GIANT – Victory Garden Tour</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/young-the-giant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/18/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EVANESCENCE</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/evanescence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/31/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/motionless-in-white/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/ive/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08/13/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/melanie-martinez/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/omar-courtz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/chicago-styx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09/11/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SODA STEREO – ECOS TOUR</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/soda-stereo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>09/23/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ROBYN – The Sexistential Tour</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/robyn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ROBYN – The Sexistential Tour</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/robyn-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/lily-allen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BILLY STRINGS</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/billy-strings-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>KLANGKUENSTLER – OUTWORLD – Klangkuenstler All Night Long</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/klangkuenstler/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mumford-sons/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SOMBR – You Are The Reason Tour</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/sombr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10/16/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JUANES</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/juanes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10/20/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/monsta-x/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10/22/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DOJA CAT – Tour Ma Vie World Tour</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/doja-cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GORILLAZ – The Mountain Tour</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/gorillaz-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DON OMAR – The Last King World Tour</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/don-omar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MON LAFERTE – Femme Fatale Tour</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/mon-laferte/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SLAYER – Reign in Blood 40th Anniversary</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/slayer-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>11/15/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/rawayana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>11/18/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TEDDY SWIMS – The UGLY Tour</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/teddy-swims/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12/14/2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/gracie-abrams-5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12/18/2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/gracie-abrams-6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>12/19/2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/gracie-abrams-4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>12/20/2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/gracie-abrams-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>05/22/2027</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NIALL HORAN – Dinner Party Live On Tour</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://thekiaforum.com/event/niall-horan/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11399,14 +13909,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11439,11 +13949,174 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs LAFC</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-lafc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07/22/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-st-louis-city-sc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07/25/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Campeón de Campeones 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/campeon-de-campeones-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs FC Dallas</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-fc-dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08/19/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-jose-earthquakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs New England Revolution</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-england-revolution</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12344,14 +15017,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12384,11 +15057,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Alex Warren: Finding Family on the Road – With special guests Nat &amp; Alex Wolff</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/alexwarren060626</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12399,14 +15151,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12439,11 +15191,258 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FIFA Fan Festival™ Los Angeles</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/fifa-fan-festival-los-angeles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>America250 July 4 Concert</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/america250-july-4-concert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08/29/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Jose State vs USC</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/sanjosestate-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fresno State vs USC</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/fresno-state-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Louisiana vs USC</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/louisiana-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oregon vs USC</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/oregon-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Washington vs USC</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/washington-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ohio State vs USC</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/ohio-state-vs-usc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11/21/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Maryland vs USC</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lacoliseum.com/events/maryland-vs-usc-2026/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13652,14 +16651,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13692,11 +16691,1490 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No events found</t>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>05/29/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7:15 PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>vs. Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823946</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>05/30/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>vs. Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823945</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>05/31/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1:10 PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vs. Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823944</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>vs. Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823943</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>vs. Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823942</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1:10 PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>vs. Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823941</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06/15/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>vs. Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823938</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06/16/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>vs. Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823939</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06/17/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12:10 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>vs. Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823940</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06/19/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>vs. Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823936</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>06/20/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>vs. Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823937</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06/21/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1:10 PM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>vs. Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823934</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>vs. San Diego Padres</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823935</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>vs. San Diego Padres</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823933</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>vs. San Diego Padres</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823932</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4:20 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>vs. San Diego Padres</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823931</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>vs. Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823930</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>vs. Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823929</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>vs. Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823928</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>vs. Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823927</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6:10 PM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>vs. Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823926</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1:10 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>vs. Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823925</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>07/28/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>vs. Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823923</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>07/29/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>vs. Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823924</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>07/30/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>vs. Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823921</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>07/31/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>vs. Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823922</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6:10 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>vs. Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823920</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08/02/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4:20 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>vs. Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823919</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>vs. Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823918</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>vs. Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823917</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>vs. Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823916</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>08/13/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>vs. Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823915</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>vs. Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823913</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4:15 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>vs. Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823914</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>08/16/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1:10 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>vs. Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823912</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>vs. Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823911</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>08/22/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>6:10 PM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>vs. Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823910</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>08/23/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1:10 PM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>vs. Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823909</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>vs. St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823908</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>vs. St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823906</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>vs. St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823907</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>vs. Washington Nationals</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823905</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6:10 PM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>vs. Washington Nationals</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823904</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>vs. Washington Nationals</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823903</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6:10 PM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>vs. Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823902</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>vs. Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823901</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>vs. Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823900</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>09/18/2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>vs. San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823898</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>6:10 PM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>vs. San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823899</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>09/20/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1:10 PM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>vs. San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823896</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>09/22/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>vs. San Diego Padres</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823897</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>09/23/2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>vs. San Diego Padres</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823894</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7:10 PM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>vs. San Diego Padres</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/gameday/823895</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Dodger Stadium" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Hollywood Bowl" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Past Events" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SoFi Stadium" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuit Dome" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kia Forum" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dignity Health Sports Park" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rose Bowl Stadium" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto.com Arena" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L.A. Memorial Coliseum" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LA Convention Center" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dodger Stadium" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hollywood Bowl" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Past Events" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11289,14 +11289,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11329,930 +11329,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>01/13/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>01/16/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>01/17/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>01/20/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>01/21/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>01/24/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>01/25/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>01/28/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01/29/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Olivia Rodrigo</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MORAT</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>06/13/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3671?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260613</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>06/14/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SHAKIRA: Las Mujeres Ya No Lloran World Tour 2026</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3672?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=shakira_260614</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>06/20/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>12:30 PM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>BIG3</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3898?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=big3_260620</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>JOJI: SOLARIS</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3506?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260711</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>07/12/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>JOJI: SOLARIS</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3513?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=joji_260712</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>07/17/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Forrest Frank</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3285?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=forrest_frank_260717</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>07/27/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4:30 PM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>WWE Monday Night RAW</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3937?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wwe_monday_night_raw_260727</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Grupo Frontera</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3520?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=grupo_frontera_260807</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Lionel Richie and Earth, Wind &amp; Fire</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3449?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lionel_richie_earth_wind_fire_260809</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>08/15/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Yeat</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3699?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=yeat_260815</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>08/21/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Ne-Yo &amp; Akon</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3454?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=ne-yo_akon_260821</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>J. Cole</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3492?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>J. Cole</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3498?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=j_cole_260903</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>World of Warcraft®: 20 Years of Music</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3683?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=world_of_warcraft_260910</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>09/18/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>8:30 PM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Maná</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260918</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>09/19/2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>8:30 PM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Maná</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://intuitdome.com/events/mana?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=mana_260919</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>09/24/2026</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Kehlani</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/4033?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kehlani_260924</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>aespa LIVE TOUR – SYNK : COMPLæXITY – in Los Angeles</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3850?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=aespa_live_tour_261003</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TLC and Salt-N-Pepa</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3613?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=tlc_salt-n-pepa_261010</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>10/17/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Young Miko</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3707?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=young_miko_261017</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>10/24/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Pokémon Night Out</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3674?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=pokemon_night_out_261024</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>11/22/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Three Days Grace</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12263,14 +11344,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12303,1602 +11384,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>06/13/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RUSH – Fifty Something</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rush-4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06/17/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>06/19/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>06/20/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ARIANA GRANDE – The Eternal Sunshine Tour</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ariana-grande-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>06/24/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MADISON BEER – the locket tour</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/madison-beer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>06/26/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PALOMAZO NORTEÑO – CLASE MAESTRA TOUR</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/palomazo-norteno/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>06/27/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>A$AP ROCKY – Don't Be Dumb World Tour</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/aap-rocky/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>06/29/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ROSALÍA – LUX TOUR 2026</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rosalia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>07/01/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ROSALÍA – LUX TOUR 2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rosalia-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HILARY DUFF – the lucky me tour</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/hilary-duff/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HILARY DUFF – the lucky me tour</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/hilary-duff-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5 SECONDS OF SUMMER – EVERYONE’S A STAR! World Tour</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/5-seconds-of-summer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>07/17/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>YOUNG THE GIANT – Victory Garden Tour</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/young-the-giant/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>07/18/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>EVANESCENCE</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/evanescence/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MOTIONLESS IN WHITE – The Sweat and Blood Tour</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/motionless-in-white/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>IVE – WORLD TOUR [SHOW WHAT I AM] IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/ive/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>08/11/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>08/12/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>08/13/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>RÜFÜS DU SOL – with Ben Böhmer</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rufus-du-sol-5/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>08/14/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>MELANIE MARTINEZ – HADES: THE SACRIFICE</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/melanie-martinez/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>08/21/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OMAR COURTZ – POR SI MAÑANA NO ESTOY USA TOUR</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/omar-courtz/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CHICAGO &amp; STYX – The Windy Cities Tour - All The Hits... Your Kind of Tour</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/chicago-styx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>09/11/2026</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>JOHNNY BLUE SKIES &amp; THE DARK CLOUDS – Mutiny for the Masses 2026 Tour</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/johnny-blue-skies-the-dark-clouds/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>09/12/2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SODA STEREO – ECOS TOUR</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/soda-stereo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>09/23/2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ROBYN – The Sexistential Tour</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/robyn/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>09/24/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ROBYN – The Sexistential Tour</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/robyn-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>09/25/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LILY ALLEN – Lily Allen Performs West End Girl</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/lily-allen/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>09/26/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>BILLY STRINGS</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/billy-strings-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>09/30/2026</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DISNEY DESCENDANTS, ZOMBIES &amp; CAMP ROCK: WORLDS COLLIDE CONCERT TOUR</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/worlds-collide-concert-tour/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>KLANGKUENSTLER – OUTWORLD – Klangkuenstler All Night Long</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/klangkuenstler/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/mumford-sons/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>MUMFORD &amp; SONS – Prizefighter Tour</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/mumford-sons-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SOMBR – You Are The Reason Tour</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/sombr/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10/16/2026</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>JUANES</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/juanes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>10/20/2026</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>MONSTA X – 2026 MONSTA X WORLD TOUR [THE X : NEXUS] IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/monsta-x/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10/22/2026</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>DOJA CAT – Tour Ma Vie World Tour</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/doja-cat/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>10/24/2026</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>GORILLAZ – The Mountain Tour</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gorillaz-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>DON OMAR – The Last King World Tour</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/don-omar/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>MON LAFERTE – Femme Fatale Tour</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/mon-laferte/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>11/12/2026</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>THE SMASHING PUMPKINS – The Rats In A Cage Tour</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-smashing-pumpkins/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>11/13/2026</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/slayer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>11/14/2026</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SLAYER – Reign in Blood 40th Anniversary</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/slayer-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>11/15/2026</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>RAWAYANA – ¿Dónde es el after? World Tour</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/rawayana/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>11/18/2026</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TEDDY SWIMS – The UGLY Tour</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/teddy-swims/</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>THE NEIGHBOURHOOD – THE WOURLD TOUR</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/the-neighbourhood-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>12/14/2026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gracie-abrams-5/</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>12/18/2026</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gracie-abrams-6/</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>12/19/2026</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gracie-abrams-4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>12/20/2026</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>GRACIE ABRAMS – The Look at My Life Tour</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/gracie-abrams-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>05/22/2027</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NIALL HORAN – Dinner Party Live On Tour</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>https://thekiaforum.com/event/niall-horan/</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13909,14 +11399,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13949,174 +11439,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>07/17/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs LAFC</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-lafc</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07/22/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs St. Louis CITY SC</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-st-louis-city-sc</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>07/25/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Campeón de Campeones 2026</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/campeon-de-campeones-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs FC Dallas</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-fc-dallas</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>08/19/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs San Jose Earthquakes</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-jose-earthquakes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LA Galaxy vs New England Revolution</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-england-revolution</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15017,14 +12344,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15057,90 +12384,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/02/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks vs Dallas Wings – Commissioner's Cup</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/sparkswings060526</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7:30 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Alex Warren: Finding Family on the Road – With special guests Nat &amp; Alex Wolff</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cryptoarena.com/events/detail/alexwarren060626</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15151,14 +12399,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15191,258 +12439,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>FIFA Fan Festival™ Los Angeles</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/fifa-fan-festival-los-angeles/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>America250 July 4 Concert</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/america250-july-4-concert/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>08/29/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>San Jose State vs USC</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/sanjosestate-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Fresno State vs USC</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/fresno-state-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>09/12/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Louisiana vs USC</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/louisiana-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>09/26/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Oregon vs USC</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/oregon-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Washington vs USC</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/washington-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>10/31/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ohio State vs USC</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/ohio-state-vs-usc-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>11/21/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Maryland vs USC</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lacoliseum.com/events/maryland-vs-usc-2026/</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16651,14 +13652,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16691,1490 +13692,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>05/29/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7:15 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vs. Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823946</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>05/30/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>vs. Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823945</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>05/31/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>vs. Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823944</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>vs. Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823943</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>vs. Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823942</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vs. Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823941</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>06/15/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>vs. Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823938</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>06/16/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>vs. Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823939</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>06/17/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>12:10 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>vs. Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823940</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>06/19/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>vs. Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823936</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>06/20/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>vs. Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823937</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>06/21/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>vs. Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823934</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>07/02/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823935</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>07/03/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823933</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823932</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4:20 PM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823931</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>vs. Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823930</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>vs. Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823929</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>vs. Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823928</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>vs. Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823927</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>07/11/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>vs. Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823926</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>07/12/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>vs. Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823925</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>07/28/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>vs. Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823923</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>07/29/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>vs. Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823924</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>07/30/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>vs. Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823921</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>vs. Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823922</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>vs. Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823920</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>08/02/2026</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>4:20 PM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>vs. Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823919</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>vs. Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823918</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>08/11/2026</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>vs. Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823917</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>08/12/2026</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>vs. Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823916</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>08/13/2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823915</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>08/14/2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823913</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>08/15/2026</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>4:15 PM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823914</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>08/16/2026</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>vs. Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823912</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>08/21/2026</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>vs. Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823911</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>08/22/2026</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>vs. Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823910</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>08/23/2026</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>vs. Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823909</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>vs. St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823908</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>09/02/2026</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>vs. St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823906</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>vs. St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823907</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>vs. Washington Nationals</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823905</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>vs. Washington Nationals</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823904</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>vs. Washington Nationals</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823903</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>vs. Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823902</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>09/08/2026</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>vs. Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823901</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>vs. Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823900</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>09/18/2026</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>vs. San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823898</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>09/19/2026</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>6:10 PM</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>vs. San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823899</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>09/20/2026</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1:10 PM</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>vs. San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823896</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>09/22/2026</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823897</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>09/23/2026</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823894</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>09/24/2026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>7:10 PM</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>vs. San Diego Padres</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mlb.com/gameday/823895</t>
+          <t>No events found</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -15017,12 +15017,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
@@ -15135,11 +15135,1103 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Portland Fire – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksfire060726</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Louis Tomlinson – How Did We Get Here? World Tour 2026 with Guests The Aces</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/louistomlinson061126</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ariana Grande – The Eternal Sunshine Tour</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/arianagrande26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06/17/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Minnesota Lynx – Commissioner's Cup</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparkslynx061726</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06/18/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Diljit Dosanjh – Aura North American Tour 2026</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/diljitdosanjh061826</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06/21/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs New York Liberty</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksliberty062126</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06/25/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Summer Walker – Still Finally Over It Tour</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/summerwalker062526</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>06/26/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kid Cudi Presents: The Rebel Ragers Tour 2026 – With Big Boi, Dot Da Genius, and Chip Tha Ripper</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/kidkudi062626</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06/28/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Don Toliver – Octane Tour with SahBabii, SoFaygo, and Chase B</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/dontoliver062926</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>J-POP SOUND CAPSULE 2026 – ALI | Roselia | SPYAIR | Yoko Kanno | Yoko Takahashi</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/j-pop-sound-capsule-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Seattle Storm</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksstorm070626</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Indiana Fever</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksfever070826</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Chicago Sky</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparkssky071026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/14/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Olivia Dean – The Art of Living - Live 2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/oliviadean26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Monster Jam</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/monsterjam26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>07/22/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksmercury072226</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>07/28/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs New York Liberty</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksliberty072826</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Megan Moroney – The Cloud 9 Tour with JP Saxe and Solon Holt</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/megan-moroney-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksvalkyries080926</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Benson Boone – Wanted Man Tour 2026</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/bensonboone26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>KCON LA 2026 M Countdown</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/kcon26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>08/20/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksdream082026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08/22/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparkssun082226</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksdream082426</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08/25/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MAMAMOO – 2026 USA TOUR</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/mamamoo082526</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Washington Mystics</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksmystics082826</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Journey – FINAL FRONTIER TOUR</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/journey091226</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09/16/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026 LE SSERAFIM TOUR 'PUREFLOW' IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/lesserafim26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>09/20/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Portland Fire</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksfire092026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks vs Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/sparksvalkyries092426</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>09/25/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Yandel – SINFÓNICO USA TOUR 2026</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/yandel092526</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>09/28/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Disney Descendants, ZOMBIES &amp; Camp Rock: Worlds Collide Concert Tour – Malachi Barton, Liamani Segura, Dara Reneé, Mekonnen Knife, Hudson Stone, Swayam Bhatia, Kiara Romero, Alexandro Byrd</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/disneydescendants092826</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>JUNGLE – World Tour 2026 with RIO KOSTA</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/jungle101026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10/18/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Kacey Musgraves – Middle of Nowhere Tour with Gabriella Rose and Estevie</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/kaceymusgraves26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10/24/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Weezer: The Gathering – With special guests The Shins &amp; Silversun Pickups</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/weezer102426</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>XG WORLD TOUR: THE CORE IN LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/xg-110526</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>11/21/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>KATSEYE – The WILDWORLD Tour</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/katseye26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>J. Cole – The Fall-Off World Tour</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/jcole090126</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NCAA West Regional</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptoarena.com/events/detail/ncaawestregional2027</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -13909,7 +13909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14108,6 +14108,168 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-seattle-sounders</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SuperMotocross Playoff Round 2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/supermotocross</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-colorado-rapids</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs Portland Timbers FC</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-portland-timbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs San Diego FC</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-san-diego-fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs Austin FC</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-austin-fc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
@@ -14116,6 +14278,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Salsa Spectacular: Nathy Peluso &amp; Grupo Niche</t>
+          <t>Salsa Spectacular: Nathy Peluso &amp; Grupo Niche – El Marchante</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -14625,7 +14625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14697,34 +14697,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Demo Days</t>
+          <t>Picture on the Pitch</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/649/demo-days</t>
+          <t>https://www.rosebowlstadium.com/events/details/652/picture-on-the-pitch</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06/28/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14739,51 +14739,51 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/650/demo-days</t>
+          <t>https://www.rosebowlstadium.com/events/details/649/demo-days</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>06/28/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Foodieland</t>
+          <t>Demo Days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/637/foodieland</t>
+          <t>https://www.rosebowlstadium.com/events/details/650/demo-days</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -14793,19 +14793,19 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/638/foodieland</t>
+          <t>https://www.rosebowlstadium.com/events/details/637/foodieland</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14820,142 +14820,142 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/639/foodieland</t>
+          <t>https://www.rosebowlstadium.com/events/details/638/foodieland</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5:15 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DRUM CORPS AT THE ROSE BOWL</t>
+          <t>Foodieland</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/644/drum-corps-at-the-rose-bowl</t>
+          <t>https://www.rosebowlstadium.com/events/details/639/foodieland</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>DRUM CORPS AT THE ROSE BOWL</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/602/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/644/drum-corps-at-the-rose-bowl</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>07/12/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Head in the Clouds</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/642/head-in-the-clouds</t>
+          <t>https://www.rosebowlstadium.com/events/details/602/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Head in the Clouds</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/603/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/642/head-in-the-clouds</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08/15/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6:30 PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NOAH KAHAN - THE GREAT DIVIDE TOUR</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/633/noah-kahan-the-great-divide-tour</t>
+          <t>https://www.rosebowlstadium.com/events/details/603/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
@@ -14967,22 +14967,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08/22/2026</t>
+          <t>08/15/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>6:30 PM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Just Like Heaven</t>
+          <t>NOAH KAHAN - THE GREAT DIVIDE TOUR</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/640/just-like-heaven</t>
+          <t>https://www.rosebowlstadium.com/events/details/633/noah-kahan-the-great-divide-tour</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>08/22/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GUNS N’ ROSES</t>
+          <t>Just Like Heaven</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/579/guns-n'-roses</t>
+          <t>https://www.rosebowlstadium.com/events/details/640/just-like-heaven</t>
         </is>
       </c>
     </row>
@@ -15021,130 +15021,130 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09/12/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4:15 PM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN DIEGO STATE VS UCLA</t>
+          <t>GUNS N’ ROSES</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/594/san-diego-state-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/579/guns-n'-roses</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09/13/2026</t>
+          <t>09/12/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>4:15 PM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>SAN DIEGO STATE VS UCLA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/604/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/594/san-diego-state-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09/19/2026</t>
+          <t>09/13/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PURDUE VS UCLA</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/595/purdue-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/604/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10/11/2026</t>
+          <t>09/19/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>PURDUE VS UCLA</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/605/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/595/purdue-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10/17/2026</t>
+          <t>10/11/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WISCONSIN VS UCLA</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/627/wisconsin-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/605/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10/24/2026</t>
+          <t>10/17/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MICHIGAN STATE VS UCLA</t>
+          <t>WISCONSIN VS UCLA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/628/michigan-state-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/627/wisconsin-vs-ucla</t>
         </is>
       </c>
     </row>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10/31/2026</t>
+          <t>10/24/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -15193,159 +15193,159 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NEVADA VS UCLA</t>
+          <t>MICHIGAN STATE VS UCLA</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/629/nevada-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/628/michigan-state-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>10/31/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>NEVADA VS UCLA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/606/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/629/nevada-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11/13/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ILLINOIS VS UCLA</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/630/illinois-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/606/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11/28/2026</t>
+          <t>11/13/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>USC VS UCLA</t>
+          <t>ILLINOIS VS UCLA</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/631/usc-vs-ucla</t>
+          <t>https://www.rosebowlstadium.com/events/details/630/illinois-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12/13/2026</t>
+          <t>11/28/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>USC VS UCLA</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/607/rose-bowl-flea-market</t>
+          <t>https://www.rosebowlstadium.com/events/details/631/usc-vs-ucla</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12/26/2026</t>
+          <t>12/13/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HOLIDAY TOURS</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/484/holiday-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/607/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12/27/2026</t>
+          <t>12/26/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -15360,19 +15360,19 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/485/holiday-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/484/holiday-tours</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12/28/2026</t>
+          <t>12/27/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -15387,19 +15387,19 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/486/holiday-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/485/holiday-tours</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01/02/2027</t>
+          <t>12/28/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/487/holiday-tours</t>
+          <t>https://www.rosebowlstadium.com/events/details/486/holiday-tours</t>
         </is>
       </c>
     </row>
@@ -15436,37 +15436,64 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HOLIDAY TOURS (duplicate)</t>
+          <t>HOLIDAY TOURS</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/647/holiday-tours-(duplicate)</t>
+          <t>https://www.rosebowlstadium.com/events/details/487/holiday-tours</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>01/02/2027</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HOLIDAY TOURS (duplicate)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rosebowlstadium.com/events/details/647/holiday-tours-(duplicate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>01/17/2027</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Rose Bowl Half Marathon &amp; 5K</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>https://www.rosebowlstadium.com/events/details/626/rose-bowl-half-marathon-and-5k</t>
         </is>
@@ -15504,6 +15531,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1722,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1762,120 +1762,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Human League – Soft Cell, Alison Moyet</t>
+          <t>37th Mariachi USA with Fireworks</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4283/2026-06-04/the-human-league</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4274/2026-06-06/37th-mariachi-usa-with-fireworks</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>37th Mariachi USA with Fireworks</t>
+          <t>Paul Simon</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4274/2026-06-06/37th-mariachi-usa-with-fireworks</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4359/2026-06-07/paul-simon</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paul Simon</t>
+          <t>Rod Stewart – Richard Marx</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4359/2026-06-07/paul-simon</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4258/2026-06-10/rod-stewart</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rod Stewart – Richard Marx</t>
+          <t>Blue Note Jazz Festival – Day One: Saturday</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4258/2026-06-10/rod-stewart</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4273/2026-06-13/blue-note-jazz-festival</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/14/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1885,51 +1885,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Blue Note Jazz Festival – Day One: Saturday</t>
+          <t>Blue Note Jazz Festival – Day Two: Sunday</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4273/2026-06-13/blue-note-jazz-festival</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4291/2026-06-14/blue-note-jazz-festival</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06/14/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Blue Note Jazz Festival – Day Two: Sunday</t>
+          <t>Chance the Rapper – A Juneteenth Celebration</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4291/2026-06-14/blue-note-jazz-festival</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4292/2026-06-19/chance-the-rapper</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1939,78 +1939,78 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chance the Rapper – A Juneteenth Celebration</t>
+          <t>Opening Night at the Bowl: The Best of Broadway</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4292/2026-06-19/chance-the-rapper</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4247/2026-06-20/opening-night-at-the-bowl-the-best-of-broadway</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/21/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Opening Night at the Bowl: The Best of Broadway</t>
+          <t>Reggae Night XXIV – Ziggy Marley, Burning Spear, Zuri Marley, KCRW Festival</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4247/2026-06-20/opening-night-at-the-bowl-the-best-of-broadway</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4293/2026-06-21/reggae-night-xxiv</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06/21/2026</t>
+          <t>06/24/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Reggae Night XXIV – Ziggy Marley, Burning Spear, Zuri Marley, KCRW Festival</t>
+          <t>The Tabernacle Choir at Temple Square: Songs of Hope Benefit Concert</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4293/2026-06-21/reggae-night-xxiv</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4838/2026-06-24/the-tabernacle-choir-at-temple-square-songs-of-hope-benefit-concert</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>06/24/2026</t>
+          <t>06/25/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2025,46 +2025,46 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4838/2026-06-24/the-tabernacle-choir-at-temple-square-songs-of-hope-benefit-concert</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4839/2026-06-25/the-tabernacle-choir-at-temple-square-songs-of-hope-benefit-concert</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>06/25/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The Tabernacle Choir at Temple Square: Songs of Hope Benefit Concert</t>
+          <t>A Roots Picnic Experience – A Great Night in Hip-Hop</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4839/2026-06-25/the-tabernacle-choir-at-temple-square-songs-of-hope-benefit-concert</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4248/2026-06-27/a-roots-picnic-experience</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2074,24 +2074,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A Roots Picnic Experience – A Great Night in Hip-Hop</t>
+          <t>July Fourth Fireworks Spectacular with The Beach Boys – with Special Guest John Stamos</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4248/2026-06-27/a-roots-picnic-experience</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4249/2026-07-02/july-fourth-fireworks-spectacular-with-the-beach-boys</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4249/2026-07-02/july-fourth-fireworks-spectacular-with-the-beach-boys</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4250/2026-07-03/july-fourth-fireworks-spectacular-with-the-beach-boys</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2133,19 +2133,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4250/2026-07-03/july-fourth-fireworks-spectacular-with-the-beach-boys</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4251/2026-07-04/july-fourth-fireworks-spectacular-with-the-beach-boys</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2155,51 +2155,51 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>July Fourth Fireworks Spectacular with The Beach Boys – with Special Guest John Stamos</t>
+          <t>Herb Alpert &amp; The Tijuana Brass &amp; Other Delights</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4251/2026-07-04/july-fourth-fireworks-spectacular-with-the-beach-boys</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4294/2026-07-05/herb-alpert-the-tijuana-brass-other-delights</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Herb Alpert &amp; The Tijuana Brass &amp; Other Delights</t>
+          <t>Wilkins Conducts Bernstein &amp; Ellington</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4294/2026-07-05/herb-alpert-the-tijuana-brass-other-delights</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4295/2026-07-08/wilkins-conducts-bernstein-ellington</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2209,24 +2209,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wilkins Conducts Bernstein &amp; Ellington</t>
+          <t>The Classical World Cup</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4295/2026-07-08/wilkins-conducts-bernstein-ellington</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4296/2026-07-09/the-classical-world-cup</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The Classical World Cup</t>
+          <t>Music from the Films of Wes Anderson</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4296/2026-07-09/the-classical-world-cup</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4288/2026-07-10/music-from-the-films-of-wes-anderson</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2268,73 +2268,73 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4288/2026-07-10/music-from-the-films-of-wes-anderson</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4289/2026-07-11/music-from-the-films-of-wes-anderson</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/12/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Music from the Films of Wes Anderson</t>
+          <t>Music from the Films of Wes Anderson – KCRW Festival</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4289/2026-07-11/music-from-the-films-of-wes-anderson</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4534/2026-07-12/music-from-the-films-of-wes-anderson</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07/12/2026</t>
+          <t>07/14/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Music from the Films of Wes Anderson – KCRW Festival</t>
+          <t>Tchaikovsky &amp; Beethoven</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4534/2026-07-12/music-from-the-films-of-wes-anderson</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4297/2026-07-14/tchaikovsky-beethoven</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>07/15/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2344,24 +2344,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tchaikovsky &amp; Beethoven</t>
+          <t>Salsa Spectacular: Nathy Peluso &amp; Grupo Niche – El Marchante</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4297/2026-07-14/tchaikovsky-beethoven</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4298/2026-07-15/salsa-spectacular-nathy-peluso-grupo-niche</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07/15/2026</t>
+          <t>07/16/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2371,24 +2371,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Salsa Spectacular: Nathy Peluso &amp; Grupo Niche – El Marchante</t>
+          <t>Mozart &amp; Brahms</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4298/2026-07-15/salsa-spectacular-nathy-peluso-grupo-niche</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4299/2026-07-16/mozart-brahms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>07/16/2026</t>
+          <t>07/17/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2398,24 +2398,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mozart &amp; Brahms</t>
+          <t>Let the Sunshine In: The Music of ’69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4299/2026-07-16/mozart-brahms</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4300/2026-07-17/let-the-sunshine-in-the-music-of-69</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>07/17/2026</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2425,78 +2425,78 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Let the Sunshine In: The Music of ’69</t>
+          <t>Blues Traveler • Gin Blossoms – Spin Doctors</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4300/2026-07-17/let-the-sunshine-in-the-music-of-69</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4301/2026-07-18/blues-traveler-gin-blossoms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>07/18/2026</t>
+          <t>07/19/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Blues Traveler • Gin Blossoms – Spin Doctors</t>
+          <t>Bob Moses and Cannons: Afterglow Tour – Oxis, KCRW Festival</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4301/2026-07-18/blues-traveler-gin-blossoms</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4302/2026-07-19/bob-moses-and-cannons-afterglow-tour</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>07/19/2026</t>
+          <t>07/21/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bob Moses and Cannons: Afterglow Tour – Oxis, KCRW Festival</t>
+          <t>Joe Hisaishi Film Music Concert – Featuring Studio Ghibli &amp; More</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4302/2026-07-19/bob-moses-and-cannons-afterglow-tour</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4303/2026-07-21/joe-hisaishi-film-music-concert</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>07/21/2026</t>
+          <t>07/22/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2511,19 +2511,19 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4303/2026-07-21/joe-hisaishi-film-music-concert</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4304/2026-07-22/joe-hisaishi-film-music-concert</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>07/22/2026</t>
+          <t>07/23/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2538,19 +2538,19 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4304/2026-07-22/joe-hisaishi-film-music-concert</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4305/2026-07-23/joe-hisaishi-film-music-concert</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07/23/2026</t>
+          <t>07/24/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2560,24 +2560,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Joe Hisaishi Film Music Concert – Featuring Studio Ghibli &amp; More</t>
+          <t>Smokey Robinson &amp; Gladys Knight: Just the Two of Us</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4305/2026-07-23/joe-hisaishi-film-music-concert</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4259/2026-07-24/smokey-robinson-gladys-knight-just-the-two-of-us</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07/24/2026</t>
+          <t>07/25/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2592,73 +2592,73 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4259/2026-07-24/smokey-robinson-gladys-knight-just-the-two-of-us</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4260/2026-07-25/smokey-robinson-gladys-knight-just-the-two-of-us</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07/25/2026</t>
+          <t>07/26/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Smokey Robinson &amp; Gladys Knight: Just the Two of Us</t>
+          <t>Boris Brejcha with the Hollywood Bowl Orchestra – KCRW Festival</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4260/2026-07-25/smokey-robinson-gladys-knight-just-the-two-of-us</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4308/2026-07-26/boris-brejcha-with-the-hollywood-bowl-orchestra</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>07/26/2026</t>
+          <t>07/28/2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Boris Brejcha with the Hollywood Bowl Orchestra – KCRW Festival</t>
+          <t>Rhapsody in Blue&amp; Shostakovich</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4308/2026-07-26/boris-brejcha-with-the-hollywood-bowl-orchestra</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4309/2026-07-28/rhapsody-in-blue-shostakovich</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>07/28/2026</t>
+          <t>07/29/2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2668,24 +2668,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Rhapsody in Blue&amp; Shostakovich</t>
+          <t>Tower of Power and Preservation Hall Jazz Band</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4309/2026-07-28/rhapsody-in-blue-shostakovich</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4310/2026-07-29/tower-of-power-and-preservation-hall-jazz-band</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>07/29/2026</t>
+          <t>07/30/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2695,24 +2695,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tower of Power and Preservation Hall Jazz Band</t>
+          <t>Pictures at an Exhibition</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4310/2026-07-29/tower-of-power-and-preservation-hall-jazz-band</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4311/2026-07-30/pictures-at-an-exhibition</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>07/30/2026</t>
+          <t>07/31/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2722,24 +2722,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pictures at an Exhibition</t>
+          <t>Tchaikovsky Spectacular with Fireworks</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4311/2026-07-30/pictures-at-an-exhibition</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4312/2026-07-31/tchaikovsky-spectacular-with-fireworks</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2754,73 +2754,73 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4312/2026-07-31/tchaikovsky-spectacular-with-fireworks</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4313/2026-08-01/tchaikovsky-spectacular-with-fireworks</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>08/02/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tchaikovsky Spectacular with Fireworks</t>
+          <t>St. Vincent with the Hollywood Bowl Orchestra – Anoushka Shankar, KCRW Festival</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4313/2026-08-01/tchaikovsky-spectacular-with-fireworks</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4314/2026-08-02/st-vincent-with-the-hollywood-bowl-orchestra</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>08/02/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>St. Vincent with the Hollywood Bowl Orchestra – Anoushka Shankar, KCRW Festival</t>
+          <t>Mendelssohn &amp; Haydn</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4314/2026-08-02/st-vincent-with-the-hollywood-bowl-orchestra</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4315/2026-08-04/mendelssohn-haydn</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2830,24 +2830,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mendelssohn &amp; Haydn</t>
+          <t>ZZ Top – with Special Guest Cheap Trick</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4315/2026-08-04/mendelssohn-haydn</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4354/2026-08-05/zz-top</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2857,24 +2857,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ZZ Top – with Special Guest Cheap Trick</t>
+          <t>Brahms &amp; Bizet</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4354/2026-08-05/zz-top</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4316/2026-08-06/brahms-bizet</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2884,24 +2884,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Brahms &amp; Bizet</t>
+          <t>Counting Crows</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4316/2026-08-06/brahms-bizet</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4317/2026-08-07/counting-crows</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2916,73 +2916,73 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4317/2026-08-07/counting-crows</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4349/2026-08-08/counting-crows</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Counting Crows</t>
+          <t>How to Train Your Dragonin Concert</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4349/2026-08-08/counting-crows</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4319/2026-08-09/how-to-train-your-dragon-in-concert</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>How to Train Your Dragonin Concert</t>
+          <t>John Mellencamp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4319/2026-08-09/how-to-train-your-dragon-in-concert</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4277/2026-08-10/john-mellencamp</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>08/11/2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2992,78 +2992,78 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>John Mellencamp</t>
+          <t>Mozart Under the Stars</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4277/2026-08-10/john-mellencamp</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4320/2026-08-11/mozart-under-the-stars</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>08/11/2026</t>
+          <t>08/13/2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mozart Under the Stars</t>
+          <t>Santana – The Doobie Brothers</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4320/2026-08-11/mozart-under-the-stars</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4364/2026-08-13/santana</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>08/13/2026</t>
+          <t>08/14/2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Santana – The Doobie Brothers</t>
+          <t>Al Green – The Womack Sisters</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4364/2026-08-13/santana</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4321/2026-08-14/al-green</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>08/14/2026</t>
+          <t>08/15/2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3073,24 +3073,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Al Green – The Womack Sisters</t>
+          <t>Top Gun: Maverickin Concert</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4321/2026-08-14/al-green</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4353/2026-08-15/top-gun-maverick-in-concert</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>08/15/2026</t>
+          <t>08/16/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3100,78 +3100,78 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Top Gun: Maverickin Concert</t>
+          <t>YOASOBI</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4353/2026-08-15/top-gun-maverick-in-concert</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4844/2026-08-16/yoasobi</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>08/16/2026</t>
+          <t>08/17/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>YOASOBI</t>
+          <t>The Black Crowes &amp; Tedeschi Trucks Band – Whiskey Myers</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4844/2026-08-16/yoasobi</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4352/2026-08-17/the-black-crowes-tedeschi-trucks-band</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>08/17/2026</t>
+          <t>08/18/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>The Black Crowes &amp; Tedeschi Trucks Band – Whiskey Myers</t>
+          <t>Gershwin, Bernstein &amp; More</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4352/2026-08-17/the-black-crowes-tedeschi-trucks-band</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4323/2026-08-18/gershwin-bernstein-more</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>08/18/2026</t>
+          <t>08/19/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Gershwin, Bernstein &amp; More</t>
+          <t>Herbie Hancock Celebrates Miles Davis</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4323/2026-08-18/gershwin-bernstein-more</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4324/2026-08-19/herbie-hancock-celebrates-miles-davis</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>08/19/2026</t>
+          <t>08/20/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3208,24 +3208,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Herbie Hancock Celebrates Miles Davis</t>
+          <t>Celebrating Gustavo at the Bowl: Beethoven 9</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4324/2026-08-19/herbie-hancock-celebrates-miles-davis</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4325/2026-08-20/celebrating-gustavo-at-the-bowl-beethoven-9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>08/20/2026</t>
+          <t>08/21/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3235,24 +3235,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Celebrating Gustavo at the Bowl: Beethoven 9</t>
+          <t>Celebrating Gustavo at the Bowl: Dudamel's Playlist</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4325/2026-08-20/celebrating-gustavo-at-the-bowl-beethoven-9</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4326/2026-08-21/celebrating-gustavo-at-the-bowl-dudamels-playlist</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>08/21/2026</t>
+          <t>08/22/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3262,78 +3262,78 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Celebrating Gustavo at the Bowl: Dudamel's Playlist</t>
+          <t>Celebrating Gustavo at the Bowl: Foo Fighters with the LA Phil and YOLA</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4326/2026-08-21/celebrating-gustavo-at-the-bowl-dudamels-playlist</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4287/2026-08-22/celebrating-gustavo-at-the-bowl-foo-fighters-with-the-la-phil-and-yola</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>08/22/2026</t>
+          <t>08/23/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Celebrating Gustavo at the Bowl: Foo Fighters with the LA Phil and YOLA</t>
+          <t>Celebrating Gustavo at the Bowl: A Musical Legacy</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4287/2026-08-22/celebrating-gustavo-at-the-bowl-foo-fighters-with-the-la-phil-and-yola</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4361/2026-08-23/celebrating-gustavo-at-the-bowl-a-musical-legacy</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>08/23/2026</t>
+          <t>08/25/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Celebrating Gustavo at the Bowl: A Musical Legacy</t>
+          <t>Beethoven’s Fifth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4361/2026-08-23/celebrating-gustavo-at-the-bowl-a-musical-legacy</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4330/2026-08-25/beethovens-fifth</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>08/25/2026</t>
+          <t>08/27/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3343,24 +3343,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Beethoven’s Fifth</t>
+          <t>Rachmaninoff &amp; Adams</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4330/2026-08-25/beethovens-fifth</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4327/2026-08-27/rachmaninoff-adams</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>08/27/2026</t>
+          <t>08/28/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Rachmaninoff &amp; Adams</t>
+          <t>David Byrne: Who is the Sky?</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4327/2026-08-27/rachmaninoff-adams</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4328/2026-08-28/david-byrne-who-is-the-sky</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>08/28/2026</t>
+          <t>08/29/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3402,100 +3402,100 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4328/2026-08-28/david-byrne-who-is-the-sky</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4329/2026-08-29/david-byrne-who-is-the-sky</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>08/29/2026</t>
+          <t>08/30/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>6:30 PM</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>David Byrne: Who is the Sky?</t>
+          <t>Smooth Summer Jazz – The Commodores • Boney James, Sheila E.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4329/2026-08-29/david-byrne-who-is-the-sky</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4252/2026-08-30/smooth-summer-jazz</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>08/30/2026</t>
+          <t>08/31/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Smooth Summer Jazz – The Commodores • Boney James, Sheila E.</t>
+          <t>MUSE – Portugal. The Man, The Temper Trap</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4252/2026-08-30/smooth-summer-jazz</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4837/2026-08-31/muse</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>08/31/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MUSE – Portugal. The Man, The Temper Trap</t>
+          <t>Dvořák &amp; Bruch</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4837/2026-08-31/muse</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4331/2026-09-01/dvorak-bruch</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3505,24 +3505,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Dvořák &amp; Bruch</t>
+          <t>Amadeusin Concert</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4331/2026-09-01/dvorak-bruch</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4332/2026-09-03/amadeus-in-concert</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3532,24 +3532,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Amadeusin Concert</t>
+          <t>Maestro of the Movies:A Tribute to John Williams</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4332/2026-09-03/amadeus-in-concert</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4333/2026-09-04/maestro-of-the-movies-a-tribute-to-john-williams</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3564,24 +3564,24 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4333/2026-09-04/maestro-of-the-movies-a-tribute-to-john-williams</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4334/2026-09-05/maestro-of-the-movies-a-tribute-to-john-williams</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3591,46 +3591,46 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4334/2026-09-05/maestro-of-the-movies-a-tribute-to-john-williams</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4335/2026-09-06/maestro-of-the-movies-a-tribute-to-john-williams</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Maestro of the Movies:A Tribute to John Williams</t>
+          <t>Los Angeles Ballet at the Bowl</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4335/2026-09-06/maestro-of-the-movies-a-tribute-to-john-williams</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4336/2026-09-08/los-angeles-ballet-at-the-bowl</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3640,24 +3640,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Los Angeles Ballet at the Bowl</t>
+          <t>Buddy Guy 90 – with Special Guests Christone “Kingfish” Ingram and his Delta Jam</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4336/2026-09-08/los-angeles-ballet-at-the-bowl</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4337/2026-09-09/buddy-guy-90</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3667,24 +3667,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Buddy Guy 90 – with Special Guests Christone “Kingfish” Ingram and his Delta Jam</t>
+          <t>Ravel, Debussy &amp; Saint-Saëns</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4337/2026-09-09/buddy-guy-90</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4338/2026-09-10/ravel-debussy-saint-saens</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3694,24 +3694,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ravel, Debussy &amp; Saint-Saëns</t>
+          <t>Fireworks Finale:OneRepublic</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4338/2026-09-10/ravel-debussy-saint-saens</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4339/2026-09-11/fireworks-finale-onerepublic</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/12/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3726,73 +3726,73 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4339/2026-09-11/fireworks-finale-onerepublic</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4340/2026-09-12/fireworks-finale-onerepublic</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09/12/2026</t>
+          <t>09/13/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fireworks Finale:OneRepublic</t>
+          <t>Lucy Dacus with the Hollywood Bowl Orchestra – Cat Power, KCRW Festival</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4340/2026-09-12/fireworks-finale-onerepublic</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4341/2026-09-13/lucy-dacus-with-the-hollywood-bowl-orchestra</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>09/13/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lucy Dacus with the Hollywood Bowl Orchestra – Cat Power, KCRW Festival</t>
+          <t>Andrea Bocelli</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4341/2026-09-13/lucy-dacus-with-the-hollywood-bowl-orchestra</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4356/2026-09-15/andrea-bocelli</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3807,19 +3807,19 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4356/2026-09-15/andrea-bocelli</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4357/2026-09-16/andrea-bocelli</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3829,24 +3829,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Andrea Bocelli</t>
+          <t>Orville Peck</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4357/2026-09-16/andrea-bocelli</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4355/2026-09-18/orville-peck</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/19/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3856,78 +3856,78 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Orville Peck</t>
+          <t>Squeeze – with special guest ADAM ANT, and The English Beat</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4355/2026-09-18/orville-peck</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4343/2026-09-19/squeeze</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>09/19/2026</t>
+          <t>09/20/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Squeeze – with special guest ADAM ANT, and The English Beat</t>
+          <t>Gregory Alan Isakov with the Hollywood Bowl Orchestra – José González</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4343/2026-09-19/squeeze</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4344/2026-09-20/gregory-alan-isakov-with-the-hollywood-bowl-orchestra</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>09/20/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Gregory Alan Isakov with the Hollywood Bowl Orchestra – José González</t>
+          <t>Jazz at Lincoln Center Orchestra with Wynton Marsalis – John Coltrane 100th Celebration with Lakecia Benjamin</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4344/2026-09-20/gregory-alan-isakov-with-the-hollywood-bowl-orchestra</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4345/2026-09-23/jazz-at-lincoln-center-orchestra-with-wynton-marsalis</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3937,24 +3937,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Jazz at Lincoln Center Orchestra with Wynton Marsalis – John Coltrane 100th Celebration with Lakecia Benjamin</t>
+          <t>Jon Bellion</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4345/2026-09-23/jazz-at-lincoln-center-orchestra-with-wynton-marsalis</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4509/2026-09-24/jon-bellion</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3964,24 +3964,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Jon Bellion</t>
+          <t>The Concert:A Tribute to ABBA – MenAlive</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4509/2026-09-24/jon-bellion</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4254/2026-09-25/the-concert-a-tribute-to-abba</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/26/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3991,78 +3991,78 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>The Concert:A Tribute to ABBA – MenAlive</t>
+          <t>Rodgers &amp; Hammerstein’s The Sound of Music Sing-A-Long</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4254/2026-09-25/the-concert-a-tribute-to-abba</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4342/2026-09-26/rodgers-hammersteins-the-sound-of-music-sing-a-long</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>09/26/2026</t>
+          <t>09/27/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Rodgers &amp; Hammerstein’s The Sound of Music Sing-A-Long</t>
+          <t>Jon Batiste</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4342/2026-09-26/rodgers-hammersteins-the-sound-of-music-sing-a-long</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4346/2026-09-27/jon-batiste</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>09/27/2026</t>
+          <t>09/29/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Jon Batiste</t>
+          <t>Lauren Halsey'semajendatwith Erykah Badu – and DJ Pee .Wee (Anderson .Paak), and Charles Gaines Collective with Black Nile</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4346/2026-09-27/jon-batiste</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4843/2026-09-29/lauren-halseys-emajendat-with-erykah-badu</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>09/29/2026</t>
+          <t>09/30/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4072,51 +4072,51 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Lauren Halsey'semajendatwith Erykah Badu – and DJ Pee .Wee (Anderson .Paak), and Charles Gaines Collective with Black Nile</t>
+          <t>Rubén Blades &amp; Roberto Delgado Big Band: Fotografías Tour – Silvana Estrada</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4843/2026-09-29/lauren-halseys-emajendat-with-erykah-badu</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4347/2026-09-30/ruben-blades-roberto-delgado-big-band-fotografias-tour</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>09/30/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Rubén Blades &amp; Roberto Delgado Big Band: Fotografías Tour – Silvana Estrada</t>
+          <t>“The Hayley Williams Show”</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4347/2026-09-30/ruben-blades-roberto-delgado-big-band-fotografias-tour</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4885/2026-10-05/the-hayley-williams-show</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4131,105 +4131,105 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4885/2026-10-05/the-hayley-williams-show</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4888/2026-10-06/the-hayley-williams-show</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>“The Hayley Williams Show”</t>
+          <t>Empire of the Sun – Polo &amp; Pan, Midnight Gen</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4888/2026-10-06/the-hayley-williams-show</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4537/2026-10-08/empire-of-the-sun</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Empire of the Sun – Polo &amp; Pan, Midnight Gen</t>
+          <t>Mac DeMarco</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4537/2026-10-08/empire-of-the-sun</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4363/2026-10-09/mac-demarco</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mac DeMarco</t>
+          <t>Jack Johnson – Hermanos Gutiérrez</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4363/2026-10-09/mac-demarco</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4256/2026-10-10/jack-johnson</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>10/11/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4239,46 +4239,46 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4256/2026-10-10/jack-johnson</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4257/2026-10-11/jack-johnson</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>10/11/2026</t>
+          <t>10/15/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Jack Johnson – Hermanos Gutiérrez</t>
+          <t>Cynthia Erivo</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4257/2026-10-11/jack-johnson</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4891/2026-10-15/cynthia-erivo</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>10/15/2026</t>
+          <t>10/17/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4288,51 +4288,51 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cynthia Erivo</t>
+          <t>SmartLess Live with Jason Bateman, Sean Hayes, &amp; Will Arnett</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4891/2026-10-15/cynthia-erivo</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4841/2026-10-17/smartless-live-with-jason-bateman-sean-hayes-will-arnett</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>10/17/2026</t>
+          <t>10/21/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SmartLess Live with Jason Bateman, Sean Hayes, &amp; Will Arnett</t>
+          <t>My Chemical Romance</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4841/2026-10-17/smartless-live-with-jason-bateman-sean-hayes-will-arnett</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4231/2026-10-21/my-chemical-romance</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>10/21/2026</t>
+          <t>10/23/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4347,19 +4347,19 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4231/2026-10-21/my-chemical-romance</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4232/2026-10-23/my-chemical-romance</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>10/23/2026</t>
+          <t>10/24/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4374,46 +4374,46 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4232/2026-10-23/my-chemical-romance</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4233/2026-10-24/my-chemical-romance</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>10/24/2026</t>
+          <t>10/30/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>My Chemical Romance</t>
+          <t>My Chemical Romance – The Used</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4233/2026-10-24/my-chemical-romance</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4263/2026-10-30/my-chemical-romance</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10/30/2026</t>
+          <t>10/31/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4423,37 +4423,10 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>My Chemical Romance – The Used</t>
+          <t>My Chemical Romance – Thrice</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4263/2026-10-30/my-chemical-romance</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>10/31/2026</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>My Chemical Romance – Thrice</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>https://www.hollywoodbowl.com/events/performances/4264/2026-10-31/my-chemical-romance</t>
         </is>
@@ -4560,7 +4533,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4572,7 +4544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4618,39 +4590,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Hollywood Bowl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
+          <t>The Human League – Soft Cell, Alison Moyet</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4283/2026-06-04/the-human-league</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4665,17 +4637,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Society of Nuclear Medicine and Molecular Imaging Annual Meeting 2026</t>
+          <t>Los Angeles Sparks vs Las Vegas Aces – Commissioner's Cup</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/society-of-nuclear-medicine-and-molecular-imaging-annual-meeting-2026</t>
+          <t>https://www.cryptoarena.com/events/detail/sparksaces060226</t>
         </is>
       </c>
     </row>
@@ -4687,12 +4659,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4714,71 +4686,71 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>05/31/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>vs. Philadelphia Phillies</t>
+          <t>Society of Nuclear Medicine and Molecular Imaging Annual Meeting 2026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823944</t>
+          <t>https://www.laconventioncenter.com/events/detail/society-of-nuclear-medicine-and-molecular-imaging-annual-meeting-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>05/31/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mexico vs Australia</t>
+          <t>vs. Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/635/mexico-vs-australia</t>
+          <t>https://www.mlb.com/gameday/823944</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4793,24 +4765,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Society of Nuclear Medicine and Molecular Imaging Annual Meeting 2026</t>
+          <t>Mexico vs Australia</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/society-of-nuclear-medicine-and-molecular-imaging-annual-meeting-2026</t>
+          <t>https://www.rosebowlstadium.com/events/details/635/mexico-vs-australia</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4825,24 +4797,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>vs. Philadelphia Phillies</t>
+          <t>Society of Nuclear Medicine and Molecular Imaging Annual Meeting 2026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823945</t>
+          <t>https://www.laconventioncenter.com/events/detail/society-of-nuclear-medicine-and-molecular-imaging-annual-meeting-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hollywood Bowl</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4857,56 +4829,56 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pitbull – Lil Jon</t>
+          <t>vs. Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://www.hollywoodbowl.com/events/performances/4278/2026-05-30/pitbull</t>
+          <t>https://www.mlb.com/gameday/823945</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Hollywood Bowl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>05/29/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VIP Fan Day MexTour Live</t>
+          <t>Pitbull – Lil Jon</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/646/vip-fan-day-mextour-live</t>
+          <t>https://www.hollywoodbowl.com/events/performances/4278/2026-05-30/pitbull</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4921,17 +4893,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7:15 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>vs. Philadelphia Phillies</t>
+          <t>VIP Fan Day MexTour Live</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823946</t>
+          <t>https://www.rosebowlstadium.com/events/details/646/vip-fan-day-mextour-live</t>
         </is>
       </c>
     </row>
@@ -4943,27 +4915,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>05/27/2026</t>
+          <t>05/29/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>7:15 PM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>vs. Colorado Rockies</t>
+          <t>vs. Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823947</t>
+          <t>https://www.mlb.com/gameday/823946</t>
         </is>
       </c>
     </row>
@@ -4975,12 +4947,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>05/27/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4995,7 +4967,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823949</t>
+          <t>https://www.mlb.com/gameday/823947</t>
         </is>
       </c>
     </row>
@@ -5007,17 +4979,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>05/25/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5027,71 +4999,71 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823948</t>
+          <t>https://www.mlb.com/gameday/823949</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>05/21/2026</t>
+          <t>05/25/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Romeo Santos &amp; Prince Royce</t>
+          <t>vs. Colorado Rockies</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/romeosantosprinceroyce052126</t>
+          <t>https://www.mlb.com/gameday/823948</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>05/20/2026</t>
+          <t>05/21/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00PM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FLORENCE + THE MACHINE</t>
+          <t>Romeo Santos &amp; Prince Royce</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/florence-the-machine/</t>
+          <t>https://www.cryptoarena.com/events/detail/romeosantosprinceroyce052126</t>
         </is>
       </c>
     </row>
@@ -5103,12 +5075,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/20/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5123,24 +5095,24 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/florence-the-machine-2/</t>
+          <t>https://thekiaforum.com/event/florence-the-machine/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>05/18/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5150,83 +5122,83 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ATD 26 | Association for Talent Development Conference &amp; Expo</t>
+          <t>FLORENCE + THE MACHINE</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/atd-2026-association-for-talent-development-conference</t>
+          <t>https://thekiaforum.com/event/florence-the-machine-2/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>05/17/2026</t>
+          <t>05/18/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks vs Toronto Tempo</t>
+          <t>ATD 26 | Association for Talent Development Conference &amp; Expo</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/sparkstempo051726</t>
+          <t>https://www.laconventioncenter.com/events/detail/atd-2026-association-for-talent-development-conference</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/17/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DEMI LOVATO</t>
+          <t>Los Angeles Sparks vs Toronto Tempo</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/demi-lovato/</t>
+          <t>https://www.cryptoarena.com/events/detail/sparkstempo051726</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5246,29 +5218,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zipangu</t>
+          <t>DEMI LOVATO</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/578/zipangu</t>
+          <t>https://thekiaforum.com/event/demi-lovato/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5278,19 +5250,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LORDE</t>
+          <t>Zipangu</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lorde-3/</t>
+          <t>https://www.rosebowlstadium.com/events/details/578/zipangu</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5305,56 +5277,56 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks vs Toronto Tempo</t>
+          <t>LORDE</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/sparkstempo051526</t>
+          <t>https://thekiaforum.com/event/lorde-3/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>05/14/2026</t>
+          <t>05/15/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LORDE</t>
+          <t>Los Angeles Sparks vs Toronto Tempo</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lorde-2/</t>
+          <t>https://www.cryptoarena.com/events/detail/sparkstempo051526</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5369,56 +5341,56 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>vs. San Francisco Giants</t>
+          <t>LORDE</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823950</t>
+          <t>https://thekiaforum.com/event/lorde-2/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>05/13/2026</t>
+          <t>05/14/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks vs Indiana Fever</t>
+          <t>vs. San Francisco Giants</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/sparksfever051326</t>
+          <t>https://www.mlb.com/gameday/823950</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5433,17 +5405,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>vs. San Francisco Giants</t>
+          <t>Los Angeles Sparks vs Indiana Fever</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823952</t>
+          <t>https://www.cryptoarena.com/events/detail/sparksfever051326</t>
         </is>
       </c>
     </row>
@@ -5455,12 +5427,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/13/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5475,7 +5447,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823951</t>
+          <t>https://www.mlb.com/gameday/823952</t>
         </is>
       </c>
     </row>
@@ -5487,12 +5459,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5507,46 +5479,46 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823953</t>
+          <t>https://www.mlb.com/gameday/823951</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Netflix is a Joke Presents: Nate Bargatze</t>
+          <t>vs. San Francisco Giants</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3431?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=nate_bargatze_260510</t>
+          <t>https://www.mlb.com/gameday/823953</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5561,24 +5533,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Netflix is a Joke Presents: Nate Bargatze</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/600/rose-bowl-flea-market</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3431?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=nate_bargatze_260510</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5593,24 +5565,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks vs Las Vegas Aces</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/sparksaces051026</t>
+          <t>https://www.rosebowlstadium.com/events/details/600/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5625,56 +5597,56 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>vs. Atlanta Braves</t>
+          <t>Los Angeles Sparks vs Las Vegas Aces</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823954</t>
+          <t>https://www.cryptoarena.com/events/detail/sparksaces051026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Netflix is a Joke Presents: Nate Bargatze</t>
+          <t>vs. Atlanta Braves</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3430?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=nate_bargatze_260509</t>
+          <t>https://www.mlb.com/gameday/823954</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5689,56 +5661,56 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>vs. Atlanta Braves</t>
+          <t>Netflix is a Joke Presents: Nate Bargatze</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823955</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3430?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=nate_bargatze_260509</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Los Angeles Pokémon Regional Championships</t>
+          <t>vs. Atlanta Braves</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/los-angeles-pokemon-regional-championships</t>
+          <t>https://www.mlb.com/gameday/823955</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5753,49 +5725,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>vs. Atlanta Braves</t>
+          <t>Los Angeles Pokémon Regional Championships</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823957</t>
+          <t>https://www.laconventioncenter.com/events/detail/los-angeles-pokemon-regional-championships</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Netflix is a Joke Presents: Kill Tony</t>
+          <t>vs. Atlanta Braves</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3435?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kill_tony_260507</t>
+          <t>https://www.mlb.com/gameday/823957</t>
         </is>
       </c>
     </row>
@@ -5807,59 +5779,59 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Netflix is a Joke Presents: Katt Williams</t>
+          <t>Netflix is a Joke Presents: Kill Tony</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3382?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=katt_williams_260505</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3435?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=kill_tony_260507</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>98th Annual AAAE Conference &amp; Exposition</t>
+          <t>Netflix is a Joke Presents: Katt Williams</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/98th-annual-aaae-conference-exposition</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3382?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=katt_williams_260505</t>
         </is>
       </c>
     </row>
@@ -5886,29 +5858,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Display Week 2026</t>
+          <t>98th Annual AAAE Conference &amp; Exposition</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/society-for-information-display-week-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/98th-annual-aaae-conference-exposition</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5918,19 +5890,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CHARLIE PUTH</t>
+          <t>Display Week 2026</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/charlie-puth/</t>
+          <t>https://www.laconventioncenter.com/events/detail/society-for-information-display-week-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5945,17 +5917,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>vs. Miami Marlins</t>
+          <t>CHARLIE PUTH</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823958</t>
+          <t>https://thekiaforum.com/event/charlie-puth/</t>
         </is>
       </c>
     </row>
@@ -5967,17 +5939,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>12:10 PM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5987,46 +5959,46 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823956</t>
+          <t>https://www.mlb.com/gameday/823958</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>04/27/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HelmsBriscoe - 2026 Annual Business Conference (ABC)</t>
+          <t>vs. Miami Marlins</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/helmsbriscoe-2026-annual-business-conference-abc</t>
+          <t>https://www.mlb.com/gameday/823956</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6041,56 +6013,56 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>vs. Miami Marlins</t>
+          <t>HelmsBriscoe - 2026 Annual Business Conference (ABC)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823961</t>
+          <t>https://www.laconventioncenter.com/events/detail/helmsbriscoe-2026-annual-business-conference-abc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>04/26/2026</t>
+          <t>04/27/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Real Salt Lake</t>
+          <t>vs. Miami Marlins</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-real-salt-lake</t>
+          <t>https://www.mlb.com/gameday/823961</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6105,17 +6077,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>vs. Chicago Cubs</t>
+          <t>LA Galaxy vs Real Salt Lake</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823959</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-real-salt-lake</t>
         </is>
       </c>
     </row>
@@ -6127,17 +6099,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>04/26/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4:15 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6147,46 +6119,46 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823960</t>
+          <t>https://www.mlb.com/gameday/823959</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>04/24/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>4:15 PM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>THIRD DAY</t>
+          <t>vs. Chicago Cubs</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/third-day/</t>
+          <t>https://www.mlb.com/gameday/823960</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6201,66 +6173,66 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7:15 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>vs. Chicago Cubs</t>
+          <t>THIRD DAY</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823962</t>
+          <t>https://thekiaforum.com/event/third-day/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>04/22/2026</t>
+          <t>04/24/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:15 PM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>The NAMA Show 2026</t>
+          <t>vs. Chicago Cubs</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/the-nama-show-2026</t>
+          <t>https://www.mlb.com/gameday/823962</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/22/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6270,76 +6242,76 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ELECTRIC CALLBOY</t>
+          <t>The NAMA Show 2026</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/electric-callboy/</t>
+          <t>https://www.laconventioncenter.com/events/detail/the-nama-show-2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>04/19/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Masters of Taste</t>
+          <t>ELECTRIC CALLBOY</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/624/masters-of-taste</t>
+          <t>https://thekiaforum.com/event/electric-callboy/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>04/16/2026</t>
+          <t>04/19/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SBMT World Congress 2026</t>
+          <t>Masters of Taste</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/sbmt-world-congress-2026</t>
+          <t>https://www.rosebowlstadium.com/events/details/624/masters-of-taste</t>
         </is>
       </c>
     </row>
@@ -6351,12 +6323,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
+          <t>04/16/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6366,19 +6338,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AOA of California Trade Show</t>
+          <t>SBMT World Congress 2026</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/aoa-of-california-trade-show-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/sbmt-world-congress-2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6393,17 +6365,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>vs. New York Mets</t>
+          <t>AOA of California Trade Show</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823963</t>
+          <t>https://www.laconventioncenter.com/events/detail/aoa-of-california-trade-show-2026</t>
         </is>
       </c>
     </row>
@@ -6415,12 +6387,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/15/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6435,7 +6407,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823965</t>
+          <t>https://www.mlb.com/gameday/823963</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6419,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>04/13/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6467,46 +6439,46 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823964</t>
+          <t>https://www.mlb.com/gameday/823965</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>04/13/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Golden State Warriors vs LA Clippers</t>
+          <t>vs. New York Mets</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2695?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260412</t>
+          <t>https://www.mlb.com/gameday/823964</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6521,24 +6493,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Golden State Warriors vs LA Clippers</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/599/rose-bowl-flea-market</t>
+          <t>https://intuitdome.com/events/event-schedule/2695?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260412</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6553,24 +6525,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Utah Jazz vs Los Angeles Lakers</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersjazz041226</t>
+          <t>https://www.rosebowlstadium.com/events/details/599/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6585,56 +6557,56 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1:10 PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>vs. Texas Rangers</t>
+          <t>Utah Jazz vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823966</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersjazz041226</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>1:10 PM</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>We Them One's Comedy Tour</t>
+          <t>vs. Texas Rangers</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3131?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wethemones_260411</t>
+          <t>https://www.mlb.com/gameday/823966</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6649,24 +6621,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Edmonton Oilers vs Los Angeles Kings</t>
+          <t>We Them One's Comedy Tour</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsoilers041126</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3131?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=wethemones_260411</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6681,24 +6653,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Los Angeles Career Forum 2026</t>
+          <t>Edmonton Oilers vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/los-angeles-career-forum-2026</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsoilers041126</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6713,56 +6685,56 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>vs. Texas Rangers</t>
+          <t>Los Angeles Career Forum 2026</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823967</t>
+          <t>https://www.laconventioncenter.com/events/detail/los-angeles-career-forum-2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>REIK</t>
+          <t>vs. Texas Rangers</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/reik/</t>
+          <t>https://www.mlb.com/gameday/823967</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6777,24 +6749,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Phoenix Suns vs Los Angeles Lakers</t>
+          <t>REIK</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerssuns041026</t>
+          <t>https://thekiaforum.com/event/reik/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6809,88 +6781,88 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>vs. Texas Rangers</t>
+          <t>Phoenix Suns vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823968</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerssuns041026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vancouver Canucks vs Los Angeles Kings</t>
+          <t>vs. Texas Rangers</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingscanucks040926</t>
+          <t>https://www.mlb.com/gameday/823968</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder vs LA Clippers</t>
+          <t>Vancouver Canucks vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2694?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260408</t>
+          <t>https://www.cryptoarena.com/events/detail/kingscanucks040926</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6905,56 +6877,56 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026 AERA Annual Meeting</t>
+          <t>Oklahoma City Thunder vs LA Clippers</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/2026-aera-annual-meeting</t>
+          <t>https://intuitdome.com/events/event-schedule/2694?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260408</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dallas Mavericks vs LA Clippers</t>
+          <t>2026 AERA Annual Meeting</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2672?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260407</t>
+          <t>https://www.laconventioncenter.com/events/detail/2026-aera-annual-meeting</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6969,17 +6941,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
+          <t>Dallas Mavericks vs LA Clippers</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersthunder040726</t>
+          <t>https://intuitdome.com/events/event-schedule/2672?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260407</t>
         </is>
       </c>
     </row>
@@ -6991,12 +6963,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7006,51 +6978,51 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nashville Predators vs Los Angeles Kings</t>
+          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingspreds040626</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersthunder040726</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LANY</t>
+          <t>Nashville Predators vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3066?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lany_260404</t>
+          <t>https://www.cryptoarena.com/events/detail/kingspreds040626</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7070,19 +7042,19 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Minnesota United FC</t>
+          <t>LANY</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-minnesota-united-fc</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3066?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=lany_260404</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7097,56 +7069,56 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Toronto Maple Leafs vs Los Angeles Kings</t>
+          <t>LA Galaxy vs Minnesota United FC</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsleafs040426</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-minnesota-united-fc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>San Antonio Spurs vs LA Clippers</t>
+          <t>Toronto Maple Leafs vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2671?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260402</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsleafs040426</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7161,24 +7133,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nashville Predators vs Los Angeles Kings</t>
+          <t>San Antonio Spurs vs LA Clippers</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingspreds040226</t>
+          <t>https://intuitdome.com/events/event-schedule/2671?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260402</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L.A. Memorial Coliseum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7193,56 +7165,56 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>March for Babies</t>
+          <t>Nashville Predators vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/march-for-babies-2026/</t>
+          <t>https://www.cryptoarena.com/events/detail/kingspreds040226</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>L.A. Memorial Coliseum</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St Louis Blues vs Los Angeles Kings</t>
+          <t>March for Babies</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsblues040126</t>
+          <t>https://www.lacoliseum.com/events/march-for-babies-2026/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L.A. Memorial Coliseum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7257,24 +7229,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hope Fest LA</t>
+          <t>St Louis Blues vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/hopefest-la-2026/</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsblues040126</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>L.A. Memorial Coliseum</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7289,56 +7261,56 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>5:20 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>vs. Cleveland Guardians</t>
+          <t>Hope Fest LA</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823970</t>
+          <t>https://www.lacoliseum.com/events/hopefest-la-2026/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>5:20 PM</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers vs LA Clippers</t>
+          <t>vs. Cleveland Guardians</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2693?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260331</t>
+          <t>https://www.mlb.com/gameday/823970</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7353,24 +7325,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>JACKSON WANG</t>
+          <t>Portland Trail Blazers vs LA Clippers</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/jackson-wang/</t>
+          <t>https://intuitdome.com/events/event-schedule/2693?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260331</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7385,24 +7357,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers vs Los Angeles Lakers</t>
+          <t>JACKSON WANG</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerscavs033126</t>
+          <t>https://thekiaforum.com/event/jackson-wang/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7417,56 +7389,56 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>vs. Cleveland Guardians</t>
+          <t>Cleveland Cavaliers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823969</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerscavs033126</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>03/30/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Washington Wizards vs Los Angeles Lakers</t>
+          <t>vs. Cleveland Guardians</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerswizards033026</t>
+          <t>https://www.mlb.com/gameday/823969</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7481,88 +7453,88 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>vs. Cleveland Guardians</t>
+          <t>Washington Wizards vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823972</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerswizards033026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>03/29/2026</t>
+          <t>03/30/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Walk MS: Greater Los Angeles</t>
+          <t>vs. Cleveland Guardians</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/589/walk-ms:-greater-los-angeles</t>
+          <t>https://www.mlb.com/gameday/823972</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>03/29/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Utah Mammoth vs Los Angeles Kings</t>
+          <t>Walk MS: Greater Los Angeles</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsmammoth032826</t>
+          <t>https://www.rosebowlstadium.com/events/details/589/walk-ms:-greater-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7577,24 +7549,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Victory Gymnastics - XCEL State Championship</t>
+          <t>Utah Mammoth vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/victory-gymnastics-xcel-state-championship</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsmammoth032826</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7609,56 +7581,56 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>vs. Arizona Diamondbacks</t>
+          <t>Victory Gymnastics - XCEL State Championship</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823973</t>
+          <t>https://www.laconventioncenter.com/events/detail/victory-gymnastics-xcel-state-championship</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>03/27/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>6:10 PM</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brooklyn Nets vs Los Angeles Lakers</t>
+          <t>vs. Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersnets032726</t>
+          <t>https://www.mlb.com/gameday/823973</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7673,24 +7645,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>American Pharmacists Association (APhA) Annual Meeting &amp; Exposition 2026</t>
+          <t>Brooklyn Nets vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/american-pharmacists-association</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersnets032726</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7705,56 +7677,56 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>vs. Arizona Diamondbacks</t>
+          <t>American Pharmacists Association (APhA) Annual Meeting &amp; Exposition 2026</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823971</t>
+          <t>https://www.laconventioncenter.com/events/detail/american-pharmacists-association</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>03/27/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BAD OMENS</t>
+          <t>vs. Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/bad-omens/</t>
+          <t>https://www.mlb.com/gameday/823971</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Dodger Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7769,56 +7741,56 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>vs. Arizona Diamondbacks</t>
+          <t>BAD OMENS</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>https://www.mlb.com/gameday/823974</t>
+          <t>https://thekiaforum.com/event/bad-omens/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Dodger Stadium</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>03/25/2026</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Toronto Raptors vs LA Clippers</t>
+          <t>vs. Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2670?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260325</t>
+          <t>https://www.mlb.com/gameday/823974</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7833,120 +7805,120 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HR Star Conference 2026</t>
+          <t>Toronto Raptors vs LA Clippers</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/hr-star-conference-2026</t>
+          <t>https://intuitdome.com/events/event-schedule/2670?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260325</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>03/23/2026</t>
+          <t>03/25/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks vs LA Clippers</t>
+          <t>HR Star Conference 2026</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2668?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260323</t>
+          <t>https://www.laconventioncenter.com/events/detail/hr-star-conference-2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>03/22/2026</t>
+          <t>03/23/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>B2K &amp; BOW WOW</t>
+          <t>Milwaukee Bucks vs LA Clippers</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/b2k-bow-wow/</t>
+          <t>https://intuitdome.com/events/event-schedule/2668?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260323</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/22/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>7 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gabriel "Fluffy" Iglesias &amp; Jo Koy</t>
+          <t>B2K &amp; BOW WOW</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/gabriel-fluffy-iglesias-jo-koy</t>
+          <t>https://thekiaforum.com/event/b2k-bow-wow/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7961,24 +7933,24 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>7 PM</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Breakthrough T1D, Walk Los Angeles</t>
+          <t>Gabriel "Fluffy" Iglesias &amp; Jo Koy</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/625/breakthrough-t1d-walk-los-angeles</t>
+          <t>https://www.sofistadium.com/events/detail/gabriel-fluffy-iglesias-jo-koy</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7993,56 +7965,56 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Buffalo Sabres vs Los Angeles Kings</t>
+          <t>Breakthrough T1D, Walk Los Angeles</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingssabres032126</t>
+          <t>https://www.rosebowlstadium.com/events/details/625/breakthrough-t1d-walk-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Peso Pluma</t>
+          <t>Buffalo Sabres vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3401?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=peso_pluma_260320</t>
+          <t>https://www.cryptoarena.com/events/detail/kingssabres032126</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8057,152 +8029,152 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CONAN GRAY</t>
+          <t>Peso Pluma</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/conan-gray/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3401?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=peso_pluma_260320</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>03/19/2026</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Philadelphia Flyers vs Los Angeles Kings</t>
+          <t>CONAN GRAY</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsflyers031926</t>
+          <t>https://thekiaforum.com/event/conan-gray/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>03/16/2026</t>
+          <t>03/19/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>San Antonio Spurs vs LA Clippers</t>
+          <t>Philadelphia Flyers vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2692?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260316</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsflyers031926</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>03/15/2026</t>
+          <t>03/16/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AEW presents REVOLUTION</t>
+          <t>San Antonio Spurs vs LA Clippers</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/aew031526</t>
+          <t>https://intuitdome.com/events/event-schedule/2692?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260316</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/15/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sacramento Kings vs LA Clippers</t>
+          <t>AEW presents REVOLUTION</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2691?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260314</t>
+          <t>https://www.cryptoarena.com/events/detail/aew031526</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8217,24 +8189,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6:30 PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Sporting KC</t>
+          <t>Sacramento Kings vs LA Clippers</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-kc</t>
+          <t>https://intuitdome.com/events/event-schedule/2691?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260314</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8249,56 +8221,56 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>6:30 PM</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Denver Nuggets vs Los Angeles Lakers</t>
+          <t>LA Galaxy vs Sporting KC</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersnuggets031426</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-kc</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>03/13/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chicago Bulls vs LA Clippers</t>
+          <t>Denver Nuggets vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2666?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260313</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersnuggets031426</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8313,184 +8285,184 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>Chicago Bulls vs LA Clippers</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/miguel/</t>
+          <t>https://intuitdome.com/events/event-schedule/2666?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260313</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>03/12/2026</t>
+          <t>03/13/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chicago Bulls vs Los Angeles Lakers</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersbulls031226</t>
+          <t>https://thekiaforum.com/event/miguel/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>03/11/2026</t>
+          <t>03/12/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves vs LA Clippers</t>
+          <t>Chicago Bulls vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2690?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260311</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersbulls031226</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves vs Los Angeles Lakers</t>
+          <t>Minnesota Timberwolves vs LA Clippers</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerswolves031026</t>
+          <t>https://intuitdome.com/events/event-schedule/2690?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260311</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8:00PM</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>New York Knicks vs LA Clippers</t>
+          <t>Minnesota Timberwolves vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2665?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260309</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerswolves031026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>New York Knicks vs LA Clippers</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/598/rose-bowl-flea-market</t>
+          <t>https://intuitdome.com/events/event-schedule/2665?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260309</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8505,24 +8477,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>New York Knicks vs Los Angeles Lakers</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersknicks030826</t>
+          <t>https://www.rosebowlstadium.com/events/details/598/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8537,56 +8509,56 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>California Bridal &amp; Wedding Expo</t>
+          <t>New York Knicks vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/california-bridal-wedding-expo-14</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersknicks030826</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>6 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sip &amp; Stroll at SoFi Stadium</t>
+          <t>California Bridal &amp; Wedding Expo</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/sofi-tour-sip-wine-stroll-march-29</t>
+          <t>https://www.laconventioncenter.com/events/detail/california-bridal-wedding-expo-14</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8601,24 +8573,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6 PM</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>EXCISION</t>
+          <t>Sip &amp; Stroll at SoFi Stadium</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/excision/</t>
+          <t>https://www.sofistadium.com/events/detail/sofi-tour-sip-wine-stroll-march-29</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8633,24 +8605,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Montreal Canadiens vs Los Angeles Kings</t>
+          <t>EXCISION</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingscanadiens030726</t>
+          <t>https://thekiaforum.com/event/excision/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8665,34 +8637,34 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Black Men in White Coats Youth Summit 2026</t>
+          <t>Montreal Canadiens vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/black-men-in-white-coats-2026</t>
+          <t>https://www.cryptoarena.com/events/detail/kingscanadiens030726</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8702,19 +8674,19 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>EXCISION</t>
+          <t>Black Men in White Coats Youth Summit 2026</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/excision-2/</t>
+          <t>https://www.laconventioncenter.com/events/detail/black-men-in-white-coats-2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8729,24 +8701,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Indiana Pacers vs Los Angeles Lakers</t>
+          <t>EXCISION</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerspacer030626</t>
+          <t>https://thekiaforum.com/event/excision-2/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8761,88 +8733,88 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Victory Gymnastics - Victory Classic</t>
+          <t>Indiana Pacers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/victory-gymnastics-victory-classic</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerspacer030626</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>New York Islanders vs Los Angeles Kings</t>
+          <t>Victory Gymnastics - Victory Classic</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsislanders030526</t>
+          <t>https://www.laconventioncenter.com/events/detail/victory-gymnastics-victory-classic</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Indiana Pacers vs LA Clippers</t>
+          <t>New York Islanders vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2664?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260304</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsislanders030526</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8857,56 +8829,56 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MakeUp + Luxe Pack in Los Angeles 2026</t>
+          <t>Indiana Pacers vs LA Clippers</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/makeup-in-los-angeles-2026</t>
+          <t>https://intuitdome.com/events/event-schedule/2664?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260304</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans vs Los Angeles Lakers</t>
+          <t>MakeUp + Luxe Pack in Los Angeles 2026</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerspelicans030326</t>
+          <t>https://www.laconventioncenter.com/events/detail/makeup-in-los-angeles-2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8921,88 +8893,88 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Catersource &amp; The Special Event Expo</t>
+          <t>New Orleans Pelicans vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/catersource-the-special-event-expo</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerspelicans030326</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Colorado Avalanche vs Los Angeles Kings</t>
+          <t>Catersource &amp; The Special Event Expo</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsavs030226</t>
+          <t>https://www.laconventioncenter.com/events/detail/catersource-the-special-event-expo</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans vs LA Clippers</t>
+          <t>Colorado Avalanche vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2689?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260301</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsavs030226</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9017,24 +8989,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>The Michael J. Fox Foundation’s Los Angeles Run/Walk</t>
+          <t>New Orleans Pelicans vs LA Clippers</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/623/the-michael-j.-fox-foundation's-los-angeles-runwalk</t>
+          <t>https://intuitdome.com/events/event-schedule/2689?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260301</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9049,56 +9021,56 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sacramento Kings vs Los Angeles Lakers</t>
+          <t>The Michael J. Fox Foundation’s Los Angeles Run/Walk</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerskings030126</t>
+          <t>https://www.rosebowlstadium.com/events/details/623/the-michael-j.-fox-foundation's-los-angeles-runwalk</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ricardo Arjona</t>
+          <t>Sacramento Kings vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2819?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ricardo_arjona_260228</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerskings030126</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9113,24 +9085,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Charlotte FC</t>
+          <t>Ricardo Arjona</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-charlotte-fc-1</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2819?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ricardo_arjona_260228</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9145,24 +9117,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Calgary Flames vs Los Angeles Kings</t>
+          <t>LA Galaxy vs Charlotte FC</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsflames022826</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-charlotte-fc-1</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9177,17 +9149,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>El Sembrador Ministries - Metanoia de Mujeres</t>
+          <t>Calgary Flames vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/el-sembrador-ministries-metanoia-de-mujeres-2</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsflames022826</t>
         </is>
       </c>
     </row>
@@ -9214,12 +9186,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Spotlight Card Show</t>
+          <t>El Sembrador Ministries - Metanoia de Mujeres</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/spotlight-card-show</t>
+          <t>https://www.laconventioncenter.com/events/detail/el-sembrador-ministries-metanoia-de-mujeres-2</t>
         </is>
       </c>
     </row>
@@ -9246,29 +9218,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Import Expo x Cali Creaming</t>
+          <t>Spotlight Card Show</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/import-expo-x-cali-creaming</t>
+          <t>https://www.laconventioncenter.com/events/detail/spotlight-card-show</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>02/27/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9278,51 +9250,51 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>BRANDI CARLILE</t>
+          <t>Import Expo x Cali Creaming</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/brandi-carlile/</t>
+          <t>https://www.laconventioncenter.com/events/detail/import-expo-x-cali-creaming</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>02/27/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves vs LA Clippers</t>
+          <t>BRANDI CARLILE</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2663?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260226</t>
+          <t>https://thekiaforum.com/event/brandi-carlile/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9337,24 +9309,24 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Edmonton Oilers vs Los Angeles Kings</t>
+          <t>Minnesota Timberwolves vs LA Clippers</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsoilers022626</t>
+          <t>https://intuitdome.com/events/event-schedule/2663?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260226</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9369,34 +9341,34 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>MORAT</t>
+          <t>Edmonton Oilers vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsoilers022626</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9406,19 +9378,19 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Sporting San Miguelito</t>
+          <t>MORAT</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-san-miguelito</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3967?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=morat_270226</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9433,17 +9405,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vegas Golden Knights vs Los Angeles Kings</t>
+          <t>LA Galaxy vs Sporting San Miguelito</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingsknights022526</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-sporting-san-miguelito</t>
         </is>
       </c>
     </row>
@@ -9455,66 +9427,66 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>02/24/2026</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Orlando Magic vs Los Angeles Lakers</t>
+          <t>Vegas Golden Knights vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersmagic022426</t>
+          <t>https://www.cryptoarena.com/events/detail/kingsknights022526</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>02/23/2026</t>
+          <t>02/24/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>GHOST: Skeletour World Tour 2026</t>
+          <t>Orlando Magic vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2964?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ghost_260223</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersmagic022426</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9529,56 +9501,56 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>GHOST: Skeletour World Tour 2026</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-8/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2964?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=ghost_260223</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>02/23/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Orlando Magic vs LA Clippers</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2688?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260222</t>
+          <t>https://thekiaforum.com/event/lady-gaga-8/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9593,24 +9565,24 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>Orlando Magic vs LA Clippers</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-7/</t>
+          <t>https://intuitdome.com/events/event-schedule/2688?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260222</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9625,24 +9597,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>LA Galaxy vs New York City FC</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-york-city-fc</t>
+          <t>https://thekiaforum.com/event/lady-gaga-7/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Dignity Health Sports Park</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9657,17 +9629,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>LA Galaxy vs New York City FC</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/585/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.dignityhealthsportspark.com/events/detail/la-galaxy-vs-new-york-city-fc</t>
         </is>
       </c>
     </row>
@@ -9689,24 +9661,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/588/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/585/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9721,24 +9693,24 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Boston Celtics vs Los Angeles Lakers</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersceltics022226</t>
+          <t>https://www.rosebowlstadium.com/events/details/588/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9753,56 +9725,56 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ViVE 2026</t>
+          <t>Boston Celtics vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/vive-2026</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersceltics022226</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>8 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Los Bukis</t>
+          <t>ViVE 2026</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/los-bukis-february-21-2026</t>
+          <t>https://www.laconventioncenter.com/events/detail/vive-2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9817,24 +9789,24 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8 PM</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Los Tigres del Norte</t>
+          <t>Los Bukis</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2912?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=los_tigres_del_norte_260221</t>
+          <t>https://www.sofistadium.com/events/detail/los-bukis-february-21-2026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9849,17 +9821,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Los Tigres del Norte</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/584/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2912?utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=IDevents25&amp;utm_content=los_tigres_del_norte_260221</t>
         </is>
       </c>
     </row>
@@ -9881,56 +9853,56 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/587/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/584/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>8 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Los Bukis</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofistadium.com/events/detail/los-bukis-2026</t>
+          <t>https://www.rosebowlstadium.com/events/details/587/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -9945,24 +9917,24 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>8 PM</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Harlem Globetrotters</t>
+          <t>Los Bukis</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/2904</t>
+          <t>https://www.sofistadium.com/events/detail/los-bukis-2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -9977,24 +9949,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SABATON</t>
+          <t>Harlem Globetrotters</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/sabaton/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/2904</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10009,17 +9981,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>SABATON</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/583/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://thekiaforum.com/event/sabaton/</t>
         </is>
       </c>
     </row>
@@ -10041,24 +10013,24 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
+          <t>Mega Night at Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/586/pokemon-go-tour:-kalos-los-angeles</t>
+          <t>https://www.rosebowlstadium.com/events/details/583/mega-night-at-pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10073,56 +10045,56 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Los Angeles Clippers vs Los Angeles Lakers</t>
+          <t>Pokémon GO Tour: Kalos – Los Angeles</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersclippers022026</t>
+          <t>https://www.rosebowlstadium.com/events/details/586/pokemon-go-tour:-kalos-los-angeles</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Denver Nuggets vs LA Clippers</t>
+          <t>Los Angeles Clippers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2687?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260219</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersclippers022026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10137,17 +10109,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>LADY GAGA</t>
+          <t>Denver Nuggets vs LA Clippers</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-5/</t>
+          <t>https://intuitdome.com/events/event-schedule/2687?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260219</t>
         </is>
       </c>
     </row>
@@ -10159,12 +10131,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>02/18/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10179,7 +10151,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/lady-gaga-6/</t>
+          <t>https://thekiaforum.com/event/lady-gaga-5/</t>
         </is>
       </c>
     </row>
@@ -10191,12 +10163,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/18/2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10206,51 +10178,51 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>CARDI B</t>
+          <t>LADY GAGA</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/cardi-b-2/</t>
+          <t>https://thekiaforum.com/event/lady-gaga-6/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>75th NBA All-Star Game</t>
+          <t>CARDI B</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3002?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_game_260215</t>
+          <t>https://thekiaforum.com/event/cardi-b-2/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10265,56 +10237,56 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>CARDI B</t>
+          <t>75th NBA All-Star Game</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/cardi-b/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3002?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_game_260215</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/15/2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>All-Star Saturday</t>
+          <t>CARDI B</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3003?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_saturday_260214</t>
+          <t>https://thekiaforum.com/event/cardi-b/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10329,56 +10301,56 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>DJ CASSIDY'S PASS THE MIC LIVE!</t>
+          <t>All-Star Saturday</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/dj-cassidys-pass-the-mic-live/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3003?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=all_star_saturday_260214</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Castrol Rising Stars</t>
+          <t>DJ CASSIDY'S PASS THE MIC LIVE!</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3004?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=castrol_rising_stars_260213</t>
+          <t>https://thekiaforum.com/event/dj-cassidys-pass-the-mic-live/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10393,17 +10365,17 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>HBCU CLASSIC PRESENTED BY AT&amp;T</t>
+          <t>Castrol Rising Stars</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/hbcu-classic-presented-by-att/</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3004?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=All_Star26&amp;utm_content=castrol_rising_stars_260213</t>
         </is>
       </c>
     </row>
@@ -10430,19 +10402,19 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>RUFFLES CELEBRITY GAME</t>
+          <t>HBCU CLASSIC PRESENTED BY AT&amp;T</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/ruffles-celebrity-game/</t>
+          <t>https://thekiaforum.com/event/hbcu-classic-presented-by-att/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10462,29 +10434,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Banda MS de Sergio Lizarraga</t>
+          <t>RUFFLES CELEBRITY GAME</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/bandams021326</t>
+          <t>https://thekiaforum.com/event/ruffles-celebrity-game/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10494,19 +10466,19 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>NBA ALL-STAR PITCH COMPETITION</t>
+          <t>Banda MS de Sergio Lizarraga</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/nba-all-star-pitch-competition/</t>
+          <t>https://www.cryptoarena.com/events/detail/bandams021326</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -10521,24 +10493,24 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Dallas Mavericks vs Los Angeles Lakers</t>
+          <t>NBA ALL-STAR PITCH COMPETITION</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersmavs021226</t>
+          <t>https://thekiaforum.com/event/nba-all-star-pitch-competition/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10553,49 +10525,49 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>NBA Crossover: The Ultimate Fan Experience</t>
+          <t>Dallas Mavericks vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/nba-crossover-ultimate-fan-experience</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersmavs021226</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>San Antonio Spurs vs Los Angeles Lakers</t>
+          <t>NBA Crossover: The Ultimate Fan Experience</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersspurs021026</t>
+          <t>https://www.laconventioncenter.com/events/detail/nba-crossover-ultimate-fan-experience</t>
         </is>
       </c>
     </row>
@@ -10607,91 +10579,91 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
+          <t>San Antonio Spurs vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakersthuner020926</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersspurs021026</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Rose Bowl Stadium</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>ROSE BOWL FLEA MARKET</t>
+          <t>Oklahoma City Thunder vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>https://www.rosebowlstadium.com/events/details/597/rose-bowl-flea-market</t>
+          <t>https://www.cryptoarena.com/events/detail/lakersthuner020926</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rose Bowl Stadium</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Golden State Warriors vs Los Angeles Lakers</t>
+          <t>ROSE BOWL FLEA MARKET</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakerswarriors020726</t>
+          <t>https://www.rosebowlstadium.com/events/details/597/rose-bowl-flea-market</t>
         </is>
       </c>
     </row>
@@ -10703,66 +10675,66 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers vs Los Angeles Lakers</t>
+          <t>Golden State Warriors vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/lakers76ers020526</t>
+          <t>https://www.cryptoarena.com/events/detail/lakerswarriors020726</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers vs LA Clippers</t>
+          <t>Philadelphia 76ers vs Los Angeles Lakers</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2662?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260204</t>
+          <t>https://www.cryptoarena.com/events/detail/lakers76ers020526</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -10777,56 +10749,56 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Seattle Kraken vs Los Angeles Kings</t>
+          <t>Cleveland Cavaliers vs LA Clippers</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>https://www.cryptoarena.com/events/detail/kingskraken020426</t>
+          <t>https://intuitdome.com/events/event-schedule/2662?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260204</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers vs LA Clippers</t>
+          <t>Seattle Kraken vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>https://intuitdome.com/events/event-schedule/2686?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260202</t>
+          <t>https://www.cryptoarena.com/events/detail/kingskraken020426</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>L.A. Memorial Coliseum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -10841,17 +10813,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>LAFC vs Inter Miami CF</t>
+          <t>Philadelphia 76ers vs LA Clippers</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/lafc-vs-intermiami-2026/</t>
+          <t>https://intuitdome.com/events/event-schedule/2686?type=games&amp;utm_source=eventschedule&amp;utm_medium=IDwebsite&amp;utm_campaign=SGT_2526&amp;utm_content=SGT_2526_260202</t>
         </is>
       </c>
     </row>
@@ -10878,29 +10850,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Night of Hope</t>
+          <t>LAFC vs Inter Miami CF</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>https://www.lacoliseum.com/events/night-of-hope/</t>
+          <t>https://www.lacoliseum.com/events/lafc-vs-intermiami-2026/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Kia Forum</t>
+          <t>L.A. Memorial Coliseum</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10910,19 +10882,19 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>NEW EDITION</t>
+          <t>Night of Hope</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>https://thekiaforum.com/event/new-edition/</t>
+          <t>https://www.lacoliseum.com/events/night-of-hope/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10942,12 +10914,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>IBJJF Jiu Jitsu Championship</t>
+          <t>NEW EDITION</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/ibjjf-jiu-jitsu-championship</t>
+          <t>https://thekiaforum.com/event/new-edition/</t>
         </is>
       </c>
     </row>
@@ -10974,44 +10946,44 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Grand Archive Phantom Monarch Regional Championships</t>
+          <t>IBJJF Jiu Jitsu Championship</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/grand-archive-phantom-monarch-regional-championships</t>
+          <t>https://www.laconventioncenter.com/events/detail/ibjjf-jiu-jitsu-championship</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>LA Convention Center</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Olivia Rodrigo</t>
+          <t>Grand Archive Phantom Monarch Regional Championships</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
+          <t>https://www.laconventioncenter.com/events/detail/grand-archive-phantom-monarch-regional-championships</t>
         </is>
       </c>
     </row>
@@ -11023,12 +10995,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>01/28/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11043,7 +11015,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3918?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270129</t>
         </is>
       </c>
     </row>
@@ -11055,12 +11027,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>01/25/2026</t>
+          <t>01/28/2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11075,7 +11047,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3917?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270128</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11059,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/25/2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -11107,7 +11079,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3916?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270125</t>
         </is>
       </c>
     </row>
@@ -11119,12 +11091,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>01/21/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11139,7 +11111,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3915?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270124</t>
         </is>
       </c>
     </row>
@@ -11151,12 +11123,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>01/20/2026</t>
+          <t>01/21/2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11171,7 +11143,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3914?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270121</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11155,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/20/2026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -11203,7 +11175,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3913?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270120</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11187,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>01/16/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -11235,7 +11207,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3891?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270117</t>
         </is>
       </c>
     </row>
@@ -11247,12 +11219,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>01/13/2026</t>
+          <t>01/16/2026</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -11267,7 +11239,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3890?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270116</t>
         </is>
       </c>
     </row>
@@ -11279,12 +11251,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/13/2026</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11299,39 +11271,39 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3889?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270113</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>LA Convention Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Modern Language Association Annual Convention 2027</t>
+          <t>Olivia Rodrigo</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>https://www.laconventioncenter.com/events/detail/modern-language-association-annual-convention-2027</t>
+          <t>https://www.intuitdome.com/events/event-schedule/3888?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=olivia_rodrigo_270112</t>
         </is>
       </c>
     </row>
@@ -11343,25 +11315,57 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Modern Language Association Annual Convention 2027</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laconventioncenter.com/events/detail/modern-language-association-annual-convention-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>LA Convention Center</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>TBA</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>LA Art Show 2027</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>https://www.laconventioncenter.com/events/detail/la-art-show-2027</t>
         </is>
@@ -11580,6 +11584,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId209"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId212"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11591,7 +11596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12522,25 +12527,79 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10/30/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Phoebe Bridgers</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/4041?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=phoebe_bridgers_261030</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Phoebe Bridgers</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intuitdome.com/events/event-schedule/4050?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=phoebe_bridgers_261031</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>11/22/2026</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Three Days Grace</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>https://www.intuitdome.com/events/event-schedule/3149?utm_source=IDwebsite&amp;utm_medium=eventschedule&amp;utm_campaign=IDevents26&amp;utm_content=three_days_grace_261122</t>
         </is>
@@ -12582,6 +12641,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -440,14 +440,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,1238 +480,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>06/12/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>USA vs. Paraguay – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-usa-paraguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>06/15/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>IR Iran vs. New Zealand – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-iran-new-zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>06/18/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Switzerland vs. Bosnia and Herzegovina – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-switzerland-vs-bosnia-and-herzegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>06/21/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Belgium vs. IR Iran – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-belgium-iran</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06/25/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Türkiye vs. USA – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-turkiye-vs-usa</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>06/28/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-june28</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>07/02/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Round of 32: TBD vs. TBD – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-roundof32-july2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Quarterfinals: TBD vs. TBD – FIFA World Cup 26™</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/fifa-world-cup-quarterfinal-july10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>08/08/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5:30 PM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Ed Sheeran – With Myles Smith, Sigrid, Aaron Rowe</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/ed-sheeran-august-8-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>08/14/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/karol-g-august-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>08/15/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/karol-g-august-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>08/16/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>KAROL G - VIAJANDO POR EL MUNDO TROPITOUR</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/karol-g-august-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>08/20/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Chargers vs 49ers – Preseason</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-49ers-preseason-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>08/22/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1:00 PM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Rams vs. Saints – Preseason</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/rams-saints-preseason-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>08/27/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Chargers vs Rams – Preseason</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/chargers-rams-preseason-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/bts-september-1-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>09/02/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/bts-september-2-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/bts-september-5-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>BTS – BTS WORLD TOUR ‘ARIRANG’ IN LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofistadium.com/events/detail/bts-september-6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>09/13/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1:25 PM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Chargers vs. Cardinals – We